--- a/Previsao Orcamentaria.xlsx
+++ b/Previsao Orcamentaria.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="505" documentId="11_A8DEA55DA9ACCEB6161F69D90F8A6D5701A14124" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7AB715C-8C42-496C-A72D-1A8FF6A97B01}"/>
+  <xr:revisionPtr revIDLastSave="518" documentId="11_A8DEA55DA9ACCEB6161F69D90F8A6D5701A14124" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8DA7EA-994A-42D6-9645-833B6A1F1DBC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PREVISTO 2026 REVISADO" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="JR_PAGE_ANCHOR_0_1" localSheetId="2">'PREVISTO 2026 REVISADO (2)'!#REF!</definedName>
     <definedName name="JR_PAGE_ANCHOR_0_1">'REALIZADO 2025'!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -981,6 +981,39 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -996,43 +1029,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1041,17 +1038,20 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1394,53 +1394,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
+      <c r="C1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
     </row>
     <row r="2" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
     </row>
     <row r="3" spans="3:22" ht="16.5" customHeight="1">
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83"/>
       <c r="F3" s="31" t="s">
         <v>3</v>
       </c>
@@ -1486,11 +1486,11 @@
       <c r="T3" s="32"/>
     </row>
     <row r="4" spans="3:22" ht="12">
-      <c r="C4" s="77" t="s">
+      <c r="C4" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
       <c r="F4" s="23" t="e">
         <f>F5+F22+F38+F78+F86+#REF!</f>
         <v>#REF!</v>
@@ -1552,11 +1552,11 @@
       </c>
     </row>
     <row r="5" spans="3:22" ht="12">
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
       <c r="F5" s="8">
         <f>SUM(F6:F21)</f>
         <v>9137.3607499999998</v>
@@ -1615,11 +1615,11 @@
       </c>
     </row>
     <row r="6" spans="3:22" ht="12">
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
       <c r="F6" s="3">
         <v>34</v>
       </c>
@@ -1676,11 +1676,11 @@
       <c r="T6" s="5"/>
     </row>
     <row r="7" spans="3:22" ht="12">
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="3">
         <f>'REALIZADO 2025'!D29*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1740,11 +1740,11 @@
       <c r="T7" s="5"/>
     </row>
     <row r="8" spans="3:22" ht="12">
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="F8" s="3">
         <f>'REALIZADO 2025'!D30*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1804,11 +1804,11 @@
       <c r="T8" s="5"/>
     </row>
     <row r="9" spans="3:22" ht="12">
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
       <c r="F9" s="3">
         <f>'REALIZADO 2025'!D31*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1868,11 +1868,11 @@
       <c r="T9" s="5"/>
     </row>
     <row r="10" spans="3:22" ht="12">
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
       <c r="F10" s="3">
         <f>'REALIZADO 2025'!D34*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1932,11 +1932,11 @@
       <c r="T10" s="5"/>
     </row>
     <row r="11" spans="3:22" ht="12">
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
       <c r="F11" s="3">
         <f>'REALIZADO 2025'!D35*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>372.17674999999997</v>
@@ -1996,11 +1996,11 @@
       <c r="T11" s="5"/>
     </row>
     <row r="12" spans="3:22" ht="12">
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
       <c r="F12" s="3">
         <f>'REALIZADO 2025'!D36*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>522.5</v>
@@ -2060,11 +2060,11 @@
       <c r="T12" s="5"/>
     </row>
     <row r="13" spans="3:22" ht="12">
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
       <c r="F13" s="3">
         <f>'REALIZADO 2025'!D37*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2124,11 +2124,11 @@
       <c r="T13" s="5"/>
     </row>
     <row r="14" spans="3:22" ht="12">
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
       <c r="F14" s="3">
         <f t="shared" ref="F14:Q14" si="3">5043.17*$U$4</f>
         <v>5270.11265</v>
@@ -2188,11 +2188,11 @@
       <c r="T14" s="5"/>
     </row>
     <row r="15" spans="3:22" ht="12">
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
       <c r="F15" s="3">
         <f t="shared" ref="F15:Q15" si="4">2570.4*$U$4</f>
         <v>2686.0679999999998</v>
@@ -2252,11 +2252,11 @@
       <c r="T15" s="5"/>
     </row>
     <row r="16" spans="3:22" ht="12">
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
       <c r="F16" s="3">
         <f>'REALIZADO 2025'!D40*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2316,11 +2316,11 @@
       <c r="T16" s="5"/>
     </row>
     <row r="17" spans="3:22" ht="12">
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="3">
         <f>'REALIZADO 2025'!D41*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2380,11 +2380,11 @@
       <c r="T17" s="5"/>
     </row>
     <row r="18" spans="3:22" ht="12">
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
       <c r="F18" s="3">
         <f>'REALIZADO 2025'!D42*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2444,11 +2444,11 @@
       <c r="T18" s="5"/>
     </row>
     <row r="19" spans="3:22" ht="12">
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
       <c r="F19" s="3">
         <f>'REALIZADO 2025'!D43*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2508,11 +2508,11 @@
       <c r="T19" s="5"/>
     </row>
     <row r="20" spans="3:22" ht="12">
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
       <c r="F20" s="3">
         <f>'REALIZADO 2025'!D44*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>252.50334999999998</v>
@@ -2572,11 +2572,11 @@
       <c r="T20" s="5"/>
     </row>
     <row r="21" spans="3:22" ht="12">
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="3">
         <f>'REALIZADO 2025'!D45*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2636,11 +2636,11 @@
       <c r="T21" s="5"/>
     </row>
     <row r="22" spans="3:22" ht="12">
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
       <c r="F22" s="7">
         <f>SUM(F23:F37)</f>
         <v>154479.97080000001</v>
@@ -2708,11 +2708,11 @@
       </c>
     </row>
     <row r="23" spans="3:22" ht="12">
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
       <c r="F23" s="3">
         <f>'REALIZADO 2025'!D47*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>52560.36</v>
@@ -2772,11 +2772,11 @@
       <c r="T23" s="5"/>
     </row>
     <row r="24" spans="3:22" ht="12">
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
       <c r="F24" s="3">
         <f>'REALIZADO 2025'!D48*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>23252.497200000002</v>
@@ -2836,11 +2836,11 @@
       <c r="T24" s="5"/>
     </row>
     <row r="25" spans="3:22" ht="12">
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
       <c r="F25" s="3">
         <f>'REALIZADO 2025'!D49*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>77.652000000000015</v>
@@ -2899,11 +2899,11 @@
       <c r="T25" s="5"/>
     </row>
     <row r="26" spans="3:22" ht="12">
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
       <c r="F26" s="3">
         <f>'REALIZADO 2025'!D50*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>266.14440000000002</v>
@@ -2963,11 +2963,11 @@
       <c r="T26" s="5"/>
     </row>
     <row r="27" spans="3:22" ht="12">
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
       <c r="F27" s="3">
         <f>'REALIZADO 2025'!D51*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3027,11 +3027,11 @@
       <c r="T27" s="5"/>
     </row>
     <row r="28" spans="3:22" ht="12">
-      <c r="C28" s="79" t="s">
+      <c r="C28" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
       <c r="F28" s="3">
         <f>'REALIZADO 2025'!D52*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>3033.6120000000001</v>
@@ -3091,11 +3091,11 @@
       <c r="T28" s="5"/>
     </row>
     <row r="29" spans="3:22" ht="12">
-      <c r="C29" s="79" t="s">
+      <c r="C29" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
       <c r="F29" s="3">
         <f>'REALIZADO 2025'!D53*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>319.59360000000004</v>
@@ -3155,11 +3155,11 @@
       <c r="T29" s="5"/>
     </row>
     <row r="30" spans="3:22" ht="12">
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="3">
         <f>'REALIZADO 2025'!D54*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>324</v>
@@ -3219,11 +3219,11 @@
       <c r="T30" s="5"/>
     </row>
     <row r="31" spans="3:22" ht="12">
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
       <c r="F31" s="3">
         <f>'REALIZADO 2025'!D55*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3283,11 +3283,11 @@
       <c r="T31" s="5"/>
     </row>
     <row r="32" spans="3:22" ht="12">
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
       <c r="F32" s="3">
         <f>'REALIZADO 2025'!D57*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>26005.406400000003</v>
@@ -3347,11 +3347,11 @@
       <c r="T32" s="5"/>
     </row>
     <row r="33" spans="3:22" ht="12">
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
       <c r="F33" s="3">
         <f>'REALIZADO 2025'!D58*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>5940.0108000000009</v>
@@ -3411,11 +3411,11 @@
       <c r="T33" s="5"/>
     </row>
     <row r="34" spans="3:22" ht="12">
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
       <c r="F34" s="3">
         <f>'REALIZADO 2025'!D59*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3475,11 +3475,11 @@
       <c r="T34" s="5"/>
     </row>
     <row r="35" spans="3:22" ht="12">
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
       <c r="F35" s="3">
         <f>'REALIZADO 2025'!D60*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>41884.214400000004</v>
@@ -3539,11 +3539,11 @@
       <c r="T35" s="5"/>
     </row>
     <row r="36" spans="3:22" ht="12">
-      <c r="C36" s="79" t="s">
+      <c r="C36" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
       <c r="F36" s="3">
         <f>'REALIZADO 2025'!D61*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3602,11 +3602,11 @@
       <c r="T36" s="5"/>
     </row>
     <row r="37" spans="3:22" ht="12">
-      <c r="C37" s="79" t="s">
+      <c r="C37" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
       <c r="F37" s="3">
         <f>'REALIZADO 2025'!D62*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>816.48</v>
@@ -3666,11 +3666,11 @@
       <c r="T37" s="5"/>
     </row>
     <row r="38" spans="3:22" ht="12.75" customHeight="1">
-      <c r="C38" s="80" t="s">
+      <c r="C38" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
       <c r="F38" s="7">
         <f t="shared" ref="F38:R38" si="7">F39+F55+F68+F72</f>
         <v>48895.278299999998</v>
@@ -3738,11 +3738,11 @@
       </c>
     </row>
     <row r="39" spans="3:22" ht="12" customHeight="1">
-      <c r="C39" s="78" t="s">
+      <c r="C39" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="8">
         <f>SUM(F40:F48)</f>
         <v>11772.990900000001</v>
@@ -3803,11 +3803,11 @@
       <c r="V39" s="58"/>
     </row>
     <row r="40" spans="3:22" ht="12">
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
       <c r="F40" s="3">
         <f>'REALIZADO 2025'!D65*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1550.68595</v>
@@ -3867,11 +3867,11 @@
       <c r="V40" s="58"/>
     </row>
     <row r="41" spans="3:22" ht="12">
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="79"/>
-      <c r="E41" s="79"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
       <c r="F41" s="3">
         <f>'REALIZADO 2025'!D67*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -3932,11 +3932,11 @@
       <c r="V41" s="58"/>
     </row>
     <row r="42" spans="3:22" ht="12">
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
       <c r="F42" s="3">
         <f>'REALIZADO 2025'!D68*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>3193.8857499999995</v>
@@ -3996,11 +3996,11 @@
       <c r="V42" s="58"/>
     </row>
     <row r="43" spans="3:22" ht="12">
-      <c r="C43" s="79" t="s">
+      <c r="C43" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="79"/>
-      <c r="E43" s="79"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
       <c r="F43" s="3">
         <f>'REALIZADO 2025'!D69*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>610.80250000000001</v>
@@ -4059,11 +4059,11 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="3:22" ht="12">
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
       <c r="F44" s="3">
         <f>'REALIZADO 2025'!D70*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>554.51879999999994</v>
@@ -4123,11 +4123,11 @@
       <c r="T44" s="5"/>
     </row>
     <row r="45" spans="3:22" ht="12">
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="79"/>
-      <c r="E45" s="79"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
       <c r="F45" s="3">
         <f>'REALIZADO 2025'!D71*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4187,11 +4187,11 @@
       <c r="T45" s="5"/>
     </row>
     <row r="46" spans="3:22" ht="12">
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
       <c r="F46" s="3">
         <f>'REALIZADO 2025'!D72*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>5500.8486499999999</v>
@@ -4250,11 +4250,11 @@
       <c r="T46" s="5"/>
     </row>
     <row r="47" spans="3:22" ht="12">
-      <c r="C47" s="82" t="s">
+      <c r="C47" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
       <c r="F47" s="3">
         <f>'REALIZADO 2025'!D73*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>349.70924999999994</v>
@@ -4313,11 +4313,11 @@
       <c r="T47" s="5"/>
     </row>
     <row r="48" spans="3:22" ht="12">
-      <c r="C48" s="79" t="s">
+      <c r="C48" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
       <c r="F48" s="3">
         <f>'REALIZADO 2025'!D74*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>12.54</v>
@@ -4377,11 +4377,11 @@
       <c r="T48" s="5"/>
     </row>
     <row r="49" spans="3:20" ht="12">
-      <c r="C49" s="81" t="s">
+      <c r="C49" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
@@ -4404,11 +4404,11 @@
       <c r="T49" s="5"/>
     </row>
     <row r="50" spans="3:20" ht="12">
-      <c r="C50" s="81" t="s">
+      <c r="C50" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -4431,11 +4431,11 @@
       <c r="T50" s="5"/>
     </row>
     <row r="51" spans="3:20" ht="12">
-      <c r="C51" s="81" t="s">
+      <c r="C51" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
@@ -4458,11 +4458,11 @@
       <c r="T51" s="5"/>
     </row>
     <row r="52" spans="3:20" ht="12">
-      <c r="C52" s="81" t="s">
+      <c r="C52" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
+      <c r="D52" s="76"/>
+      <c r="E52" s="76"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -4485,11 +4485,11 @@
       <c r="T52" s="5"/>
     </row>
     <row r="53" spans="3:20" ht="12">
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="76"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -4512,11 +4512,11 @@
       <c r="T53" s="5"/>
     </row>
     <row r="54" spans="3:20" ht="12">
-      <c r="C54" s="81" t="s">
+      <c r="C54" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="81"/>
-      <c r="E54" s="81"/>
+      <c r="D54" s="75"/>
+      <c r="E54" s="75"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -4539,11 +4539,11 @@
       <c r="T54" s="5"/>
     </row>
     <row r="55" spans="3:20" ht="12" customHeight="1">
-      <c r="C55" s="78" t="s">
+      <c r="C55" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="D55" s="78"/>
-      <c r="E55" s="78"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
       <c r="F55" s="8">
         <f>SUM(F56:F67)</f>
         <v>13069.940399999999</v>
@@ -4603,11 +4603,11 @@
       <c r="T55" s="5"/>
     </row>
     <row r="56" spans="3:20" ht="12">
-      <c r="C56" s="79" t="s">
+      <c r="C56" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="69"/>
       <c r="F56" s="3">
         <f>'REALIZADO 2025'!D76*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1201.7082</v>
@@ -4667,11 +4667,11 @@
       <c r="T56" s="5"/>
     </row>
     <row r="57" spans="3:20" ht="12">
-      <c r="C57" s="79" t="s">
+      <c r="C57" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="69"/>
       <c r="F57" s="3">
         <f>'REALIZADO 2025'!D77*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4731,11 +4731,11 @@
       <c r="T57" s="5"/>
     </row>
     <row r="58" spans="3:20" ht="12">
-      <c r="C58" s="79" t="s">
+      <c r="C58" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="69"/>
       <c r="F58" s="3">
         <f>'REALIZADO 2025'!D78*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>888.24999999999989</v>
@@ -4795,11 +4795,11 @@
       <c r="T58" s="5"/>
     </row>
     <row r="59" spans="3:20" ht="12">
-      <c r="C59" s="79" t="s">
+      <c r="C59" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="69"/>
       <c r="F59" s="3">
         <f>'REALIZADO 2025'!D79*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4859,11 +4859,11 @@
       <c r="T59" s="5"/>
     </row>
     <row r="60" spans="3:20" ht="12">
-      <c r="C60" s="79" t="s">
+      <c r="C60" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="79"/>
-      <c r="E60" s="79"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="69"/>
       <c r="F60" s="3">
         <f>'REALIZADO 2025'!D80*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2080.5113999999999</v>
@@ -4922,11 +4922,11 @@
       <c r="T60" s="5"/>
     </row>
     <row r="61" spans="3:20" ht="12">
-      <c r="C61" s="79" t="s">
+      <c r="C61" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="69"/>
       <c r="F61" s="3">
         <f>'REALIZADO 2025'!D81*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4986,11 +4986,11 @@
       <c r="T61" s="5"/>
     </row>
     <row r="62" spans="3:20" ht="12">
-      <c r="C62" s="79" t="s">
+      <c r="C62" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D62" s="79"/>
-      <c r="E62" s="79"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="69"/>
       <c r="F62" s="3">
         <f>'REALIZADO 2025'!D82*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>7691.6597999999994</v>
@@ -5050,11 +5050,11 @@
       <c r="T62" s="5"/>
     </row>
     <row r="63" spans="3:20" ht="12">
-      <c r="C63" s="79" t="s">
+      <c r="C63" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="79"/>
-      <c r="E63" s="79"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="69"/>
       <c r="F63" s="3">
         <f>'REALIZADO 2025'!D83*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1149.5</v>
@@ -5113,11 +5113,11 @@
       <c r="T63" s="5"/>
     </row>
     <row r="64" spans="3:20" ht="12">
-      <c r="C64" s="79" t="s">
+      <c r="C64" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="79"/>
-      <c r="E64" s="79"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="69"/>
       <c r="F64" s="3">
         <f>'REALIZADO 2025'!D84*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -5177,11 +5177,11 @@
       <c r="T64" s="5"/>
     </row>
     <row r="65" spans="3:21" ht="12">
-      <c r="C65" s="79" t="s">
+      <c r="C65" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="79"/>
-      <c r="E65" s="79"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="69"/>
       <c r="F65" s="3">
         <f>'REALIZADO 2025'!D85*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>58.310999999999993</v>
@@ -5241,11 +5241,11 @@
       <c r="T65" s="5"/>
     </row>
     <row r="66" spans="3:21" ht="12">
-      <c r="C66" s="79" t="s">
+      <c r="C66" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="79"/>
-      <c r="E66" s="79"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="69"/>
       <c r="F66" s="3">
         <f>'REALIZADO 2025'!D86*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -5305,11 +5305,11 @@
       <c r="T66" s="5"/>
     </row>
     <row r="67" spans="3:21" ht="12">
-      <c r="C67" s="79" t="s">
+      <c r="C67" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="D67" s="79"/>
-      <c r="E67" s="79"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="69"/>
       <c r="F67" s="3">
         <f>'REALIZADO 2025'!D87*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -5369,11 +5369,11 @@
       <c r="T67" s="5"/>
     </row>
     <row r="68" spans="3:21" ht="12">
-      <c r="C68" s="78" t="s">
+      <c r="C68" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="D68" s="78"/>
-      <c r="E68" s="78"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="74"/>
       <c r="F68" s="8">
         <f>SUM(F69:F71)</f>
         <v>16132.187499999998</v>
@@ -5433,11 +5433,11 @@
       <c r="T68" s="5"/>
     </row>
     <row r="69" spans="3:21" ht="12">
-      <c r="C69" s="79" t="s">
+      <c r="C69" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="69"/>
       <c r="F69" s="3">
         <f>'REALIZADO 2025'!D89*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>6040.6224999999995</v>
@@ -5497,11 +5497,11 @@
       <c r="T69" s="5"/>
     </row>
     <row r="70" spans="3:21" ht="12">
-      <c r="C70" s="79" t="s">
+      <c r="C70" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
       <c r="F70" s="3">
         <f>'REALIZADO 2025'!D90*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>7357.8449999999993</v>
@@ -5560,11 +5560,11 @@
       <c r="T70" s="5"/>
     </row>
     <row r="71" spans="3:21" ht="12">
-      <c r="C71" s="79" t="s">
+      <c r="C71" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D71" s="79"/>
-      <c r="E71" s="79"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
       <c r="F71" s="3">
         <f>'REALIZADO 2025'!D91*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2733.72</v>
@@ -5624,11 +5624,11 @@
       <c r="T71" s="5"/>
     </row>
     <row r="72" spans="3:21" ht="12">
-      <c r="C72" s="78" t="s">
+      <c r="C72" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
       <c r="F72" s="8">
         <f>SUM(F73:F77)</f>
         <v>7920.1594999999998</v>
@@ -5688,11 +5688,11 @@
       <c r="T72" s="5"/>
     </row>
     <row r="73" spans="3:21" ht="12">
-      <c r="C73" s="79" t="s">
+      <c r="C73" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="D73" s="79"/>
-      <c r="E73" s="79"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
       <c r="F73" s="3">
         <f>'REALIZADO 2025'!D93*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>909.15</v>
@@ -5752,11 +5752,11 @@
       <c r="T73" s="5"/>
     </row>
     <row r="74" spans="3:21" ht="12">
-      <c r="C74" s="79" t="s">
+      <c r="C74" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="D74" s="79"/>
-      <c r="E74" s="79"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
       <c r="F74" s="3">
         <f>'REALIZADO 2025'!D94*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>752.4</v>
@@ -5816,11 +5816,11 @@
       <c r="T74" s="5"/>
     </row>
     <row r="75" spans="3:21" ht="12">
-      <c r="C75" s="79" t="s">
+      <c r="C75" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="D75" s="79"/>
-      <c r="E75" s="79"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
       <c r="F75" s="3">
         <f>'REALIZADO 2025'!D95*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2403.5</v>
@@ -5880,11 +5880,11 @@
       <c r="T75" s="5"/>
     </row>
     <row r="76" spans="3:21" ht="12">
-      <c r="C76" s="79" t="s">
+      <c r="C76" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="D76" s="79"/>
-      <c r="E76" s="79"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
       <c r="F76" s="3">
         <f>'REALIZADO 2025'!D96*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1472.5094999999999</v>
@@ -5943,11 +5943,11 @@
       <c r="T76" s="5"/>
     </row>
     <row r="77" spans="3:21" ht="12">
-      <c r="C77" s="79" t="s">
+      <c r="C77" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="79"/>
-      <c r="E77" s="79"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="69"/>
       <c r="F77" s="3">
         <f>'REALIZADO 2025'!D97*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2382.6</v>
@@ -6007,11 +6007,11 @@
       <c r="T77" s="5"/>
     </row>
     <row r="78" spans="3:21" ht="12">
-      <c r="C78" s="78" t="s">
+      <c r="C78" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="78"/>
-      <c r="E78" s="78"/>
+      <c r="D78" s="74"/>
+      <c r="E78" s="74"/>
       <c r="F78" s="8">
         <f t="shared" ref="F78:R78" si="13">SUM(F79:F85)</f>
         <v>74062.399949999992</v>
@@ -6076,11 +6076,11 @@
       </c>
     </row>
     <row r="79" spans="3:21" ht="12">
-      <c r="C79" s="79" t="s">
+      <c r="C79" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="79"/>
-      <c r="E79" s="79"/>
+      <c r="D79" s="69"/>
+      <c r="E79" s="69"/>
       <c r="F79" s="3">
         <f>'REALIZADO 2025'!D99*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>4117.2999999999993</v>
@@ -6140,11 +6140,11 @@
       <c r="T79" s="5"/>
     </row>
     <row r="80" spans="3:21" ht="12">
-      <c r="C80" s="79" t="s">
+      <c r="C80" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="D80" s="79"/>
-      <c r="E80" s="79"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="69"/>
       <c r="F80" s="3">
         <f>'REALIZADO 2025'!D100*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>2951.08</v>
@@ -6204,11 +6204,11 @@
       <c r="T80" s="5"/>
     </row>
     <row r="81" spans="3:21" ht="12">
-      <c r="C81" s="79" t="s">
+      <c r="C81" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D81" s="79"/>
-      <c r="E81" s="79"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="69"/>
       <c r="F81" s="3">
         <f>'REALIZADO 2025'!D101*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>4270.2671</v>
@@ -6268,11 +6268,11 @@
       <c r="T81" s="5"/>
     </row>
     <row r="82" spans="3:21" ht="12">
-      <c r="C82" s="79" t="s">
+      <c r="C82" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="D82" s="79"/>
-      <c r="E82" s="79"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="69"/>
       <c r="F82" s="3">
         <f>'REALIZADO 2025'!D102*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>58965.410349999998</v>
@@ -6332,11 +6332,11 @@
       <c r="T82" s="5"/>
     </row>
     <row r="83" spans="3:21" ht="12">
-      <c r="C83" s="79" t="s">
+      <c r="C83" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="D83" s="79"/>
-      <c r="E83" s="79"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="69"/>
       <c r="F83" s="3">
         <f>'REALIZADO 2025'!D103*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>0</v>
@@ -6396,11 +6396,11 @@
       <c r="T83" s="5"/>
     </row>
     <row r="84" spans="3:21" ht="12">
-      <c r="C84" s="79" t="s">
+      <c r="C84" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="D84" s="79"/>
-      <c r="E84" s="79"/>
+      <c r="D84" s="69"/>
+      <c r="E84" s="69"/>
       <c r="F84" s="3">
         <f>'REALIZADO 2025'!D104*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>2508</v>
@@ -6460,11 +6460,11 @@
       <c r="T84" s="5"/>
     </row>
     <row r="85" spans="3:21" ht="12">
-      <c r="C85" s="79" t="s">
+      <c r="C85" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="69"/>
       <c r="F85" s="3">
         <f>'REALIZADO 2025'!D106*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>1250.3425</v>
@@ -6524,11 +6524,11 @@
       <c r="T85" s="5"/>
     </row>
     <row r="86" spans="3:21" ht="12">
-      <c r="C86" s="78" t="s">
+      <c r="C86" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="D86" s="78"/>
-      <c r="E86" s="78"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="74"/>
       <c r="F86" s="8">
         <f>SUM(F87:F98)</f>
         <v>15905.234399999999</v>
@@ -6593,11 +6593,11 @@
       </c>
     </row>
     <row r="87" spans="3:21" ht="12">
-      <c r="C87" s="79" t="s">
+      <c r="C87" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="D87" s="79"/>
-      <c r="E87" s="79"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="69"/>
       <c r="F87" s="3">
         <f>'REALIZADO 2025'!D109*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>11147.161299999998</v>
@@ -6656,11 +6656,11 @@
       <c r="T87" s="5"/>
     </row>
     <row r="88" spans="3:21" ht="12">
-      <c r="C88" s="79" t="s">
+      <c r="C88" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="D88" s="79"/>
-      <c r="E88" s="79"/>
+      <c r="D88" s="69"/>
+      <c r="E88" s="69"/>
       <c r="F88" s="3">
         <f>'REALIZADO 2025'!D110*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>1863.7366</v>
@@ -6719,11 +6719,11 @@
       <c r="T88" s="5"/>
     </row>
     <row r="89" spans="3:21" ht="12">
-      <c r="C89" s="79" t="s">
+      <c r="C89" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="D89" s="79"/>
-      <c r="E89" s="79"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
       <c r="F89" s="3">
         <f>'REALIZADO 2025'!D111*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>0</v>
@@ -6783,11 +6783,11 @@
       <c r="T89" s="5"/>
     </row>
     <row r="90" spans="3:21" ht="12">
-      <c r="C90" s="79" t="s">
+      <c r="C90" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="79"/>
-      <c r="E90" s="79"/>
+      <c r="D90" s="69"/>
+      <c r="E90" s="69"/>
       <c r="F90" s="3">
         <f>'REALIZADO 2025'!D112*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>169.6035</v>
@@ -6847,11 +6847,11 @@
       <c r="T90" s="5"/>
     </row>
     <row r="91" spans="3:21" ht="12">
-      <c r="C91" s="79" t="s">
+      <c r="C91" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="D91" s="79"/>
-      <c r="E91" s="79"/>
+      <c r="D91" s="69"/>
+      <c r="E91" s="69"/>
       <c r="F91" s="3">
         <f>'REALIZADO 2025'!D113*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>0</v>
@@ -6911,11 +6911,11 @@
       <c r="T91" s="5"/>
     </row>
     <row r="92" spans="3:21" ht="12">
-      <c r="C92" s="79" t="s">
+      <c r="C92" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="D92" s="79"/>
-      <c r="E92" s="79"/>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
       <c r="F92" s="3">
         <f>'REALIZADO 2025'!D114*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>102.8489</v>
@@ -6975,11 +6975,11 @@
       <c r="T92" s="5"/>
     </row>
     <row r="93" spans="3:21" ht="12">
-      <c r="C93" s="79" t="s">
+      <c r="C93" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="D93" s="79"/>
-      <c r="E93" s="79"/>
+      <c r="D93" s="69"/>
+      <c r="E93" s="69"/>
       <c r="F93" s="3">
         <f>'REALIZADO 2025'!D115*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>208.98955000000001</v>
@@ -7039,11 +7039,11 @@
       <c r="T93" s="5"/>
     </row>
     <row r="94" spans="3:21" ht="12">
-      <c r="C94" s="79" t="s">
+      <c r="C94" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="D94" s="79"/>
-      <c r="E94" s="79"/>
+      <c r="D94" s="69"/>
+      <c r="E94" s="69"/>
       <c r="F94" s="3">
         <f>'REALIZADO 2025'!D116*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>0</v>
@@ -7103,11 +7103,11 @@
       <c r="T94" s="5"/>
     </row>
     <row r="95" spans="3:21" ht="12">
-      <c r="C95" s="79" t="s">
+      <c r="C95" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="D95" s="79"/>
-      <c r="E95" s="79"/>
+      <c r="D95" s="69"/>
+      <c r="E95" s="69"/>
       <c r="F95" s="3">
         <f>'REALIZADO 2025'!D117*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>101.25004999999999</v>
@@ -7167,11 +7167,11 @@
       <c r="T95" s="5"/>
     </row>
     <row r="96" spans="3:21" ht="12">
-      <c r="C96" s="79" t="s">
+      <c r="C96" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="79"/>
-      <c r="E96" s="79"/>
+      <c r="D96" s="69"/>
+      <c r="E96" s="69"/>
       <c r="F96" s="3">
         <f>'REALIZADO 2025'!D118*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>36.470499999999994</v>
@@ -7231,11 +7231,11 @@
       <c r="T96" s="5"/>
     </row>
     <row r="97" spans="3:20" ht="12">
-      <c r="C97" s="79" t="s">
+      <c r="C97" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="D97" s="79"/>
-      <c r="E97" s="79"/>
+      <c r="D97" s="69"/>
+      <c r="E97" s="69"/>
       <c r="F97" s="3">
         <f>'REALIZADO 2025'!D119*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>762.84999999999991</v>
@@ -7295,11 +7295,11 @@
       <c r="T97" s="5"/>
     </row>
     <row r="98" spans="3:20" ht="12">
-      <c r="C98" s="79" t="s">
+      <c r="C98" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="D98" s="79"/>
-      <c r="E98" s="79"/>
+      <c r="D98" s="69"/>
+      <c r="E98" s="69"/>
       <c r="F98" s="3">
         <f>'REALIZADO 2025'!D120*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>1512.3239999999998</v>
@@ -7359,11 +7359,11 @@
       <c r="T98" s="5"/>
     </row>
     <row r="99" spans="3:20" ht="12">
-      <c r="C99" s="84" t="s">
+      <c r="C99" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="84"/>
-      <c r="E99" s="84"/>
+      <c r="D99" s="70"/>
+      <c r="E99" s="70"/>
       <c r="F99" s="60" t="e">
         <f>F4</f>
         <v>#REF!</v>
@@ -7443,19 +7443,19 @@
       <c r="T100" s="32"/>
     </row>
     <row r="101" spans="3:20" ht="14.4">
-      <c r="C101" s="74" t="s">
+      <c r="C101" s="71" t="s">
         <v>114</v>
       </c>
-      <c r="D101" s="74"/>
+      <c r="D101" s="71"/>
       <c r="E101" s="64">
         <v>270297.34000000003</v>
       </c>
     </row>
     <row r="102" spans="3:20" ht="14.4">
-      <c r="C102" s="73" t="s">
+      <c r="C102" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="D102" s="73"/>
+      <c r="D102" s="72"/>
       <c r="E102" s="65">
         <f>S99</f>
         <v>284113.14483333332</v>
@@ -7463,10 +7463,10 @@
       <c r="F102" s="59"/>
     </row>
     <row r="103" spans="3:20" ht="14.4">
-      <c r="C103" s="75" t="s">
+      <c r="C103" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="D103" s="75"/>
+      <c r="D103" s="73"/>
       <c r="E103" s="66">
         <f>E102-E101</f>
         <v>13815.804833333299</v>
@@ -7474,10 +7474,10 @@
       <c r="F103" s="59"/>
     </row>
     <row r="104" spans="3:20" ht="14.4">
-      <c r="C104" s="76" t="s">
+      <c r="C104" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="D104" s="76"/>
+      <c r="D104" s="68"/>
       <c r="E104" s="67">
         <f>E103/E101</f>
         <v>5.1113358471575408E-2</v>
@@ -7521,85 +7521,6 @@
     <row r="135" ht="12"/>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C1:S1"/>
     <mergeCell ref="C2:S2"/>
     <mergeCell ref="C3:E3"/>
@@ -7624,6 +7545,85 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C96:E96"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -7651,11 +7651,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
       <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
@@ -7701,11 +7701,11 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:18" ht="12">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
       <c r="D2" s="33">
         <f>SUM(D3:D24)</f>
         <v>290185.64999999997</v>
@@ -7765,11 +7765,11 @@
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:18" ht="12">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="85" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="35">
         <v>239580.04</v>
       </c>
@@ -7817,11 +7817,11 @@
       <c r="R3" s="32"/>
     </row>
     <row r="4" spans="1:18" ht="12">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
       <c r="D4" s="38">
         <v>8221.9500000000007</v>
       </c>
@@ -7869,11 +7869,11 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:18" ht="12">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
       <c r="D5" s="35">
         <v>0</v>
       </c>
@@ -7921,11 +7921,11 @@
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:18" ht="12">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="86" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
       <c r="D6" s="38">
         <v>0</v>
       </c>
@@ -7973,11 +7973,11 @@
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:18" ht="12">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="85" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
       <c r="D7" s="35">
         <v>0</v>
       </c>
@@ -8025,11 +8025,11 @@
       <c r="R7" s="32"/>
     </row>
     <row r="8" spans="1:18" ht="12">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="38">
         <v>525</v>
       </c>
@@ -8077,11 +8077,11 @@
       <c r="R8" s="32"/>
     </row>
     <row r="9" spans="1:18" ht="12">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="85" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="35">
         <v>1260</v>
       </c>
@@ -8129,11 +8129,11 @@
       <c r="R9" s="32"/>
     </row>
     <row r="10" spans="1:18" ht="12">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="38">
         <v>1706.95</v>
       </c>
@@ -8181,11 +8181,11 @@
       <c r="R10" s="32"/>
     </row>
     <row r="11" spans="1:18" ht="12">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="35">
         <v>23926.35</v>
       </c>
@@ -8233,11 +8233,11 @@
       <c r="R11" s="32"/>
     </row>
     <row r="12" spans="1:18" ht="12">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="87"/>
-      <c r="C12" s="87"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="38">
         <v>150</v>
       </c>
@@ -8285,11 +8285,11 @@
       <c r="R12" s="32"/>
     </row>
     <row r="13" spans="1:18" ht="12">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="85"/>
       <c r="D13" s="35">
         <v>0</v>
       </c>
@@ -8337,11 +8337,11 @@
       <c r="R13" s="32"/>
     </row>
     <row r="14" spans="1:18" ht="12">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="87"/>
-      <c r="C14" s="87"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
       <c r="D14" s="38">
         <v>317.67</v>
       </c>
@@ -8389,11 +8389,11 @@
       <c r="R14" s="32"/>
     </row>
     <row r="15" spans="1:18" ht="12">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="85" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="85"/>
       <c r="D15" s="35">
         <v>1730</v>
       </c>
@@ -8441,11 +8441,11 @@
       <c r="R15" s="32"/>
     </row>
     <row r="16" spans="1:18" ht="12">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="87"/>
-      <c r="C16" s="87"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
       <c r="D16" s="38">
         <v>8050.48</v>
       </c>
@@ -8493,11 +8493,11 @@
       <c r="R16" s="32"/>
     </row>
     <row r="17" spans="1:18" ht="12">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="85" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="35">
         <v>50.02</v>
       </c>
@@ -8545,11 +8545,11 @@
       <c r="R17" s="32"/>
     </row>
     <row r="18" spans="1:18" ht="12">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="86" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="38">
         <v>500</v>
       </c>
@@ -8597,11 +8597,11 @@
       <c r="R18" s="32"/>
     </row>
     <row r="19" spans="1:18" ht="12">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="35">
         <v>0</v>
       </c>
@@ -8649,11 +8649,11 @@
       <c r="R19" s="32"/>
     </row>
     <row r="20" spans="1:18" ht="12">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
       <c r="D20" s="38">
         <v>2450.54</v>
       </c>
@@ -8701,11 +8701,11 @@
       <c r="R20" s="32"/>
     </row>
     <row r="21" spans="1:18" ht="12">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
       <c r="D21" s="35">
         <v>754.13</v>
       </c>
@@ -8753,11 +8753,11 @@
       <c r="R21" s="32"/>
     </row>
     <row r="22" spans="1:18" ht="12">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="86" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="87"/>
-      <c r="C22" s="87"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="38">
         <v>797.85</v>
       </c>
@@ -8805,11 +8805,11 @@
       <c r="R22" s="32"/>
     </row>
     <row r="23" spans="1:18" ht="12">
-      <c r="A23" s="86" t="s">
+      <c r="A23" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="35">
         <v>0</v>
       </c>
@@ -8857,11 +8857,11 @@
       <c r="R23" s="32"/>
     </row>
     <row r="24" spans="1:18" ht="12">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="87"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
       <c r="D24" s="38">
         <v>164.67</v>
       </c>
@@ -8909,11 +8909,11 @@
       <c r="R24" s="32"/>
     </row>
     <row r="25" spans="1:18" ht="12">
-      <c r="A25" s="85" t="s">
+      <c r="A25" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="39">
         <f>D2</f>
         <v>290185.64999999997</v>
@@ -8973,11 +8973,11 @@
       <c r="R25" s="32"/>
     </row>
     <row r="26" spans="1:18" ht="12">
-      <c r="A26" s="90" t="s">
+      <c r="A26" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
+      <c r="B26" s="87"/>
+      <c r="C26" s="87"/>
       <c r="D26" s="40">
         <f>D27+D46+D63+D98+D108+D121</f>
         <v>308825.78999999998</v>
@@ -9101,11 +9101,11 @@
       <c r="R27" s="32"/>
     </row>
     <row r="28" spans="1:18" ht="12">
-      <c r="A28" s="87" t="s">
+      <c r="A28" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="87"/>
-      <c r="C28" s="87"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
       <c r="D28" s="38">
         <v>553.58000000000004</v>
       </c>
@@ -9153,11 +9153,11 @@
       <c r="R28" s="32"/>
     </row>
     <row r="29" spans="1:18" ht="12">
-      <c r="A29" s="86" t="s">
+      <c r="A29" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
+      <c r="B29" s="85"/>
+      <c r="C29" s="85"/>
       <c r="D29" s="35">
         <v>0</v>
       </c>
@@ -9205,11 +9205,11 @@
       <c r="R29" s="32"/>
     </row>
     <row r="30" spans="1:18" ht="12">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
+      <c r="B30" s="86"/>
+      <c r="C30" s="86"/>
       <c r="D30" s="38">
         <v>0</v>
       </c>
@@ -9257,11 +9257,11 @@
       <c r="R30" s="32"/>
     </row>
     <row r="31" spans="1:18" ht="12">
-      <c r="A31" s="86" t="s">
+      <c r="A31" s="85" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="86"/>
-      <c r="C31" s="86"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="85"/>
       <c r="D31" s="35">
         <v>0</v>
       </c>
@@ -9309,11 +9309,11 @@
       <c r="R31" s="32"/>
     </row>
     <row r="32" spans="1:18" ht="12">
-      <c r="A32" s="87" t="s">
+      <c r="A32" s="86" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="87"/>
-      <c r="C32" s="87"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
       <c r="D32" s="38">
         <v>0</v>
       </c>
@@ -9361,11 +9361,11 @@
       <c r="R32" s="32"/>
     </row>
     <row r="33" spans="1:18" ht="12">
-      <c r="A33" s="86" t="s">
+      <c r="A33" s="85" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
+      <c r="B33" s="85"/>
+      <c r="C33" s="85"/>
       <c r="D33" s="35">
         <v>0</v>
       </c>
@@ -9413,11 +9413,11 @@
       <c r="R33" s="32"/>
     </row>
     <row r="34" spans="1:18" ht="12">
-      <c r="A34" s="87" t="s">
+      <c r="A34" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="87"/>
-      <c r="C34" s="87"/>
+      <c r="B34" s="86"/>
+      <c r="C34" s="86"/>
       <c r="D34" s="38">
         <v>0</v>
       </c>
@@ -9465,11 +9465,11 @@
       <c r="R34" s="32"/>
     </row>
     <row r="35" spans="1:18" ht="12">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="86"/>
-      <c r="C35" s="86"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="85"/>
       <c r="D35" s="35">
         <v>356.15</v>
       </c>
@@ -9517,11 +9517,11 @@
       <c r="R35" s="32"/>
     </row>
     <row r="36" spans="1:18" ht="12">
-      <c r="A36" s="87" t="s">
+      <c r="A36" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="87"/>
-      <c r="C36" s="87"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
       <c r="D36" s="38">
         <v>500</v>
       </c>
@@ -9569,11 +9569,11 @@
       <c r="R36" s="32"/>
     </row>
     <row r="37" spans="1:18" ht="12">
-      <c r="A37" s="86" t="s">
+      <c r="A37" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="86"/>
-      <c r="C37" s="86"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
       <c r="D37" s="35">
         <v>0</v>
       </c>
@@ -9621,11 +9621,11 @@
       <c r="R37" s="32"/>
     </row>
     <row r="38" spans="1:18" ht="12">
-      <c r="A38" s="87" t="s">
+      <c r="A38" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="87"/>
-      <c r="C38" s="87"/>
+      <c r="B38" s="86"/>
+      <c r="C38" s="86"/>
       <c r="D38" s="38">
         <v>4540</v>
       </c>
@@ -9673,11 +9673,11 @@
       <c r="R38" s="32"/>
     </row>
     <row r="39" spans="1:18" ht="12">
-      <c r="A39" s="86" t="s">
+      <c r="A39" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="86"/>
-      <c r="C39" s="86"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="85"/>
       <c r="D39" s="35">
         <v>2237.23</v>
       </c>
@@ -9725,11 +9725,11 @@
       <c r="R39" s="32"/>
     </row>
     <row r="40" spans="1:18" ht="12">
-      <c r="A40" s="87" t="s">
+      <c r="A40" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
       <c r="D40" s="38">
         <v>0</v>
       </c>
@@ -9777,11 +9777,11 @@
       <c r="R40" s="32"/>
     </row>
     <row r="41" spans="1:18" ht="12">
-      <c r="A41" s="86" t="s">
+      <c r="A41" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="85"/>
       <c r="D41" s="35">
         <v>0</v>
       </c>
@@ -9829,11 +9829,11 @@
       <c r="R41" s="32"/>
     </row>
     <row r="42" spans="1:18" ht="12">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="86"/>
       <c r="D42" s="38">
         <v>0</v>
       </c>
@@ -9881,11 +9881,11 @@
       <c r="R42" s="32"/>
     </row>
     <row r="43" spans="1:18" ht="12">
-      <c r="A43" s="86" t="s">
+      <c r="A43" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="86"/>
-      <c r="C43" s="86"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="85"/>
       <c r="D43" s="35">
         <v>0</v>
       </c>
@@ -9933,11 +9933,11 @@
       <c r="R43" s="32"/>
     </row>
     <row r="44" spans="1:18" ht="12">
-      <c r="A44" s="87" t="s">
+      <c r="A44" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="B44" s="87"/>
-      <c r="C44" s="87"/>
+      <c r="B44" s="86"/>
+      <c r="C44" s="86"/>
       <c r="D44" s="38">
         <v>241.63</v>
       </c>
@@ -9985,11 +9985,11 @@
       <c r="R44" s="32"/>
     </row>
     <row r="45" spans="1:18" ht="12">
-      <c r="A45" s="86" t="s">
+      <c r="A45" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="B45" s="86"/>
-      <c r="C45" s="86"/>
+      <c r="B45" s="85"/>
+      <c r="C45" s="85"/>
       <c r="D45" s="35">
         <v>0</v>
       </c>
@@ -10037,11 +10037,11 @@
       <c r="R45" s="32"/>
     </row>
     <row r="46" spans="1:18" ht="12">
-      <c r="A46" s="90" t="s">
+      <c r="A46" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="B46" s="90"/>
-      <c r="C46" s="90"/>
+      <c r="B46" s="87"/>
+      <c r="C46" s="87"/>
       <c r="D46" s="40">
         <f>SUM(D47:D62)</f>
         <v>143203.00999999998</v>
@@ -10101,11 +10101,11 @@
       <c r="R46" s="32"/>
     </row>
     <row r="47" spans="1:18" ht="12">
-      <c r="A47" s="86" t="s">
+      <c r="A47" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="85"/>
       <c r="D47" s="35">
         <v>48667</v>
       </c>
@@ -10153,11 +10153,11 @@
       <c r="R47" s="32"/>
     </row>
     <row r="48" spans="1:18" ht="12">
-      <c r="A48" s="87" t="s">
+      <c r="A48" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="87"/>
-      <c r="C48" s="87"/>
+      <c r="B48" s="86"/>
+      <c r="C48" s="86"/>
       <c r="D48" s="38">
         <v>21530.09</v>
       </c>
@@ -10205,11 +10205,11 @@
       <c r="R48" s="32"/>
     </row>
     <row r="49" spans="1:18" ht="12">
-      <c r="A49" s="86" t="s">
+      <c r="A49" s="85" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="86"/>
-      <c r="C49" s="86"/>
+      <c r="B49" s="85"/>
+      <c r="C49" s="85"/>
       <c r="D49" s="35">
         <v>71.900000000000006</v>
       </c>
@@ -10257,11 +10257,11 @@
       <c r="R49" s="32"/>
     </row>
     <row r="50" spans="1:18" ht="12">
-      <c r="A50" s="87" t="s">
+      <c r="A50" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="87"/>
-      <c r="C50" s="87"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="86"/>
       <c r="D50" s="38">
         <v>246.43</v>
       </c>
@@ -10309,11 +10309,11 @@
       <c r="R50" s="32"/>
     </row>
     <row r="51" spans="1:18" ht="12">
-      <c r="A51" s="86" t="s">
+      <c r="A51" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="86"/>
-      <c r="C51" s="86"/>
+      <c r="B51" s="85"/>
+      <c r="C51" s="85"/>
       <c r="D51" s="35">
         <v>0</v>
       </c>
@@ -10361,11 +10361,11 @@
       <c r="R51" s="32"/>
     </row>
     <row r="52" spans="1:18" ht="12">
-      <c r="A52" s="87" t="s">
+      <c r="A52" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="87"/>
-      <c r="C52" s="87"/>
+      <c r="B52" s="86"/>
+      <c r="C52" s="86"/>
       <c r="D52" s="38">
         <v>2808.9</v>
       </c>
@@ -10413,11 +10413,11 @@
       <c r="R52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="12">
-      <c r="A53" s="86" t="s">
+      <c r="A53" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="86"/>
-      <c r="C53" s="86"/>
+      <c r="B53" s="85"/>
+      <c r="C53" s="85"/>
       <c r="D53" s="35">
         <v>295.92</v>
       </c>
@@ -10465,11 +10465,11 @@
       <c r="R53" s="32"/>
     </row>
     <row r="54" spans="1:18" ht="12">
-      <c r="A54" s="87" t="s">
+      <c r="A54" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="87"/>
-      <c r="C54" s="87"/>
+      <c r="B54" s="86"/>
+      <c r="C54" s="86"/>
       <c r="D54" s="38">
         <v>300</v>
       </c>
@@ -10517,11 +10517,11 @@
       <c r="R54" s="32"/>
     </row>
     <row r="55" spans="1:18" ht="12">
-      <c r="A55" s="86" t="s">
+      <c r="A55" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="86"/>
-      <c r="C55" s="86"/>
+      <c r="B55" s="85"/>
+      <c r="C55" s="85"/>
       <c r="D55" s="35">
         <v>0</v>
       </c>
@@ -10569,11 +10569,11 @@
       <c r="R55" s="32"/>
     </row>
     <row r="56" spans="1:18" ht="12">
-      <c r="A56" s="87" t="s">
+      <c r="A56" s="86" t="s">
         <v>146</v>
       </c>
-      <c r="B56" s="87"/>
-      <c r="C56" s="87"/>
+      <c r="B56" s="86"/>
+      <c r="C56" s="86"/>
       <c r="D56" s="38">
         <v>166</v>
       </c>
@@ -10621,11 +10621,11 @@
       <c r="R56" s="32"/>
     </row>
     <row r="57" spans="1:18" ht="12">
-      <c r="A57" s="86" t="s">
+      <c r="A57" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="86"/>
-      <c r="C57" s="86"/>
+      <c r="B57" s="85"/>
+      <c r="C57" s="85"/>
       <c r="D57" s="35">
         <v>24079.08</v>
       </c>
@@ -10673,11 +10673,11 @@
       <c r="R57" s="32"/>
     </row>
     <row r="58" spans="1:18" ht="12">
-      <c r="A58" s="87" t="s">
+      <c r="A58" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="87"/>
-      <c r="C58" s="87"/>
+      <c r="B58" s="86"/>
+      <c r="C58" s="86"/>
       <c r="D58" s="38">
         <v>5500.01</v>
       </c>
@@ -10725,11 +10725,11 @@
       <c r="R58" s="32"/>
     </row>
     <row r="59" spans="1:18" ht="12">
-      <c r="A59" s="86" t="s">
+      <c r="A59" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="B59" s="86"/>
-      <c r="C59" s="86"/>
+      <c r="B59" s="85"/>
+      <c r="C59" s="85"/>
       <c r="D59" s="35">
         <v>0</v>
       </c>
@@ -10777,11 +10777,11 @@
       <c r="R59" s="32"/>
     </row>
     <row r="60" spans="1:18" ht="12">
-      <c r="A60" s="87" t="s">
+      <c r="A60" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="B60" s="87"/>
-      <c r="C60" s="87"/>
+      <c r="B60" s="86"/>
+      <c r="C60" s="86"/>
       <c r="D60" s="38">
         <v>38781.68</v>
       </c>
@@ -10829,11 +10829,11 @@
       <c r="R60" s="32"/>
     </row>
     <row r="61" spans="1:18" ht="12">
-      <c r="A61" s="86" t="s">
+      <c r="A61" s="85" t="s">
         <v>50</v>
       </c>
-      <c r="B61" s="86"/>
-      <c r="C61" s="86"/>
+      <c r="B61" s="85"/>
+      <c r="C61" s="85"/>
       <c r="D61" s="35">
         <v>0</v>
       </c>
@@ -10881,11 +10881,11 @@
       <c r="R61" s="32"/>
     </row>
     <row r="62" spans="1:18" ht="12">
-      <c r="A62" s="87" t="s">
+      <c r="A62" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="B62" s="87"/>
-      <c r="C62" s="87"/>
+      <c r="B62" s="86"/>
+      <c r="C62" s="86"/>
       <c r="D62" s="38">
         <v>756</v>
       </c>
@@ -10997,11 +10997,11 @@
       <c r="R63" s="32"/>
     </row>
     <row r="64" spans="1:18" ht="12">
-      <c r="A64" s="90" t="s">
+      <c r="A64" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="90"/>
-      <c r="C64" s="90"/>
+      <c r="B64" s="87"/>
+      <c r="C64" s="87"/>
       <c r="D64" s="40">
         <f>SUM(D65:D74)</f>
         <v>11409.97</v>
@@ -11061,11 +11061,11 @@
       <c r="R64" s="32"/>
     </row>
     <row r="65" spans="1:18" ht="12">
-      <c r="A65" s="86" t="s">
+      <c r="A65" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="B65" s="86"/>
-      <c r="C65" s="86"/>
+      <c r="B65" s="85"/>
+      <c r="C65" s="85"/>
       <c r="D65" s="35">
         <v>1483.91</v>
       </c>
@@ -11113,11 +11113,11 @@
       <c r="R65" s="32"/>
     </row>
     <row r="66" spans="1:18" ht="12">
-      <c r="A66" s="87" t="s">
+      <c r="A66" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="87"/>
-      <c r="C66" s="87"/>
+      <c r="B66" s="86"/>
+      <c r="C66" s="86"/>
       <c r="D66" s="38">
         <v>143.94999999999999</v>
       </c>
@@ -11165,11 +11165,11 @@
       <c r="R66" s="32"/>
     </row>
     <row r="67" spans="1:18" ht="12">
-      <c r="A67" s="86" t="s">
+      <c r="A67" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="B67" s="86"/>
-      <c r="C67" s="86"/>
+      <c r="B67" s="85"/>
+      <c r="C67" s="85"/>
       <c r="D67" s="35">
         <v>0</v>
       </c>
@@ -11217,11 +11217,11 @@
       <c r="R67" s="32"/>
     </row>
     <row r="68" spans="1:18" s="51" customFormat="1" ht="12">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="B68" s="88"/>
-      <c r="C68" s="88"/>
+      <c r="B68" s="91"/>
+      <c r="C68" s="91"/>
       <c r="D68" s="48">
         <v>3056.35</v>
       </c>
@@ -11269,11 +11269,11 @@
       <c r="R68" s="50"/>
     </row>
     <row r="69" spans="1:18" s="51" customFormat="1" ht="12">
-      <c r="A69" s="88" t="s">
+      <c r="A69" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="B69" s="88"/>
-      <c r="C69" s="88"/>
+      <c r="B69" s="91"/>
+      <c r="C69" s="91"/>
       <c r="D69" s="48">
         <v>584.5</v>
       </c>
@@ -11321,11 +11321,11 @@
       <c r="R69" s="50"/>
     </row>
     <row r="70" spans="1:18" ht="12">
-      <c r="A70" s="87" t="s">
+      <c r="A70" s="86" t="s">
         <v>58</v>
       </c>
-      <c r="B70" s="87"/>
-      <c r="C70" s="87"/>
+      <c r="B70" s="86"/>
+      <c r="C70" s="86"/>
       <c r="D70" s="38">
         <v>530.64</v>
       </c>
@@ -11373,11 +11373,11 @@
       <c r="R70" s="32"/>
     </row>
     <row r="71" spans="1:18" ht="12">
-      <c r="A71" s="86" t="s">
+      <c r="A71" s="85" t="s">
         <v>59</v>
       </c>
-      <c r="B71" s="86"/>
-      <c r="C71" s="86"/>
+      <c r="B71" s="85"/>
+      <c r="C71" s="85"/>
       <c r="D71" s="35">
         <v>0</v>
       </c>
@@ -11425,11 +11425,11 @@
       <c r="R71" s="32"/>
     </row>
     <row r="72" spans="1:18" ht="12">
-      <c r="A72" s="87" t="s">
+      <c r="A72" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="B72" s="87"/>
-      <c r="C72" s="87"/>
+      <c r="B72" s="86"/>
+      <c r="C72" s="86"/>
       <c r="D72" s="38">
         <v>5263.97</v>
       </c>
@@ -11477,11 +11477,11 @@
       <c r="R72" s="32"/>
     </row>
     <row r="73" spans="1:18" ht="12">
-      <c r="A73" s="86" t="s">
+      <c r="A73" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="B73" s="86"/>
-      <c r="C73" s="86"/>
+      <c r="B73" s="85"/>
+      <c r="C73" s="85"/>
       <c r="D73" s="35">
         <v>334.65</v>
       </c>
@@ -11529,11 +11529,11 @@
       <c r="R73" s="32"/>
     </row>
     <row r="74" spans="1:18" ht="12">
-      <c r="A74" s="87" t="s">
+      <c r="A74" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="B74" s="87"/>
-      <c r="C74" s="87"/>
+      <c r="B74" s="86"/>
+      <c r="C74" s="86"/>
       <c r="D74" s="38">
         <v>12</v>
       </c>
@@ -11645,11 +11645,11 @@
       <c r="R75" s="32"/>
     </row>
     <row r="76" spans="1:18" ht="12">
-      <c r="A76" s="87" t="s">
+      <c r="A76" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="B76" s="87"/>
-      <c r="C76" s="87"/>
+      <c r="B76" s="86"/>
+      <c r="C76" s="86"/>
       <c r="D76" s="38">
         <v>1149.96</v>
       </c>
@@ -11697,11 +11697,11 @@
       <c r="R76" s="32"/>
     </row>
     <row r="77" spans="1:18" ht="12">
-      <c r="A77" s="86" t="s">
+      <c r="A77" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="B77" s="86"/>
-      <c r="C77" s="86"/>
+      <c r="B77" s="85"/>
+      <c r="C77" s="85"/>
       <c r="D77" s="35">
         <v>0</v>
       </c>
@@ -11749,11 +11749,11 @@
       <c r="R77" s="32"/>
     </row>
     <row r="78" spans="1:18" ht="12">
-      <c r="A78" s="87" t="s">
+      <c r="A78" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="87"/>
-      <c r="C78" s="87"/>
+      <c r="B78" s="86"/>
+      <c r="C78" s="86"/>
       <c r="D78" s="38">
         <v>850</v>
       </c>
@@ -11801,11 +11801,11 @@
       <c r="R78" s="32"/>
     </row>
     <row r="79" spans="1:18" ht="12">
-      <c r="A79" s="86" t="s">
+      <c r="A79" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="B79" s="86"/>
-      <c r="C79" s="86"/>
+      <c r="B79" s="85"/>
+      <c r="C79" s="85"/>
       <c r="D79" s="35">
         <v>0</v>
       </c>
@@ -11853,11 +11853,11 @@
       <c r="R79" s="32"/>
     </row>
     <row r="80" spans="1:18" ht="12">
-      <c r="A80" s="87" t="s">
+      <c r="A80" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="87"/>
-      <c r="C80" s="87"/>
+      <c r="B80" s="86"/>
+      <c r="C80" s="86"/>
       <c r="D80" s="38">
         <v>1990.92</v>
       </c>
@@ -11905,11 +11905,11 @@
       <c r="R80" s="32"/>
     </row>
     <row r="81" spans="1:18" ht="12">
-      <c r="A81" s="86" t="s">
+      <c r="A81" s="85" t="s">
         <v>75</v>
       </c>
-      <c r="B81" s="86"/>
-      <c r="C81" s="86"/>
+      <c r="B81" s="85"/>
+      <c r="C81" s="85"/>
       <c r="D81" s="35">
         <v>0</v>
       </c>
@@ -11957,11 +11957,11 @@
       <c r="R81" s="32"/>
     </row>
     <row r="82" spans="1:18" ht="12">
-      <c r="A82" s="87" t="s">
+      <c r="A82" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="B82" s="87"/>
-      <c r="C82" s="87"/>
+      <c r="B82" s="86"/>
+      <c r="C82" s="86"/>
       <c r="D82" s="38">
         <v>7360.44</v>
       </c>
@@ -12009,11 +12009,11 @@
       <c r="R82" s="32"/>
     </row>
     <row r="83" spans="1:18" ht="12">
-      <c r="A83" s="86" t="s">
+      <c r="A83" s="85" t="s">
         <v>77</v>
       </c>
-      <c r="B83" s="86"/>
-      <c r="C83" s="86"/>
+      <c r="B83" s="85"/>
+      <c r="C83" s="85"/>
       <c r="D83" s="35">
         <v>1100</v>
       </c>
@@ -12061,11 +12061,11 @@
       <c r="R83" s="32"/>
     </row>
     <row r="84" spans="1:18" ht="12">
-      <c r="A84" s="87" t="s">
+      <c r="A84" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="B84" s="87"/>
-      <c r="C84" s="87"/>
+      <c r="B84" s="86"/>
+      <c r="C84" s="86"/>
       <c r="D84" s="38">
         <v>0</v>
       </c>
@@ -12113,11 +12113,11 @@
       <c r="R84" s="32"/>
     </row>
     <row r="85" spans="1:18" ht="12">
-      <c r="A85" s="86" t="s">
+      <c r="A85" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B85" s="86"/>
-      <c r="C85" s="86"/>
+      <c r="B85" s="85"/>
+      <c r="C85" s="85"/>
       <c r="D85" s="35">
         <v>55.8</v>
       </c>
@@ -12165,11 +12165,11 @@
       <c r="R85" s="32"/>
     </row>
     <row r="86" spans="1:18" ht="12">
-      <c r="A86" s="87" t="s">
+      <c r="A86" s="86" t="s">
         <v>80</v>
       </c>
-      <c r="B86" s="87"/>
-      <c r="C86" s="87"/>
+      <c r="B86" s="86"/>
+      <c r="C86" s="86"/>
       <c r="D86" s="38">
         <v>0</v>
       </c>
@@ -12217,11 +12217,11 @@
       <c r="R86" s="32"/>
     </row>
     <row r="87" spans="1:18" ht="12">
-      <c r="A87" s="86" t="s">
+      <c r="A87" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="B87" s="86"/>
-      <c r="C87" s="86"/>
+      <c r="B87" s="85"/>
+      <c r="C87" s="85"/>
       <c r="D87" s="35">
         <v>0</v>
       </c>
@@ -12269,11 +12269,11 @@
       <c r="R87" s="32"/>
     </row>
     <row r="88" spans="1:18" ht="12">
-      <c r="A88" s="90" t="s">
+      <c r="A88" s="87" t="s">
         <v>82</v>
       </c>
-      <c r="B88" s="90"/>
-      <c r="C88" s="90"/>
+      <c r="B88" s="87"/>
+      <c r="C88" s="87"/>
       <c r="D88" s="40">
         <f>SUM(D89:D91)</f>
         <v>15437.5</v>
@@ -12333,11 +12333,11 @@
       <c r="R88" s="32"/>
     </row>
     <row r="89" spans="1:18" ht="12">
-      <c r="A89" s="86" t="s">
+      <c r="A89" s="85" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="86"/>
-      <c r="C89" s="86"/>
+      <c r="B89" s="85"/>
+      <c r="C89" s="85"/>
       <c r="D89" s="35">
         <v>5780.5</v>
       </c>
@@ -12385,11 +12385,11 @@
       <c r="R89" s="32"/>
     </row>
     <row r="90" spans="1:18" ht="12">
-      <c r="A90" s="87" t="s">
+      <c r="A90" s="86" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="87"/>
-      <c r="C90" s="87"/>
+      <c r="B90" s="86"/>
+      <c r="C90" s="86"/>
       <c r="D90" s="38">
         <v>7041</v>
       </c>
@@ -12437,11 +12437,11 @@
       <c r="R90" s="32"/>
     </row>
     <row r="91" spans="1:18" ht="12">
-      <c r="A91" s="86" t="s">
+      <c r="A91" s="85" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="86"/>
-      <c r="C91" s="86"/>
+      <c r="B91" s="85"/>
+      <c r="C91" s="85"/>
       <c r="D91" s="35">
         <v>2616</v>
       </c>
@@ -12489,11 +12489,11 @@
       <c r="R91" s="32"/>
     </row>
     <row r="92" spans="1:18" ht="12">
-      <c r="A92" s="90" t="s">
+      <c r="A92" s="87" t="s">
         <v>86</v>
       </c>
-      <c r="B92" s="90"/>
-      <c r="C92" s="90"/>
+      <c r="B92" s="87"/>
+      <c r="C92" s="87"/>
       <c r="D92" s="40">
         <f>SUM(D93:D97)</f>
         <v>7579.1</v>
@@ -12553,11 +12553,11 @@
       <c r="R92" s="32"/>
     </row>
     <row r="93" spans="1:18" ht="12">
-      <c r="A93" s="86" t="s">
+      <c r="A93" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="B93" s="86"/>
-      <c r="C93" s="86"/>
+      <c r="B93" s="85"/>
+      <c r="C93" s="85"/>
       <c r="D93" s="35">
         <v>870</v>
       </c>
@@ -12605,11 +12605,11 @@
       <c r="R93" s="32"/>
     </row>
     <row r="94" spans="1:18" ht="12">
-      <c r="A94" s="87" t="s">
+      <c r="A94" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="B94" s="87"/>
-      <c r="C94" s="87"/>
+      <c r="B94" s="86"/>
+      <c r="C94" s="86"/>
       <c r="D94" s="38">
         <v>720</v>
       </c>
@@ -12657,11 +12657,11 @@
       <c r="R94" s="32"/>
     </row>
     <row r="95" spans="1:18" ht="12">
-      <c r="A95" s="86" t="s">
+      <c r="A95" s="85" t="s">
         <v>89</v>
       </c>
-      <c r="B95" s="86"/>
-      <c r="C95" s="86"/>
+      <c r="B95" s="85"/>
+      <c r="C95" s="85"/>
       <c r="D95" s="35">
         <v>2300</v>
       </c>
@@ -12709,11 +12709,11 @@
       <c r="R95" s="32"/>
     </row>
     <row r="96" spans="1:18" ht="12">
-      <c r="A96" s="87" t="s">
+      <c r="A96" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="B96" s="87"/>
-      <c r="C96" s="87"/>
+      <c r="B96" s="86"/>
+      <c r="C96" s="86"/>
       <c r="D96" s="38">
         <v>1409.1</v>
       </c>
@@ -12761,11 +12761,11 @@
       <c r="R96" s="32"/>
     </row>
     <row r="97" spans="1:18" ht="12">
-      <c r="A97" s="86" t="s">
+      <c r="A97" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="B97" s="86"/>
-      <c r="C97" s="86"/>
+      <c r="B97" s="85"/>
+      <c r="C97" s="85"/>
       <c r="D97" s="35">
         <v>2280</v>
       </c>
@@ -12813,11 +12813,11 @@
       <c r="R97" s="32"/>
     </row>
     <row r="98" spans="1:18" ht="12">
-      <c r="A98" s="90" t="s">
+      <c r="A98" s="87" t="s">
         <v>92</v>
       </c>
-      <c r="B98" s="90"/>
-      <c r="C98" s="90"/>
+      <c r="B98" s="87"/>
+      <c r="C98" s="87"/>
       <c r="D98" s="40">
         <f>SUM(D99:D107)</f>
         <v>70873.11</v>
@@ -12877,11 +12877,11 @@
       <c r="R98" s="32"/>
     </row>
     <row r="99" spans="1:18" ht="12">
-      <c r="A99" s="86" t="s">
+      <c r="A99" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="B99" s="86"/>
-      <c r="C99" s="86"/>
+      <c r="B99" s="85"/>
+      <c r="C99" s="85"/>
       <c r="D99" s="35">
         <v>3940</v>
       </c>
@@ -12929,11 +12929,11 @@
       <c r="R99" s="32"/>
     </row>
     <row r="100" spans="1:18" ht="12">
-      <c r="A100" s="87" t="s">
+      <c r="A100" s="86" t="s">
         <v>94</v>
       </c>
-      <c r="B100" s="87"/>
-      <c r="C100" s="87"/>
+      <c r="B100" s="86"/>
+      <c r="C100" s="86"/>
       <c r="D100" s="38">
         <v>2824</v>
       </c>
@@ -12981,11 +12981,11 @@
       <c r="R100" s="32"/>
     </row>
     <row r="101" spans="1:18" ht="12">
-      <c r="A101" s="86" t="s">
+      <c r="A101" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="B101" s="86"/>
-      <c r="C101" s="86"/>
+      <c r="B101" s="85"/>
+      <c r="C101" s="85"/>
       <c r="D101" s="35">
         <v>4086.38</v>
       </c>
@@ -13033,11 +13033,11 @@
       <c r="R101" s="32"/>
     </row>
     <row r="102" spans="1:18" ht="12">
-      <c r="A102" s="87" t="s">
+      <c r="A102" s="86" t="s">
         <v>96</v>
       </c>
-      <c r="B102" s="87"/>
-      <c r="C102" s="87"/>
+      <c r="B102" s="86"/>
+      <c r="C102" s="86"/>
       <c r="D102" s="38">
         <v>56426.23</v>
       </c>
@@ -13085,11 +13085,11 @@
       <c r="R102" s="32"/>
     </row>
     <row r="103" spans="1:18" ht="12">
-      <c r="A103" s="86" t="s">
+      <c r="A103" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="B103" s="86"/>
-      <c r="C103" s="86"/>
+      <c r="B103" s="85"/>
+      <c r="C103" s="85"/>
       <c r="D103" s="35">
         <v>0</v>
       </c>
@@ -13137,11 +13137,11 @@
       <c r="R103" s="32"/>
     </row>
     <row r="104" spans="1:18" ht="12">
-      <c r="A104" s="87" t="s">
+      <c r="A104" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="B104" s="87"/>
-      <c r="C104" s="87"/>
+      <c r="B104" s="86"/>
+      <c r="C104" s="86"/>
       <c r="D104" s="38">
         <v>2400</v>
       </c>
@@ -13189,11 +13189,11 @@
       <c r="R104" s="32"/>
     </row>
     <row r="105" spans="1:18" ht="12">
-      <c r="A105" s="86" t="s">
+      <c r="A105" s="85" t="s">
         <v>149</v>
       </c>
-      <c r="B105" s="86"/>
-      <c r="C105" s="86"/>
+      <c r="B105" s="85"/>
+      <c r="C105" s="85"/>
       <c r="D105" s="35">
         <v>0</v>
       </c>
@@ -13241,11 +13241,11 @@
       <c r="R105" s="32"/>
     </row>
     <row r="106" spans="1:18" ht="12">
-      <c r="A106" s="87" t="s">
+      <c r="A106" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="B106" s="87"/>
-      <c r="C106" s="87"/>
+      <c r="B106" s="86"/>
+      <c r="C106" s="86"/>
       <c r="D106" s="38">
         <v>1196.5</v>
       </c>
@@ -13293,11 +13293,11 @@
       <c r="R106" s="32"/>
     </row>
     <row r="107" spans="1:18" ht="12">
-      <c r="A107" s="86" t="s">
+      <c r="A107" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="B107" s="86"/>
-      <c r="C107" s="86"/>
+      <c r="B107" s="85"/>
+      <c r="C107" s="85"/>
       <c r="D107" s="35">
         <v>0</v>
       </c>
@@ -13345,11 +13345,11 @@
       <c r="R107" s="32"/>
     </row>
     <row r="108" spans="1:18" ht="12">
-      <c r="A108" s="90" t="s">
+      <c r="A108" s="87" t="s">
         <v>100</v>
       </c>
-      <c r="B108" s="90"/>
-      <c r="C108" s="90"/>
+      <c r="B108" s="87"/>
+      <c r="C108" s="87"/>
       <c r="D108" s="40">
         <f>SUM(D109:D120)</f>
         <v>15220.319999999998</v>
@@ -13409,11 +13409,11 @@
       <c r="R108" s="32"/>
     </row>
     <row r="109" spans="1:18" ht="12">
-      <c r="A109" s="86" t="s">
+      <c r="A109" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="B109" s="86"/>
-      <c r="C109" s="86"/>
+      <c r="B109" s="85"/>
+      <c r="C109" s="85"/>
       <c r="D109" s="35">
         <v>10667.14</v>
       </c>
@@ -13461,11 +13461,11 @@
       <c r="R109" s="32"/>
     </row>
     <row r="110" spans="1:18" ht="12">
-      <c r="A110" s="87" t="s">
+      <c r="A110" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="B110" s="87"/>
-      <c r="C110" s="87"/>
+      <c r="B110" s="86"/>
+      <c r="C110" s="86"/>
       <c r="D110" s="38">
         <v>1783.48</v>
       </c>
@@ -13513,11 +13513,11 @@
       <c r="R110" s="32"/>
     </row>
     <row r="111" spans="1:18" ht="12">
-      <c r="A111" s="86" t="s">
+      <c r="A111" s="85" t="s">
         <v>103</v>
       </c>
-      <c r="B111" s="86"/>
-      <c r="C111" s="86"/>
+      <c r="B111" s="85"/>
+      <c r="C111" s="85"/>
       <c r="D111" s="35">
         <v>0</v>
       </c>
@@ -13565,11 +13565,11 @@
       <c r="R111" s="32"/>
     </row>
     <row r="112" spans="1:18" ht="12">
-      <c r="A112" s="87" t="s">
+      <c r="A112" s="86" t="s">
         <v>104</v>
       </c>
-      <c r="B112" s="87"/>
-      <c r="C112" s="87"/>
+      <c r="B112" s="86"/>
+      <c r="C112" s="86"/>
       <c r="D112" s="38">
         <v>162.30000000000001</v>
       </c>
@@ -13617,11 +13617,11 @@
       <c r="R112" s="32"/>
     </row>
     <row r="113" spans="1:18" ht="12">
-      <c r="A113" s="86" t="s">
+      <c r="A113" s="85" t="s">
         <v>105</v>
       </c>
-      <c r="B113" s="86"/>
-      <c r="C113" s="86"/>
+      <c r="B113" s="85"/>
+      <c r="C113" s="85"/>
       <c r="D113" s="35">
         <v>0</v>
       </c>
@@ -13669,11 +13669,11 @@
       <c r="R113" s="32"/>
     </row>
     <row r="114" spans="1:18" ht="12">
-      <c r="A114" s="87" t="s">
+      <c r="A114" s="86" t="s">
         <v>106</v>
       </c>
-      <c r="B114" s="87"/>
-      <c r="C114" s="87"/>
+      <c r="B114" s="86"/>
+      <c r="C114" s="86"/>
       <c r="D114" s="38">
         <v>98.42</v>
       </c>
@@ -13721,11 +13721,11 @@
       <c r="R114" s="32"/>
     </row>
     <row r="115" spans="1:18" ht="12">
-      <c r="A115" s="86" t="s">
+      <c r="A115" s="85" t="s">
         <v>107</v>
       </c>
-      <c r="B115" s="86"/>
-      <c r="C115" s="86"/>
+      <c r="B115" s="85"/>
+      <c r="C115" s="85"/>
       <c r="D115" s="35">
         <v>199.99</v>
       </c>
@@ -13773,11 +13773,11 @@
       <c r="R115" s="32"/>
     </row>
     <row r="116" spans="1:18" ht="12">
-      <c r="A116" s="87" t="s">
+      <c r="A116" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="87"/>
-      <c r="C116" s="87"/>
+      <c r="B116" s="86"/>
+      <c r="C116" s="86"/>
       <c r="D116" s="38">
         <v>0</v>
       </c>
@@ -13825,11 +13825,11 @@
       <c r="R116" s="32"/>
     </row>
     <row r="117" spans="1:18" ht="12">
-      <c r="A117" s="86" t="s">
+      <c r="A117" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="B117" s="86"/>
-      <c r="C117" s="86"/>
+      <c r="B117" s="85"/>
+      <c r="C117" s="85"/>
       <c r="D117" s="35">
         <v>96.89</v>
       </c>
@@ -13877,11 +13877,11 @@
       <c r="R117" s="32"/>
     </row>
     <row r="118" spans="1:18" ht="12">
-      <c r="A118" s="87" t="s">
+      <c r="A118" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="B118" s="87"/>
-      <c r="C118" s="87"/>
+      <c r="B118" s="86"/>
+      <c r="C118" s="86"/>
       <c r="D118" s="38">
         <v>34.9</v>
       </c>
@@ -13929,11 +13929,11 @@
       <c r="R118" s="32"/>
     </row>
     <row r="119" spans="1:18" ht="12">
-      <c r="A119" s="86" t="s">
+      <c r="A119" s="85" t="s">
         <v>111</v>
       </c>
-      <c r="B119" s="86"/>
-      <c r="C119" s="86"/>
+      <c r="B119" s="85"/>
+      <c r="C119" s="85"/>
       <c r="D119" s="35">
         <v>730</v>
       </c>
@@ -13981,11 +13981,11 @@
       <c r="R119" s="32"/>
     </row>
     <row r="120" spans="1:18" ht="12">
-      <c r="A120" s="87" t="s">
+      <c r="A120" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="B120" s="87"/>
-      <c r="C120" s="87"/>
+      <c r="B120" s="86"/>
+      <c r="C120" s="86"/>
       <c r="D120" s="38">
         <v>1447.2</v>
       </c>
@@ -14097,11 +14097,11 @@
       <c r="R121" s="32"/>
     </row>
     <row r="122" spans="1:18" ht="12">
-      <c r="A122" s="87" t="s">
+      <c r="A122" s="86" t="s">
         <v>152</v>
       </c>
-      <c r="B122" s="87"/>
-      <c r="C122" s="87"/>
+      <c r="B122" s="86"/>
+      <c r="C122" s="86"/>
       <c r="D122" s="38">
         <v>142.21</v>
       </c>
@@ -14149,11 +14149,11 @@
       <c r="R122" s="32"/>
     </row>
     <row r="123" spans="1:18" ht="12">
-      <c r="A123" s="86" t="s">
+      <c r="A123" s="85" t="s">
         <v>153</v>
       </c>
-      <c r="B123" s="86"/>
-      <c r="C123" s="86"/>
+      <c r="B123" s="85"/>
+      <c r="C123" s="85"/>
       <c r="D123" s="35">
         <v>0</v>
       </c>
@@ -14201,11 +14201,11 @@
       <c r="R123" s="32"/>
     </row>
     <row r="124" spans="1:18" ht="12">
-      <c r="A124" s="87" t="s">
+      <c r="A124" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="B124" s="87"/>
-      <c r="C124" s="87"/>
+      <c r="B124" s="86"/>
+      <c r="C124" s="86"/>
       <c r="D124" s="38">
         <v>0</v>
       </c>
@@ -14253,11 +14253,11 @@
       <c r="R124" s="32"/>
     </row>
     <row r="125" spans="1:18" ht="12">
-      <c r="A125" s="86" t="s">
+      <c r="A125" s="85" t="s">
         <v>155</v>
       </c>
-      <c r="B125" s="86"/>
-      <c r="C125" s="86"/>
+      <c r="B125" s="85"/>
+      <c r="C125" s="85"/>
       <c r="D125" s="35">
         <v>0</v>
       </c>
@@ -14305,11 +14305,11 @@
       <c r="R125" s="32"/>
     </row>
     <row r="126" spans="1:18" ht="12">
-      <c r="A126" s="87" t="s">
+      <c r="A126" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="B126" s="87"/>
-      <c r="C126" s="87"/>
+      <c r="B126" s="86"/>
+      <c r="C126" s="86"/>
       <c r="D126" s="38">
         <v>0</v>
       </c>
@@ -14357,11 +14357,11 @@
       <c r="R126" s="32"/>
     </row>
     <row r="127" spans="1:18" ht="12">
-      <c r="A127" s="86" t="s">
+      <c r="A127" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="B127" s="86"/>
-      <c r="C127" s="86"/>
+      <c r="B127" s="85"/>
+      <c r="C127" s="85"/>
       <c r="D127" s="35">
         <v>0</v>
       </c>
@@ -14409,11 +14409,11 @@
       <c r="R127" s="32"/>
     </row>
     <row r="128" spans="1:18" ht="12">
-      <c r="A128" s="87" t="s">
+      <c r="A128" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="B128" s="87"/>
-      <c r="C128" s="87"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="86"/>
       <c r="D128" s="38">
         <v>0</v>
       </c>
@@ -14461,11 +14461,11 @@
       <c r="R128" s="32"/>
     </row>
     <row r="129" spans="1:20" ht="12">
-      <c r="A129" s="86" t="s">
+      <c r="A129" s="85" t="s">
         <v>159</v>
       </c>
-      <c r="B129" s="86"/>
-      <c r="C129" s="86"/>
+      <c r="B129" s="85"/>
+      <c r="C129" s="85"/>
       <c r="D129" s="35">
         <v>6364.55</v>
       </c>
@@ -14513,11 +14513,11 @@
       <c r="R129" s="32"/>
     </row>
     <row r="130" spans="1:20" s="51" customFormat="1" ht="12">
-      <c r="A130" s="88" t="s">
+      <c r="A130" s="91" t="s">
         <v>160</v>
       </c>
-      <c r="B130" s="88"/>
-      <c r="C130" s="88"/>
+      <c r="B130" s="91"/>
+      <c r="C130" s="91"/>
       <c r="D130" s="48">
         <v>0</v>
       </c>
@@ -14565,11 +14565,11 @@
       <c r="R130" s="50"/>
     </row>
     <row r="131" spans="1:20" ht="12">
-      <c r="A131" s="86" t="s">
+      <c r="A131" s="85" t="s">
         <v>161</v>
       </c>
-      <c r="B131" s="86"/>
-      <c r="C131" s="86"/>
+      <c r="B131" s="85"/>
+      <c r="C131" s="85"/>
       <c r="D131" s="35">
         <v>0</v>
       </c>
@@ -14617,11 +14617,11 @@
       <c r="R131" s="32"/>
     </row>
     <row r="132" spans="1:20" ht="12">
-      <c r="A132" s="87" t="s">
+      <c r="A132" s="86" t="s">
         <v>162</v>
       </c>
-      <c r="B132" s="87"/>
-      <c r="C132" s="87"/>
+      <c r="B132" s="86"/>
+      <c r="C132" s="86"/>
       <c r="D132" s="38">
         <v>17153.759999999998</v>
       </c>
@@ -14669,11 +14669,11 @@
       <c r="R132" s="32"/>
     </row>
     <row r="133" spans="1:20" ht="12">
-      <c r="A133" s="88" t="s">
+      <c r="A133" s="91" t="s">
         <v>163</v>
       </c>
-      <c r="B133" s="88"/>
-      <c r="C133" s="88"/>
+      <c r="B133" s="91"/>
+      <c r="C133" s="91"/>
       <c r="D133" s="35">
         <v>0</v>
       </c>
@@ -14721,11 +14721,11 @@
       <c r="R133" s="32"/>
     </row>
     <row r="134" spans="1:20" ht="12">
-      <c r="A134" s="87" t="s">
+      <c r="A134" s="86" t="s">
         <v>164</v>
       </c>
-      <c r="B134" s="87"/>
-      <c r="C134" s="87"/>
+      <c r="B134" s="86"/>
+      <c r="C134" s="86"/>
       <c r="D134" s="38">
         <v>506.55</v>
       </c>
@@ -14777,11 +14777,11 @@
       </c>
     </row>
     <row r="135" spans="1:20" ht="12">
-      <c r="A135" s="86" t="s">
+      <c r="A135" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="B135" s="86"/>
-      <c r="C135" s="86"/>
+      <c r="B135" s="85"/>
+      <c r="C135" s="85"/>
       <c r="D135" s="35">
         <v>0</v>
       </c>
@@ -14829,11 +14829,11 @@
       <c r="R135" s="32"/>
     </row>
     <row r="136" spans="1:20" ht="12">
-      <c r="A136" s="87" t="s">
+      <c r="A136" s="86" t="s">
         <v>166</v>
       </c>
-      <c r="B136" s="87"/>
-      <c r="C136" s="87"/>
+      <c r="B136" s="86"/>
+      <c r="C136" s="86"/>
       <c r="D136" s="38">
         <v>0</v>
       </c>
@@ -14881,11 +14881,11 @@
       <c r="R136" s="32"/>
     </row>
     <row r="137" spans="1:20" ht="12">
-      <c r="A137" s="86" t="s">
+      <c r="A137" s="85" t="s">
         <v>167</v>
       </c>
-      <c r="B137" s="86"/>
-      <c r="C137" s="86"/>
+      <c r="B137" s="85"/>
+      <c r="C137" s="85"/>
       <c r="D137" s="35">
         <v>0</v>
       </c>
@@ -14933,11 +14933,11 @@
       <c r="R137" s="32"/>
     </row>
     <row r="138" spans="1:20" ht="12">
-      <c r="A138" s="87" t="s">
+      <c r="A138" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="B138" s="87"/>
-      <c r="C138" s="87"/>
+      <c r="B138" s="86"/>
+      <c r="C138" s="86"/>
       <c r="D138" s="38">
         <v>0</v>
       </c>
@@ -14985,11 +14985,11 @@
       <c r="R138" s="32"/>
     </row>
     <row r="139" spans="1:20" ht="12">
-      <c r="A139" s="86" t="s">
+      <c r="A139" s="85" t="s">
         <v>169</v>
       </c>
-      <c r="B139" s="86"/>
-      <c r="C139" s="86"/>
+      <c r="B139" s="85"/>
+      <c r="C139" s="85"/>
       <c r="D139" s="35">
         <v>0</v>
       </c>
@@ -15037,11 +15037,11 @@
       <c r="R139" s="32"/>
     </row>
     <row r="140" spans="1:20" ht="12">
-      <c r="A140" s="85" t="s">
+      <c r="A140" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="B140" s="85"/>
-      <c r="C140" s="85"/>
+      <c r="B140" s="90"/>
+      <c r="C140" s="90"/>
       <c r="D140" s="39">
         <f>D26</f>
         <v>308825.78999999998</v>
@@ -15162,6 +15162,132 @@
     <row r="181" ht="12"/>
   </sheetData>
   <mergeCells count="140">
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A3:C3"/>
@@ -15176,132 +15302,6 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A131:C131"/>
-    <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A127:C127"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A139:C139"/>
-    <mergeCell ref="A138:C138"/>
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A132:C132"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -15313,7 +15313,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="C1:V135"/>
+  <dimension ref="C1:V137"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="1"/>
@@ -15331,53 +15331,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C1" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
+      <c r="C1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
     </row>
     <row r="2" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C2" s="69" t="s">
+      <c r="C2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
     </row>
     <row r="3" spans="3:22" ht="16.5" customHeight="1">
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="71"/>
-      <c r="E3" s="72"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="83"/>
       <c r="F3" s="31" t="s">
         <v>3</v>
       </c>
@@ -15423,11 +15423,11 @@
       <c r="T3" s="32"/>
     </row>
     <row r="4" spans="3:22" ht="12">
-      <c r="C4" s="77" t="s">
+      <c r="C4" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
       <c r="F4" s="23" t="e">
         <f>F5+F22+F38+F78+F86+#REF!</f>
         <v>#REF!</v>
@@ -15489,11 +15489,11 @@
       </c>
     </row>
     <row r="5" spans="3:22" ht="12">
-      <c r="C5" s="78" t="s">
+      <c r="C5" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
       <c r="F5" s="8">
         <f>SUM(F6:F21)</f>
         <v>9137.3607499999998</v>
@@ -15552,11 +15552,11 @@
       </c>
     </row>
     <row r="6" spans="3:22" ht="12">
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
       <c r="F6" s="3">
         <v>34</v>
       </c>
@@ -15613,11 +15613,11 @@
       <c r="T6" s="5"/>
     </row>
     <row r="7" spans="3:22" ht="12">
-      <c r="C7" s="79" t="s">
+      <c r="C7" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
       <c r="F7" s="3">
         <f>'REALIZADO 2025'!D29*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15677,11 +15677,11 @@
       <c r="T7" s="5"/>
     </row>
     <row r="8" spans="3:22" ht="12">
-      <c r="C8" s="79" t="s">
+      <c r="C8" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="69"/>
       <c r="F8" s="3">
         <f>'REALIZADO 2025'!D30*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15741,11 +15741,11 @@
       <c r="T8" s="5"/>
     </row>
     <row r="9" spans="3:22" ht="12">
-      <c r="C9" s="79" t="s">
+      <c r="C9" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="79"/>
-      <c r="E9" s="79"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="69"/>
       <c r="F9" s="3">
         <f>'REALIZADO 2025'!D31*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15805,11 +15805,11 @@
       <c r="T9" s="5"/>
     </row>
     <row r="10" spans="3:22" ht="12">
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
       <c r="F10" s="3">
         <f>'REALIZADO 2025'!D34*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15869,11 +15869,11 @@
       <c r="T10" s="5"/>
     </row>
     <row r="11" spans="3:22" ht="12">
-      <c r="C11" s="79" t="s">
+      <c r="C11" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="79"/>
-      <c r="E11" s="79"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="69"/>
       <c r="F11" s="3">
         <f>'REALIZADO 2025'!D35*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>372.17674999999997</v>
@@ -15933,11 +15933,11 @@
       <c r="T11" s="5"/>
     </row>
     <row r="12" spans="3:22" ht="12">
-      <c r="C12" s="79" t="s">
+      <c r="C12" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="79"/>
-      <c r="E12" s="79"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
       <c r="F12" s="3">
         <f>'REALIZADO 2025'!D36*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>522.5</v>
@@ -15997,11 +15997,11 @@
       <c r="T12" s="5"/>
     </row>
     <row r="13" spans="3:22" ht="12">
-      <c r="C13" s="79" t="s">
+      <c r="C13" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="79"/>
-      <c r="E13" s="79"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
       <c r="F13" s="3">
         <f>'REALIZADO 2025'!D37*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16061,11 +16061,11 @@
       <c r="T13" s="5"/>
     </row>
     <row r="14" spans="3:22" ht="12">
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="79"/>
-      <c r="E14" s="79"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
       <c r="F14" s="3">
         <f t="shared" ref="F14:Q14" si="3">5043.17*$U$4</f>
         <v>5270.11265</v>
@@ -16125,11 +16125,11 @@
       <c r="T14" s="5"/>
     </row>
     <row r="15" spans="3:22" ht="12">
-      <c r="C15" s="79" t="s">
+      <c r="C15" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
       <c r="F15" s="3">
         <f t="shared" ref="F15:Q15" si="4">2570.4*$U$4</f>
         <v>2686.0679999999998</v>
@@ -16189,11 +16189,11 @@
       <c r="T15" s="5"/>
     </row>
     <row r="16" spans="3:22" ht="12">
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
       <c r="F16" s="3">
         <f>'REALIZADO 2025'!D40*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16253,11 +16253,11 @@
       <c r="T16" s="5"/>
     </row>
     <row r="17" spans="3:22" ht="12">
-      <c r="C17" s="79" t="s">
+      <c r="C17" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
       <c r="F17" s="3">
         <f>'REALIZADO 2025'!D41*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16317,11 +16317,11 @@
       <c r="T17" s="5"/>
     </row>
     <row r="18" spans="3:22" ht="12">
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="79"/>
-      <c r="E18" s="79"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="69"/>
       <c r="F18" s="3">
         <f>'REALIZADO 2025'!D42*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16381,11 +16381,11 @@
       <c r="T18" s="5"/>
     </row>
     <row r="19" spans="3:22" ht="12">
-      <c r="C19" s="79" t="s">
+      <c r="C19" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="69"/>
       <c r="F19" s="3">
         <f>'REALIZADO 2025'!D43*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16445,11 +16445,11 @@
       <c r="T19" s="5"/>
     </row>
     <row r="20" spans="3:22" ht="12">
-      <c r="C20" s="79" t="s">
+      <c r="C20" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="79"/>
-      <c r="E20" s="79"/>
+      <c r="D20" s="69"/>
+      <c r="E20" s="69"/>
       <c r="F20" s="3">
         <f>'REALIZADO 2025'!D44*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>252.50334999999998</v>
@@ -16509,11 +16509,11 @@
       <c r="T20" s="5"/>
     </row>
     <row r="21" spans="3:22" ht="12">
-      <c r="C21" s="79" t="s">
+      <c r="C21" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="79"/>
-      <c r="E21" s="79"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
       <c r="F21" s="3">
         <f>'REALIZADO 2025'!D45*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16573,11 +16573,11 @@
       <c r="T21" s="5"/>
     </row>
     <row r="22" spans="3:22" ht="12">
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
       <c r="F22" s="7">
         <f>SUM(F23:F37)</f>
         <v>154479.97080000001</v>
@@ -16645,11 +16645,11 @@
       </c>
     </row>
     <row r="23" spans="3:22" ht="12">
-      <c r="C23" s="79" t="s">
+      <c r="C23" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
       <c r="F23" s="3">
         <f>'REALIZADO 2025'!D47*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>52560.36</v>
@@ -16709,11 +16709,11 @@
       <c r="T23" s="5"/>
     </row>
     <row r="24" spans="3:22" ht="12">
-      <c r="C24" s="79" t="s">
+      <c r="C24" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="79"/>
-      <c r="E24" s="79"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
       <c r="F24" s="3">
         <f>'REALIZADO 2025'!D48*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>23252.497200000002</v>
@@ -16773,11 +16773,11 @@
       <c r="T24" s="5"/>
     </row>
     <row r="25" spans="3:22" ht="12">
-      <c r="C25" s="79" t="s">
+      <c r="C25" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="79"/>
-      <c r="E25" s="79"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
       <c r="F25" s="3">
         <f>'REALIZADO 2025'!D49*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>77.652000000000015</v>
@@ -16836,11 +16836,11 @@
       <c r="T25" s="5"/>
     </row>
     <row r="26" spans="3:22" ht="12">
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
       <c r="F26" s="3">
         <f>'REALIZADO 2025'!D50*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>266.14440000000002</v>
@@ -16900,11 +16900,11 @@
       <c r="T26" s="5"/>
     </row>
     <row r="27" spans="3:22" ht="12">
-      <c r="C27" s="79" t="s">
+      <c r="C27" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="79"/>
-      <c r="E27" s="79"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="69"/>
       <c r="F27" s="3">
         <f>'REALIZADO 2025'!D51*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -16964,11 +16964,11 @@
       <c r="T27" s="5"/>
     </row>
     <row r="28" spans="3:22" ht="12">
-      <c r="C28" s="79" t="s">
+      <c r="C28" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="79"/>
-      <c r="E28" s="79"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="69"/>
       <c r="F28" s="3">
         <f>'REALIZADO 2025'!D52*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>3033.6120000000001</v>
@@ -17028,11 +17028,11 @@
       <c r="T28" s="5"/>
     </row>
     <row r="29" spans="3:22" ht="12">
-      <c r="C29" s="79" t="s">
+      <c r="C29" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="79"/>
-      <c r="E29" s="79"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="69"/>
       <c r="F29" s="3">
         <f>'REALIZADO 2025'!D53*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>319.59360000000004</v>
@@ -17092,11 +17092,11 @@
       <c r="T29" s="5"/>
     </row>
     <row r="30" spans="3:22" ht="12">
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="79"/>
-      <c r="E30" s="79"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="69"/>
       <c r="F30" s="3">
         <f>'REALIZADO 2025'!D54*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>324</v>
@@ -17156,11 +17156,11 @@
       <c r="T30" s="5"/>
     </row>
     <row r="31" spans="3:22" ht="12">
-      <c r="C31" s="79" t="s">
+      <c r="C31" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
       <c r="F31" s="3">
         <f>'REALIZADO 2025'!D55*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -17220,11 +17220,11 @@
       <c r="T31" s="5"/>
     </row>
     <row r="32" spans="3:22" ht="12">
-      <c r="C32" s="79" t="s">
+      <c r="C32" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="79"/>
-      <c r="E32" s="79"/>
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
       <c r="F32" s="3">
         <f>'REALIZADO 2025'!D57*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>26005.406400000003</v>
@@ -17284,11 +17284,11 @@
       <c r="T32" s="5"/>
     </row>
     <row r="33" spans="3:22" ht="12">
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
+      <c r="D33" s="69"/>
+      <c r="E33" s="69"/>
       <c r="F33" s="3">
         <f>'REALIZADO 2025'!D58*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>5940.0108000000009</v>
@@ -17348,11 +17348,11 @@
       <c r="T33" s="5"/>
     </row>
     <row r="34" spans="3:22" ht="12">
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="79"/>
-      <c r="E34" s="79"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
       <c r="F34" s="3">
         <f>'REALIZADO 2025'!D59*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -17412,11 +17412,11 @@
       <c r="T34" s="5"/>
     </row>
     <row r="35" spans="3:22" ht="12">
-      <c r="C35" s="79" t="s">
+      <c r="C35" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
       <c r="F35" s="3">
         <f>'REALIZADO 2025'!D60*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>41884.214400000004</v>
@@ -17476,11 +17476,11 @@
       <c r="T35" s="5"/>
     </row>
     <row r="36" spans="3:22" ht="12">
-      <c r="C36" s="79" t="s">
+      <c r="C36" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
       <c r="F36" s="3">
         <f>'REALIZADO 2025'!D61*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -17539,11 +17539,11 @@
       <c r="T36" s="5"/>
     </row>
     <row r="37" spans="3:22" ht="12">
-      <c r="C37" s="79" t="s">
+      <c r="C37" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
       <c r="F37" s="3">
         <f>'REALIZADO 2025'!D62*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>816.48</v>
@@ -17603,11 +17603,11 @@
       <c r="T37" s="5"/>
     </row>
     <row r="38" spans="3:22" ht="12.75" customHeight="1">
-      <c r="C38" s="80" t="s">
+      <c r="C38" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="80"/>
-      <c r="E38" s="80"/>
+      <c r="D38" s="78"/>
+      <c r="E38" s="78"/>
       <c r="F38" s="7">
         <f t="shared" ref="F38:R38" si="7">F39+F55+F68+F72</f>
         <v>48895.278299999998</v>
@@ -17675,11 +17675,11 @@
       </c>
     </row>
     <row r="39" spans="3:22" ht="12" customHeight="1">
-      <c r="C39" s="78" t="s">
+      <c r="C39" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="78"/>
-      <c r="E39" s="78"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="74"/>
       <c r="F39" s="8">
         <f>SUM(F40:F48)</f>
         <v>11772.990900000001</v>
@@ -17740,11 +17740,11 @@
       <c r="V39" s="58"/>
     </row>
     <row r="40" spans="3:22" ht="12">
-      <c r="C40" s="79" t="s">
+      <c r="C40" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="79"/>
-      <c r="E40" s="79"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
       <c r="F40" s="3">
         <f>'REALIZADO 2025'!D65*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1550.68595</v>
@@ -17804,11 +17804,11 @@
       <c r="V40" s="58"/>
     </row>
     <row r="41" spans="3:22" ht="12">
-      <c r="C41" s="79" t="s">
+      <c r="C41" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="79"/>
-      <c r="E41" s="79"/>
+      <c r="D41" s="69"/>
+      <c r="E41" s="69"/>
       <c r="F41" s="3">
         <f>'REALIZADO 2025'!D67*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -17869,11 +17869,11 @@
       <c r="V41" s="58"/>
     </row>
     <row r="42" spans="3:22" ht="12">
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="69"/>
       <c r="F42" s="3">
         <f>'REALIZADO 2025'!D68*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>3193.8857499999995</v>
@@ -17933,11 +17933,11 @@
       <c r="V42" s="58"/>
     </row>
     <row r="43" spans="3:22" ht="12">
-      <c r="C43" s="79" t="s">
+      <c r="C43" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="79"/>
-      <c r="E43" s="79"/>
+      <c r="D43" s="69"/>
+      <c r="E43" s="69"/>
       <c r="F43" s="3">
         <f>'REALIZADO 2025'!D69*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>610.80250000000001</v>
@@ -17996,11 +17996,11 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="3:22" ht="12">
-      <c r="C44" s="79" t="s">
+      <c r="C44" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="79"/>
-      <c r="E44" s="79"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
       <c r="F44" s="3">
         <f>'REALIZADO 2025'!D70*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>554.51879999999994</v>
@@ -18060,11 +18060,11 @@
       <c r="T44" s="5"/>
     </row>
     <row r="45" spans="3:22" ht="12">
-      <c r="C45" s="79" t="s">
+      <c r="C45" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="79"/>
-      <c r="E45" s="79"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
       <c r="F45" s="3">
         <f>'REALIZADO 2025'!D71*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18124,11 +18124,11 @@
       <c r="T45" s="5"/>
     </row>
     <row r="46" spans="3:22" ht="12">
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
+      <c r="D46" s="69"/>
+      <c r="E46" s="69"/>
       <c r="F46" s="3">
         <f>'REALIZADO 2025'!D72*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>5500.8486499999999</v>
@@ -18187,11 +18187,11 @@
       <c r="T46" s="5"/>
     </row>
     <row r="47" spans="3:22" ht="12">
-      <c r="C47" s="82" t="s">
+      <c r="C47" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="82"/>
-      <c r="E47" s="82"/>
+      <c r="D47" s="77"/>
+      <c r="E47" s="77"/>
       <c r="F47" s="3">
         <f>'REALIZADO 2025'!D73*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>349.70924999999994</v>
@@ -18250,11 +18250,11 @@
       <c r="T47" s="5"/>
     </row>
     <row r="48" spans="3:22" ht="12">
-      <c r="C48" s="79" t="s">
+      <c r="C48" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
+      <c r="D48" s="69"/>
+      <c r="E48" s="69"/>
       <c r="F48" s="3">
         <f>'REALIZADO 2025'!D74*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>12.54</v>
@@ -18314,11 +18314,11 @@
       <c r="T48" s="5"/>
     </row>
     <row r="49" spans="3:20" ht="12">
-      <c r="C49" s="81" t="s">
+      <c r="C49" s="75" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
+      <c r="D49" s="76"/>
+      <c r="E49" s="76"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
@@ -18341,11 +18341,11 @@
       <c r="T49" s="5"/>
     </row>
     <row r="50" spans="3:20" ht="12">
-      <c r="C50" s="81" t="s">
+      <c r="C50" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -18368,11 +18368,11 @@
       <c r="T50" s="5"/>
     </row>
     <row r="51" spans="3:20" ht="12">
-      <c r="C51" s="81" t="s">
+      <c r="C51" s="75" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
@@ -18395,11 +18395,11 @@
       <c r="T51" s="5"/>
     </row>
     <row r="52" spans="3:20" ht="12">
-      <c r="C52" s="81" t="s">
+      <c r="C52" s="75" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
+      <c r="D52" s="76"/>
+      <c r="E52" s="76"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -18422,11 +18422,11 @@
       <c r="T52" s="5"/>
     </row>
     <row r="53" spans="3:20" ht="12">
-      <c r="C53" s="81" t="s">
+      <c r="C53" s="75" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
+      <c r="D53" s="76"/>
+      <c r="E53" s="76"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -18449,11 +18449,11 @@
       <c r="T53" s="5"/>
     </row>
     <row r="54" spans="3:20" ht="12">
-      <c r="C54" s="81" t="s">
+      <c r="C54" s="75" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="81"/>
-      <c r="E54" s="81"/>
+      <c r="D54" s="75"/>
+      <c r="E54" s="75"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -18476,11 +18476,11 @@
       <c r="T54" s="5"/>
     </row>
     <row r="55" spans="3:20" ht="12" customHeight="1">
-      <c r="C55" s="78" t="s">
+      <c r="C55" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="D55" s="78"/>
-      <c r="E55" s="78"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="74"/>
       <c r="F55" s="8">
         <f>SUM(F56:F67)</f>
         <v>13069.940399999999</v>
@@ -18540,11 +18540,11 @@
       <c r="T55" s="5"/>
     </row>
     <row r="56" spans="3:20" ht="12">
-      <c r="C56" s="79" t="s">
+      <c r="C56" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="79"/>
-      <c r="E56" s="79"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="69"/>
       <c r="F56" s="3">
         <f>'REALIZADO 2025'!D76*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1201.7082</v>
@@ -18604,11 +18604,11 @@
       <c r="T56" s="5"/>
     </row>
     <row r="57" spans="3:20" ht="12">
-      <c r="C57" s="79" t="s">
+      <c r="C57" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="D57" s="79"/>
-      <c r="E57" s="79"/>
+      <c r="D57" s="69"/>
+      <c r="E57" s="69"/>
       <c r="F57" s="3">
         <f>'REALIZADO 2025'!D77*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18668,11 +18668,11 @@
       <c r="T57" s="5"/>
     </row>
     <row r="58" spans="3:20" ht="12">
-      <c r="C58" s="79" t="s">
+      <c r="C58" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
+      <c r="D58" s="69"/>
+      <c r="E58" s="69"/>
       <c r="F58" s="3">
         <f>'REALIZADO 2025'!D78*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>888.24999999999989</v>
@@ -18732,11 +18732,11 @@
       <c r="T58" s="5"/>
     </row>
     <row r="59" spans="3:20" ht="12">
-      <c r="C59" s="79" t="s">
+      <c r="C59" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="D59" s="79"/>
-      <c r="E59" s="79"/>
+      <c r="D59" s="69"/>
+      <c r="E59" s="69"/>
       <c r="F59" s="3">
         <f>'REALIZADO 2025'!D79*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18796,11 +18796,11 @@
       <c r="T59" s="5"/>
     </row>
     <row r="60" spans="3:20" ht="12">
-      <c r="C60" s="79" t="s">
+      <c r="C60" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="79"/>
-      <c r="E60" s="79"/>
+      <c r="D60" s="69"/>
+      <c r="E60" s="69"/>
       <c r="F60" s="3">
         <f>'REALIZADO 2025'!D80*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2080.5113999999999</v>
@@ -18859,11 +18859,11 @@
       <c r="T60" s="5"/>
     </row>
     <row r="61" spans="3:20" ht="12">
-      <c r="C61" s="79" t="s">
+      <c r="C61" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="79"/>
-      <c r="E61" s="79"/>
+      <c r="D61" s="69"/>
+      <c r="E61" s="69"/>
       <c r="F61" s="3">
         <f>'REALIZADO 2025'!D81*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18923,11 +18923,11 @@
       <c r="T61" s="5"/>
     </row>
     <row r="62" spans="3:20" ht="12">
-      <c r="C62" s="79" t="s">
+      <c r="C62" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D62" s="79"/>
-      <c r="E62" s="79"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="69"/>
       <c r="F62" s="3">
         <f>'REALIZADO 2025'!D82*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>7691.6597999999994</v>
@@ -18987,11 +18987,11 @@
       <c r="T62" s="5"/>
     </row>
     <row r="63" spans="3:20" ht="12">
-      <c r="C63" s="79" t="s">
+      <c r="C63" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="79"/>
-      <c r="E63" s="79"/>
+      <c r="D63" s="69"/>
+      <c r="E63" s="69"/>
       <c r="F63" s="3">
         <f>'REALIZADO 2025'!D83*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1149.5</v>
@@ -19050,11 +19050,11 @@
       <c r="T63" s="5"/>
     </row>
     <row r="64" spans="3:20" ht="12">
-      <c r="C64" s="79" t="s">
+      <c r="C64" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="79"/>
-      <c r="E64" s="79"/>
+      <c r="D64" s="69"/>
+      <c r="E64" s="69"/>
       <c r="F64" s="3">
         <f>'REALIZADO 2025'!D84*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -19114,11 +19114,11 @@
       <c r="T64" s="5"/>
     </row>
     <row r="65" spans="3:21" ht="12">
-      <c r="C65" s="79" t="s">
+      <c r="C65" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="79"/>
-      <c r="E65" s="79"/>
+      <c r="D65" s="69"/>
+      <c r="E65" s="69"/>
       <c r="F65" s="3">
         <f>'REALIZADO 2025'!D85*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>58.310999999999993</v>
@@ -19178,11 +19178,11 @@
       <c r="T65" s="5"/>
     </row>
     <row r="66" spans="3:21" ht="12">
-      <c r="C66" s="79" t="s">
+      <c r="C66" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="79"/>
-      <c r="E66" s="79"/>
+      <c r="D66" s="69"/>
+      <c r="E66" s="69"/>
       <c r="F66" s="3">
         <f>'REALIZADO 2025'!D86*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -19242,11 +19242,11 @@
       <c r="T66" s="5"/>
     </row>
     <row r="67" spans="3:21" ht="12">
-      <c r="C67" s="79" t="s">
+      <c r="C67" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="D67" s="79"/>
-      <c r="E67" s="79"/>
+      <c r="D67" s="69"/>
+      <c r="E67" s="69"/>
       <c r="F67" s="3">
         <f>'REALIZADO 2025'!D87*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -19306,11 +19306,11 @@
       <c r="T67" s="5"/>
     </row>
     <row r="68" spans="3:21" ht="12">
-      <c r="C68" s="78" t="s">
+      <c r="C68" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="D68" s="78"/>
-      <c r="E68" s="78"/>
+      <c r="D68" s="74"/>
+      <c r="E68" s="74"/>
       <c r="F68" s="8">
         <f>SUM(F69:F71)</f>
         <v>16132.187499999998</v>
@@ -19370,11 +19370,11 @@
       <c r="T68" s="5"/>
     </row>
     <row r="69" spans="3:21" ht="12">
-      <c r="C69" s="79" t="s">
+      <c r="C69" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="79"/>
-      <c r="E69" s="79"/>
+      <c r="D69" s="69"/>
+      <c r="E69" s="69"/>
       <c r="F69" s="3">
         <f>'REALIZADO 2025'!D89*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>6040.6224999999995</v>
@@ -19434,11 +19434,11 @@
       <c r="T69" s="5"/>
     </row>
     <row r="70" spans="3:21" ht="12">
-      <c r="C70" s="79" t="s">
+      <c r="C70" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="79"/>
-      <c r="E70" s="79"/>
+      <c r="D70" s="69"/>
+      <c r="E70" s="69"/>
       <c r="F70" s="3">
         <f>'REALIZADO 2025'!D90*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>7357.8449999999993</v>
@@ -19491,17 +19491,17 @@
         <v>25000</v>
       </c>
       <c r="S70" s="25">
-        <f t="shared" ref="S70:S124" si="11">R70/12</f>
+        <f t="shared" ref="S70:S87" si="11">R70/12</f>
         <v>2083.3333333333335</v>
       </c>
       <c r="T70" s="5"/>
     </row>
     <row r="71" spans="3:21" ht="12">
-      <c r="C71" s="79" t="s">
+      <c r="C71" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D71" s="79"/>
-      <c r="E71" s="79"/>
+      <c r="D71" s="69"/>
+      <c r="E71" s="69"/>
       <c r="F71" s="3">
         <f>'REALIZADO 2025'!D91*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2733.72</v>
@@ -19561,11 +19561,11 @@
       <c r="T71" s="5"/>
     </row>
     <row r="72" spans="3:21" ht="12">
-      <c r="C72" s="78" t="s">
+      <c r="C72" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="D72" s="78"/>
-      <c r="E72" s="78"/>
+      <c r="D72" s="74"/>
+      <c r="E72" s="74"/>
       <c r="F72" s="8">
         <f>SUM(F73:F77)</f>
         <v>7920.1594999999998</v>
@@ -19625,11 +19625,11 @@
       <c r="T72" s="5"/>
     </row>
     <row r="73" spans="3:21" ht="12">
-      <c r="C73" s="79" t="s">
+      <c r="C73" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="D73" s="79"/>
-      <c r="E73" s="79"/>
+      <c r="D73" s="69"/>
+      <c r="E73" s="69"/>
       <c r="F73" s="3">
         <f>'REALIZADO 2025'!D93*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>909.15</v>
@@ -19689,11 +19689,11 @@
       <c r="T73" s="5"/>
     </row>
     <row r="74" spans="3:21" ht="12">
-      <c r="C74" s="79" t="s">
+      <c r="C74" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="D74" s="79"/>
-      <c r="E74" s="79"/>
+      <c r="D74" s="69"/>
+      <c r="E74" s="69"/>
       <c r="F74" s="3">
         <f>'REALIZADO 2025'!D94*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>752.4</v>
@@ -19753,11 +19753,11 @@
       <c r="T74" s="5"/>
     </row>
     <row r="75" spans="3:21" ht="12">
-      <c r="C75" s="79" t="s">
+      <c r="C75" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="D75" s="79"/>
-      <c r="E75" s="79"/>
+      <c r="D75" s="69"/>
+      <c r="E75" s="69"/>
       <c r="F75" s="3">
         <f>'REALIZADO 2025'!D95*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2403.5</v>
@@ -19817,11 +19817,11 @@
       <c r="T75" s="5"/>
     </row>
     <row r="76" spans="3:21" ht="12">
-      <c r="C76" s="79" t="s">
+      <c r="C76" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="D76" s="79"/>
-      <c r="E76" s="79"/>
+      <c r="D76" s="69"/>
+      <c r="E76" s="69"/>
       <c r="F76" s="3">
         <f>'REALIZADO 2025'!D96*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1472.5094999999999</v>
@@ -19880,11 +19880,11 @@
       <c r="T76" s="5"/>
     </row>
     <row r="77" spans="3:21" ht="12">
-      <c r="C77" s="79" t="s">
+      <c r="C77" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="79"/>
-      <c r="E77" s="79"/>
+      <c r="D77" s="69"/>
+      <c r="E77" s="69"/>
       <c r="F77" s="3">
         <f>'REALIZADO 2025'!D97*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2382.6</v>
@@ -19944,11 +19944,11 @@
       <c r="T77" s="5"/>
     </row>
     <row r="78" spans="3:21" ht="12">
-      <c r="C78" s="78" t="s">
+      <c r="C78" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="D78" s="78"/>
-      <c r="E78" s="78"/>
+      <c r="D78" s="74"/>
+      <c r="E78" s="74"/>
       <c r="F78" s="8">
         <f t="shared" ref="F78:R78" si="13">SUM(F79:F85)</f>
         <v>74062.399949999992</v>
@@ -20013,11 +20013,11 @@
       </c>
     </row>
     <row r="79" spans="3:21" ht="12">
-      <c r="C79" s="79" t="s">
+      <c r="C79" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="79"/>
-      <c r="E79" s="79"/>
+      <c r="D79" s="69"/>
+      <c r="E79" s="69"/>
       <c r="F79" s="3">
         <f>'REALIZADO 2025'!D99*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>4117.2999999999993</v>
@@ -20077,11 +20077,11 @@
       <c r="T79" s="5"/>
     </row>
     <row r="80" spans="3:21" ht="12">
-      <c r="C80" s="79" t="s">
+      <c r="C80" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="D80" s="79"/>
-      <c r="E80" s="79"/>
+      <c r="D80" s="69"/>
+      <c r="E80" s="69"/>
       <c r="F80" s="3">
         <f>'REALIZADO 2025'!D100*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>2951.08</v>
@@ -20141,11 +20141,11 @@
       <c r="T80" s="5"/>
     </row>
     <row r="81" spans="3:21" ht="12">
-      <c r="C81" s="79" t="s">
+      <c r="C81" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="D81" s="79"/>
-      <c r="E81" s="79"/>
+      <c r="D81" s="69"/>
+      <c r="E81" s="69"/>
       <c r="F81" s="3">
         <f>'REALIZADO 2025'!D101*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>4270.2671</v>
@@ -20205,11 +20205,11 @@
       <c r="T81" s="5"/>
     </row>
     <row r="82" spans="3:21" ht="12">
-      <c r="C82" s="79" t="s">
+      <c r="C82" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="D82" s="79"/>
-      <c r="E82" s="79"/>
+      <c r="D82" s="69"/>
+      <c r="E82" s="69"/>
       <c r="F82" s="3">
         <f>'REALIZADO 2025'!D102*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>58965.410349999998</v>
@@ -20269,11 +20269,11 @@
       <c r="T82" s="5"/>
     </row>
     <row r="83" spans="3:21" ht="12">
-      <c r="C83" s="79" t="s">
+      <c r="C83" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="D83" s="79"/>
-      <c r="E83" s="79"/>
+      <c r="D83" s="69"/>
+      <c r="E83" s="69"/>
       <c r="F83" s="3">
         <f>'REALIZADO 2025'!D103*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>0</v>
@@ -20333,11 +20333,11 @@
       <c r="T83" s="5"/>
     </row>
     <row r="84" spans="3:21" ht="12">
-      <c r="C84" s="79" t="s">
+      <c r="C84" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="D84" s="79"/>
-      <c r="E84" s="79"/>
+      <c r="D84" s="69"/>
+      <c r="E84" s="69"/>
       <c r="F84" s="3">
         <f>'REALIZADO 2025'!D104*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>2508</v>
@@ -20397,11 +20397,11 @@
       <c r="T84" s="5"/>
     </row>
     <row r="85" spans="3:21" ht="12">
-      <c r="C85" s="79" t="s">
+      <c r="C85" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
+      <c r="D85" s="69"/>
+      <c r="E85" s="69"/>
       <c r="F85" s="3">
         <f>'REALIZADO 2025'!D106*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>1250.3425</v>
@@ -20461,66 +20461,66 @@
       <c r="T85" s="5"/>
     </row>
     <row r="86" spans="3:21" ht="12">
-      <c r="C86" s="78" t="s">
+      <c r="C86" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="D86" s="78"/>
-      <c r="E86" s="78"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="74"/>
       <c r="F86" s="8">
-        <f>SUM(F87:F98)</f>
-        <v>15905.234399999999</v>
+        <f>SUM(F87:F96)</f>
+        <v>13871.8943</v>
       </c>
       <c r="G86" s="8">
-        <f t="shared" ref="G86:Q86" si="15">SUM(G87:G98)</f>
-        <v>21901.245849999992</v>
+        <f>SUM(G87:G96)</f>
+        <v>20017.058599999997</v>
       </c>
       <c r="H86" s="8">
-        <f t="shared" si="15"/>
-        <v>21263.147949999995</v>
+        <f>SUM(H87:H96)</f>
+        <v>18725.417699999995</v>
       </c>
       <c r="I86" s="8">
-        <f t="shared" si="15"/>
-        <v>9530.8075499999995</v>
+        <f>SUM(I87:I96)</f>
+        <v>7115.7602999999981</v>
       </c>
       <c r="J86" s="8">
-        <f t="shared" si="15"/>
-        <v>35037.606450000007</v>
+        <f>SUM(J87:J96)</f>
+        <v>33776.176500000001</v>
       </c>
       <c r="K86" s="8">
-        <f t="shared" si="15"/>
-        <v>20789.78385</v>
+        <f>SUM(K87:K96)</f>
+        <v>17102.8253</v>
       </c>
       <c r="L86" s="8">
-        <f t="shared" si="15"/>
-        <v>22684.745049999998</v>
+        <f>SUM(L87:L96)</f>
+        <v>16127.474549999999</v>
       </c>
       <c r="M86" s="8">
-        <f t="shared" si="15"/>
-        <v>22941.177599999999</v>
+        <f>SUM(M87:M96)</f>
+        <v>17502.4751</v>
       </c>
       <c r="N86" s="8">
-        <f t="shared" si="15"/>
-        <v>16472.094650000003</v>
+        <f>SUM(N87:N96)</f>
+        <v>14729.24365</v>
       </c>
       <c r="O86" s="8">
-        <f t="shared" si="15"/>
-        <v>20030.570449999999</v>
+        <f>SUM(O87:O96)</f>
+        <v>16369.684649999999</v>
       </c>
       <c r="P86" s="8">
-        <f t="shared" si="15"/>
-        <v>22049.207399999996</v>
+        <f>SUM(P87:P96)</f>
+        <v>17673.928250000001</v>
       </c>
       <c r="Q86" s="8">
-        <f t="shared" si="15"/>
-        <v>10774.179899999997</v>
+        <f>SUM(Q87:Q96)</f>
+        <v>9433.4449000000004</v>
       </c>
       <c r="R86" s="9">
-        <f>SUM(R87:R98)</f>
-        <v>167560.79994999999</v>
+        <f>SUM(R87:R99)</f>
+        <v>167560.79994999996</v>
       </c>
       <c r="S86" s="28">
         <f>R86/12</f>
-        <v>13963.399995833332</v>
+        <v>13963.39999583333</v>
       </c>
       <c r="T86" s="12" t="s">
         <v>18</v>
@@ -20530,11 +20530,11 @@
       </c>
     </row>
     <row r="87" spans="3:21" ht="12">
-      <c r="C87" s="79" t="s">
+      <c r="C87" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="D87" s="79"/>
-      <c r="E87" s="79"/>
+      <c r="D87" s="69"/>
+      <c r="E87" s="69"/>
       <c r="F87" s="3">
         <f>'REALIZADO 2025'!D109*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>11147.161299999998</v>
@@ -20593,841 +20593,839 @@
       <c r="T87" s="5"/>
     </row>
     <row r="88" spans="3:21" ht="12">
-      <c r="C88" s="79" t="s">
+      <c r="C88" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="D88" s="69"/>
+      <c r="E88" s="69"/>
+      <c r="F88" s="3">
+        <f>'REALIZADO 2025'!D113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="G88" s="3">
+        <f>'REALIZADO 2025'!E113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="H88" s="3">
+        <f>'REALIZADO 2025'!F113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="I88" s="3">
+        <f>'REALIZADO 2025'!G113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="J88" s="3">
+        <f>'REALIZADO 2025'!H113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="K88" s="3">
+        <f>'REALIZADO 2025'!I113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="L88" s="3">
+        <f>'REALIZADO 2025'!J113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="M88" s="3">
+        <f>'REALIZADO 2025'!K113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="N88" s="3">
+        <f>'REALIZADO 2025'!L113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="O88" s="3">
+        <f>'REALIZADO 2025'!M113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2439.7823999999996</v>
+      </c>
+      <c r="P88" s="3">
+        <f>'REALIZADO 2025'!N113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2649.4512</v>
+      </c>
+      <c r="Q88" s="3">
+        <f>'REALIZADO 2025'!O113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2649.4512</v>
+      </c>
+      <c r="R88" s="4">
+        <f>SUM(F88:Q88)</f>
+        <v>27256.943999999996</v>
+      </c>
+      <c r="S88" s="25">
+        <f>R88/12</f>
+        <v>2271.4119999999998</v>
+      </c>
+      <c r="T88" s="5"/>
+    </row>
+    <row r="89" spans="3:21" ht="12">
+      <c r="C89" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
+      <c r="F89" s="3">
+        <f>'REALIZADO 2025'!D114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>102.8489</v>
+      </c>
+      <c r="G89" s="3">
+        <f>'REALIZADO 2025'!E114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>105.09564999999999</v>
+      </c>
+      <c r="H89" s="3">
+        <f>'REALIZADO 2025'!F114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>104.92844999999998</v>
+      </c>
+      <c r="I89" s="3">
+        <f>'REALIZADO 2025'!G114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>104.92844999999998</v>
+      </c>
+      <c r="J89" s="3">
+        <f>'REALIZADO 2025'!H114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>102.8489</v>
+      </c>
+      <c r="K89" s="3">
+        <f>'REALIZADO 2025'!I114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
+        <f>'REALIZADO 2025'!J114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>102.8489</v>
+      </c>
+      <c r="M89" s="3">
+        <f>'REALIZADO 2025'!K114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>102.8489</v>
+      </c>
+      <c r="N89" s="3">
+        <f>'REALIZADO 2025'!L114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>102.8489</v>
+      </c>
+      <c r="O89" s="3">
+        <f>'REALIZADO 2025'!M114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>102.8489</v>
+      </c>
+      <c r="P89" s="3">
+        <f>'REALIZADO 2025'!N114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>102.8489</v>
+      </c>
+      <c r="Q89" s="3">
+        <f>'REALIZADO 2025'!O114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>92.273499999999984</v>
+      </c>
+      <c r="R89" s="4">
+        <f>SUM(F89:Q89)</f>
+        <v>1127.1683499999999</v>
+      </c>
+      <c r="S89" s="25">
+        <f>R89/12</f>
+        <v>93.930695833333331</v>
+      </c>
+      <c r="T89" s="5"/>
+    </row>
+    <row r="90" spans="3:21" ht="12">
+      <c r="C90" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="D90" s="69"/>
+      <c r="E90" s="69"/>
+      <c r="F90" s="3">
+        <f>'REALIZADO 2025'!D115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>208.98955000000001</v>
+      </c>
+      <c r="G90" s="3">
+        <f>'REALIZADO 2025'!E115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>594.66769999999985</v>
+      </c>
+      <c r="H90" s="3">
+        <f>'REALIZADO 2025'!F115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>188.39259999999999</v>
+      </c>
+      <c r="I90" s="3">
+        <f>'REALIZADO 2025'!G115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>619.47599999999989</v>
+      </c>
+      <c r="J90" s="3">
+        <f>'REALIZADO 2025'!H115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>411.88674999999995</v>
+      </c>
+      <c r="K90" s="3">
+        <f>'REALIZADO 2025'!I115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>197.48409999999998</v>
+      </c>
+      <c r="L90" s="3">
+        <f>'REALIZADO 2025'!J115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>312.36095</v>
+      </c>
+      <c r="M90" s="3">
+        <f>'REALIZADO 2025'!K115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="N90" s="3">
+        <f>'REALIZADO 2025'!L115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>208.98955000000001</v>
+      </c>
+      <c r="O90" s="3">
+        <f>'REALIZADO 2025'!M115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>197.72444999999999</v>
+      </c>
+      <c r="P90" s="3">
+        <f>'REALIZADO 2025'!N115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>441.06314999999995</v>
+      </c>
+      <c r="Q90" s="3">
+        <f>'REALIZADO 2025'!O115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>88.626449999999991</v>
+      </c>
+      <c r="R90" s="4">
+        <f>SUM(F90:Q90)</f>
+        <v>3469.6612500000001</v>
+      </c>
+      <c r="S90" s="25">
+        <f>R90/12</f>
+        <v>289.13843750000001</v>
+      </c>
+      <c r="T90" s="5"/>
+    </row>
+    <row r="92" spans="3:21" ht="12">
+      <c r="C92" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="D92" s="69"/>
+      <c r="E92" s="69"/>
+      <c r="F92" s="3">
+        <f>'REALIZADO 2025'!D116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="G92" s="3">
+        <f>'REALIZADO 2025'!E116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>128.21105</v>
+      </c>
+      <c r="H92" s="3">
+        <f>'REALIZADO 2025'!F116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>256.4221</v>
+      </c>
+      <c r="I92" s="3">
+        <f>'REALIZADO 2025'!G116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>9.5408500000000007</v>
+      </c>
+      <c r="J92" s="3">
+        <f>'REALIZADO 2025'!H116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>128.21105</v>
+      </c>
+      <c r="K92" s="3">
+        <f>'REALIZADO 2025'!I116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>140.35395</v>
+      </c>
+      <c r="L92" s="3">
+        <f>'REALIZADO 2025'!J116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="M92" s="3">
+        <f>'REALIZADO 2025'!K116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>335.35095000000001</v>
+      </c>
+      <c r="N92" s="3">
+        <f>'REALIZADO 2025'!L116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>140.11359999999999</v>
+      </c>
+      <c r="O92" s="3">
+        <f>'REALIZADO 2025'!M116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>140.90779999999998</v>
+      </c>
+      <c r="P92" s="3">
+        <f>'REALIZADO 2025'!N116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>140.90779999999998</v>
+      </c>
+      <c r="Q92" s="3">
+        <f>'REALIZADO 2025'!O116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>140.90779999999998</v>
+      </c>
+      <c r="R92" s="4">
+        <f>SUM(F92:Q92)</f>
+        <v>1560.9269499999998</v>
+      </c>
+      <c r="S92" s="25">
+        <f>R92/12</f>
+        <v>130.07724583333331</v>
+      </c>
+      <c r="T92" s="5"/>
+    </row>
+    <row r="93" spans="3:21" ht="12">
+      <c r="C93" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="D93" s="69"/>
+      <c r="E93" s="69"/>
+      <c r="F93" s="3">
+        <f>'REALIZADO 2025'!D117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>101.25004999999999</v>
+      </c>
+      <c r="G93" s="3">
+        <f>'REALIZADO 2025'!E117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>101.25004999999999</v>
+      </c>
+      <c r="H93" s="3">
+        <f>'REALIZADO 2025'!F117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>101.25004999999999</v>
+      </c>
+      <c r="I93" s="3">
+        <f>'REALIZADO 2025'!G117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>101.25004999999999</v>
+      </c>
+      <c r="J93" s="3">
+        <f>'REALIZADO 2025'!H117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="K93" s="3">
+        <f>'REALIZADO 2025'!I117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>550.70454999999993</v>
+      </c>
+      <c r="L93" s="3">
+        <f>'REALIZADO 2025'!J117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>137.75189999999998</v>
+      </c>
+      <c r="M93" s="3">
+        <f>'REALIZADO 2025'!K117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>352.46805000000001</v>
+      </c>
+      <c r="N93" s="3">
+        <f>'REALIZADO 2025'!L117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>97.007349999999988</v>
+      </c>
+      <c r="O93" s="3">
+        <f>'REALIZADO 2025'!M117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>310.67849999999999</v>
+      </c>
+      <c r="P93" s="3">
+        <f>'REALIZADO 2025'!N117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>208.98955000000001</v>
+      </c>
+      <c r="Q93" s="3">
+        <f>'REALIZADO 2025'!O117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>308.93334999999996</v>
+      </c>
+      <c r="R93" s="4">
+        <f>SUM(F93:Q93)</f>
+        <v>2371.5334499999994</v>
+      </c>
+      <c r="S93" s="25">
+        <f>R93/12</f>
+        <v>197.62778749999995</v>
+      </c>
+      <c r="T93" s="5"/>
+    </row>
+    <row r="94" spans="3:21" ht="12" customHeight="1">
+      <c r="C94" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="D94" s="92"/>
+      <c r="E94" s="92"/>
+      <c r="F94" s="3">
+        <f>'REALIZADO 2025'!D118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="G94" s="3">
+        <f>'REALIZADO 2025'!E118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="H94" s="3">
+        <f>'REALIZADO 2025'!F118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="I94" s="3">
+        <f>'REALIZADO 2025'!G118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="J94" s="3">
+        <f>'REALIZADO 2025'!H118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="K94" s="3">
+        <f>'REALIZADO 2025'!I118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <f>'REALIZADO 2025'!J118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="M94" s="3">
+        <f>'REALIZADO 2025'!K118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="N94" s="3">
+        <f>'REALIZADO 2025'!L118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="O94" s="3">
+        <f>'REALIZADO 2025'!M118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="P94" s="3">
+        <f>'REALIZADO 2025'!N118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="Q94" s="3">
+        <f>'REALIZADO 2025'!O118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>36.470499999999994</v>
+      </c>
+      <c r="R94" s="4">
+        <f>SUM(F94:Q94)</f>
+        <v>401.1755</v>
+      </c>
+      <c r="S94" s="25">
+        <f>R94/12</f>
+        <v>33.431291666666667</v>
+      </c>
+      <c r="T94" s="5"/>
+    </row>
+    <row r="95" spans="3:21" ht="12" customHeight="1">
+      <c r="C95" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="D95" s="92"/>
+      <c r="E95" s="92"/>
+      <c r="F95" s="3">
+        <f>'REALIZADO 2025'!D119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>762.84999999999991</v>
+      </c>
+      <c r="G95" s="3">
+        <f>'REALIZADO 2025'!E119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="3">
+        <f>'REALIZADO 2025'!F119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="I95" s="3">
+        <f>'REALIZADO 2025'!G119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>893.47499999999991</v>
+      </c>
+      <c r="J95" s="3">
+        <f>'REALIZADO 2025'!H119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="K95" s="3">
+        <f>'REALIZADO 2025'!I119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="L95" s="3">
+        <f>'REALIZADO 2025'!J119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="M95" s="3">
+        <f>'REALIZADO 2025'!K119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>893.47499999999991</v>
+      </c>
+      <c r="N95" s="3">
+        <f>'REALIZADO 2025'!L119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="O95" s="3">
+        <f>'REALIZADO 2025'!M119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="P95" s="3">
+        <f>'REALIZADO 2025'!N119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>893.47499999999991</v>
+      </c>
+      <c r="Q95" s="3">
+        <f>'REALIZADO 2025'!O119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>0</v>
+      </c>
+      <c r="R95" s="4">
+        <f>SUM(F95:Q95)</f>
+        <v>3443.2749999999996</v>
+      </c>
+      <c r="S95" s="25">
+        <f>R95/12</f>
+        <v>286.9395833333333</v>
+      </c>
+      <c r="T95" s="5"/>
+    </row>
+    <row r="96" spans="3:21" ht="12" customHeight="1">
+      <c r="C96" s="69" t="s">
+        <v>112</v>
+      </c>
+      <c r="D96" s="92"/>
+      <c r="E96" s="92"/>
+      <c r="F96" s="3">
+        <f>'REALIZADO 2025'!D120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>1512.3239999999998</v>
+      </c>
+      <c r="G96" s="3">
+        <f>'REALIZADO 2025'!E120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2808.11355</v>
+      </c>
+      <c r="H96" s="3">
+        <f>'REALIZADO 2025'!F120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2170.7262499999997</v>
+      </c>
+      <c r="I96" s="3">
+        <f>'REALIZADO 2025'!G120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2910.8370499999996</v>
+      </c>
+      <c r="J96" s="3">
+        <f>'REALIZADO 2025'!H120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2188.1673000000001</v>
+      </c>
+      <c r="K96" s="3">
+        <f>'REALIZADO 2025'!I120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>1592.8099</v>
+      </c>
+      <c r="L96" s="3">
+        <f>'REALIZADO 2025'!J120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>1730.23785</v>
+      </c>
+      <c r="M96" s="3">
+        <f>'REALIZADO 2025'!K120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>1249.6632499999998</v>
+      </c>
+      <c r="N96" s="3">
+        <f>'REALIZADO 2025'!L120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>1607.1263999999999</v>
+      </c>
+      <c r="O96" s="3">
+        <f>'REALIZADO 2025'!M120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>1652.6674999999998</v>
+      </c>
+      <c r="P96" s="3">
+        <f>'REALIZADO 2025'!N120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2478.6459499999996</v>
+      </c>
+      <c r="Q96" s="3">
+        <f>'REALIZADO 2025'!O120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
+        <v>2191.3022999999998</v>
+      </c>
+      <c r="R96" s="4">
+        <f t="shared" ref="R96" si="15">SUM(F96:Q96)</f>
+        <v>24092.621299999995</v>
+      </c>
+      <c r="S96" s="25">
+        <f>R96/12</f>
+        <v>2007.7184416666662</v>
+      </c>
+      <c r="T96" s="5"/>
+    </row>
+    <row r="97" spans="3:20" ht="12">
+      <c r="C97" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="D88" s="79"/>
-      <c r="E88" s="79"/>
-      <c r="F88" s="3">
+      <c r="D97" s="69"/>
+      <c r="E97" s="69"/>
+      <c r="F97" s="3">
         <f>'REALIZADO 2025'!D110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1863.7366</v>
       </c>
-      <c r="G88" s="3">
+      <c r="G97" s="3">
         <f>'REALIZADO 2025'!E110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1517.8625</v>
       </c>
-      <c r="H88" s="3">
+      <c r="H97" s="3">
         <f>'REALIZADO 2025'!F110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>2064.8155000000002</v>
       </c>
-      <c r="I88" s="3">
+      <c r="I97" s="3">
         <f>'REALIZADO 2025'!G110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>2181.1239999999998</v>
       </c>
-      <c r="J88" s="3">
+      <c r="J97" s="3">
         <f>'REALIZADO 2025'!H110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1091.8264499999998</v>
       </c>
-      <c r="K88" s="3">
+      <c r="K97" s="3">
         <f>'REALIZADO 2025'!I110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>2025.4085499999999</v>
       </c>
-      <c r="L88" s="3">
+      <c r="L97" s="3">
         <f>'REALIZADO 2025'!J110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>5704.5504999999994</v>
       </c>
-      <c r="M88" s="3">
+      <c r="M97" s="3">
         <f>'REALIZADO 2025'!K110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>2946.6909999999998</v>
       </c>
-      <c r="N88" s="3">
+      <c r="N97" s="3">
         <f>'REALIZADO 2025'!L110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="O88" s="3">
+      <c r="O97" s="3">
         <f>'REALIZADO 2025'!M110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>3531.4938999999999</v>
       </c>
-      <c r="P88" s="3">
+      <c r="P97" s="3">
         <f>'REALIZADO 2025'!N110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>2828.6791499999995</v>
       </c>
-      <c r="Q88" s="3">
+      <c r="Q97" s="3">
         <f>'REALIZADO 2025'!O110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1340.7349999999999</v>
       </c>
-      <c r="R88" s="4">
+      <c r="R97" s="4">
         <v>24000</v>
       </c>
-      <c r="S88" s="25">
-        <f t="shared" si="11"/>
+      <c r="S97" s="25">
+        <f>R97/12</f>
         <v>2000</v>
       </c>
-      <c r="T88" s="5"/>
-    </row>
-    <row r="89" spans="3:21" ht="12">
-      <c r="C89" s="79" t="s">
+      <c r="T97" s="5"/>
+    </row>
+    <row r="98" spans="3:20" ht="12">
+      <c r="C98" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="D89" s="79"/>
-      <c r="E89" s="79"/>
-      <c r="F89" s="3">
+      <c r="D98" s="69"/>
+      <c r="E98" s="69"/>
+      <c r="F98" s="3">
         <f>'REALIZADO 2025'!D111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G98" s="3">
         <f>'REALIZADO 2025'!E111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H98" s="3">
         <f>'REALIZADO 2025'!F111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>276.19349999999997</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I98" s="3">
         <f>'REALIZADO 2025'!G111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>64.319749999999999</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J98" s="3">
         <f>'REALIZADO 2025'!H111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K98" s="3">
         <f>'REALIZADO 2025'!I111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1661.55</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L98" s="3">
         <f>'REALIZADO 2025'!J111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>852.71999999999991</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M98" s="3">
         <f>'REALIZADO 2025'!K111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>2309.4499999999998</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N98" s="3">
         <f>'REALIZADO 2025'!L111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1546.6</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O98" s="3">
         <f>'REALIZADO 2025'!M111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>129.39189999999999</v>
       </c>
-      <c r="P89" s="3">
+      <c r="P98" s="3">
         <f>'REALIZADO 2025'!N111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1546.6</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q98" s="3">
         <f>'REALIZADO 2025'!O111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="R89" s="4">
-        <f t="shared" ref="R89:R98" si="16">SUM(F89:Q89)</f>
+      <c r="R98" s="4">
+        <f>SUM(F98:Q98)</f>
         <v>8386.8251499999988</v>
       </c>
-      <c r="S89" s="25">
-        <f t="shared" si="11"/>
+      <c r="S98" s="25">
+        <f>R98/12</f>
         <v>698.90209583333319</v>
       </c>
-      <c r="T89" s="5"/>
-    </row>
-    <row r="90" spans="3:21" ht="12">
-      <c r="C90" s="79" t="s">
+      <c r="T98" s="5"/>
+    </row>
+    <row r="99" spans="3:20" ht="12">
+      <c r="C99" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="79"/>
-      <c r="E90" s="79"/>
-      <c r="F90" s="3">
+      <c r="D99" s="69"/>
+      <c r="E99" s="69"/>
+      <c r="F99" s="3">
         <f>'REALIZADO 2025'!D112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>169.6035</v>
       </c>
-      <c r="G90" s="3">
+      <c r="G99" s="3">
         <f>'REALIZADO 2025'!E112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>366.32474999999999</v>
       </c>
-      <c r="H90" s="3">
+      <c r="H99" s="3">
         <f>'REALIZADO 2025'!F112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>196.72125</v>
       </c>
-      <c r="I90" s="3">
+      <c r="I99" s="3">
         <f>'REALIZADO 2025'!G112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>169.6035</v>
       </c>
-      <c r="J90" s="3">
+      <c r="J99" s="3">
         <f>'REALIZADO 2025'!H112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>169.6035</v>
       </c>
-      <c r="K90" s="3">
+      <c r="K99" s="3">
         <f>'REALIZADO 2025'!I112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="L90" s="3">
+      <c r="L99" s="3">
         <f>'REALIZADO 2025'!J112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="M90" s="3">
+      <c r="M99" s="3">
         <f>'REALIZADO 2025'!K112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>182.56149999999997</v>
       </c>
-      <c r="N90" s="3">
+      <c r="N99" s="3">
         <f>'REALIZADO 2025'!L112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>196.251</v>
       </c>
-      <c r="O90" s="3">
+      <c r="O99" s="3">
         <f>'REALIZADO 2025'!M112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="P90" s="3">
+      <c r="P99" s="3">
         <f>'REALIZADO 2025'!N112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="Q90" s="3">
+      <c r="Q99" s="3">
         <f>'REALIZADO 2025'!O112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
       </c>
-      <c r="R90" s="4">
-        <f t="shared" si="16"/>
+      <c r="R99" s="4">
+        <f>SUM(F99:Q99)</f>
         <v>1450.6689999999999</v>
       </c>
-      <c r="S90" s="25">
-        <f t="shared" si="11"/>
+      <c r="S99" s="25">
+        <f>R99/12</f>
         <v>120.88908333333332</v>
       </c>
-      <c r="T90" s="5"/>
-    </row>
-    <row r="91" spans="3:21" ht="12">
-      <c r="C91" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="D91" s="79"/>
-      <c r="E91" s="79"/>
-      <c r="F91" s="3">
-        <f>'REALIZADO 2025'!D113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <f>'REALIZADO 2025'!E113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="H91" s="3">
-        <f>'REALIZADO 2025'!F113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="I91" s="3">
-        <f>'REALIZADO 2025'!G113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="J91" s="3">
-        <f>'REALIZADO 2025'!H113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="K91" s="3">
-        <f>'REALIZADO 2025'!I113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="L91" s="3">
-        <f>'REALIZADO 2025'!J113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="M91" s="3">
-        <f>'REALIZADO 2025'!K113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="N91" s="3">
-        <f>'REALIZADO 2025'!L113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="O91" s="3">
-        <f>'REALIZADO 2025'!M113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2439.7823999999996</v>
-      </c>
-      <c r="P91" s="3">
-        <f>'REALIZADO 2025'!N113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2649.4512</v>
-      </c>
-      <c r="Q91" s="3">
-        <f>'REALIZADO 2025'!O113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2649.4512</v>
-      </c>
-      <c r="R91" s="4">
-        <f t="shared" si="16"/>
-        <v>27256.943999999996</v>
-      </c>
-      <c r="S91" s="25">
-        <f t="shared" si="11"/>
-        <v>2271.4119999999998</v>
-      </c>
-      <c r="T91" s="5"/>
-    </row>
-    <row r="92" spans="3:21" ht="12">
-      <c r="C92" s="79" t="s">
-        <v>106</v>
-      </c>
-      <c r="D92" s="79"/>
-      <c r="E92" s="79"/>
-      <c r="F92" s="3">
-        <f>'REALIZADO 2025'!D114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>102.8489</v>
-      </c>
-      <c r="G92" s="3">
-        <f>'REALIZADO 2025'!E114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>105.09564999999999</v>
-      </c>
-      <c r="H92" s="3">
-        <f>'REALIZADO 2025'!F114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>104.92844999999998</v>
-      </c>
-      <c r="I92" s="3">
-        <f>'REALIZADO 2025'!G114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>104.92844999999998</v>
-      </c>
-      <c r="J92" s="3">
-        <f>'REALIZADO 2025'!H114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>102.8489</v>
-      </c>
-      <c r="K92" s="3">
-        <f>'REALIZADO 2025'!I114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="L92" s="3">
-        <f>'REALIZADO 2025'!J114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>102.8489</v>
-      </c>
-      <c r="M92" s="3">
-        <f>'REALIZADO 2025'!K114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>102.8489</v>
-      </c>
-      <c r="N92" s="3">
-        <f>'REALIZADO 2025'!L114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>102.8489</v>
-      </c>
-      <c r="O92" s="3">
-        <f>'REALIZADO 2025'!M114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>102.8489</v>
-      </c>
-      <c r="P92" s="3">
-        <f>'REALIZADO 2025'!N114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>102.8489</v>
-      </c>
-      <c r="Q92" s="3">
-        <f>'REALIZADO 2025'!O114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>92.273499999999984</v>
-      </c>
-      <c r="R92" s="4">
-        <f t="shared" si="16"/>
-        <v>1127.1683499999999</v>
-      </c>
-      <c r="S92" s="25">
-        <f t="shared" si="11"/>
-        <v>93.930695833333331</v>
-      </c>
-      <c r="T92" s="5"/>
-    </row>
-    <row r="93" spans="3:21" ht="12">
-      <c r="C93" s="79" t="s">
-        <v>107</v>
-      </c>
-      <c r="D93" s="79"/>
-      <c r="E93" s="79"/>
-      <c r="F93" s="3">
-        <f>'REALIZADO 2025'!D115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>208.98955000000001</v>
-      </c>
-      <c r="G93" s="3">
-        <f>'REALIZADO 2025'!E115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>594.66769999999985</v>
-      </c>
-      <c r="H93" s="3">
-        <f>'REALIZADO 2025'!F115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>188.39259999999999</v>
-      </c>
-      <c r="I93" s="3">
-        <f>'REALIZADO 2025'!G115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>619.47599999999989</v>
-      </c>
-      <c r="J93" s="3">
-        <f>'REALIZADO 2025'!H115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>411.88674999999995</v>
-      </c>
-      <c r="K93" s="3">
-        <f>'REALIZADO 2025'!I115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>197.48409999999998</v>
-      </c>
-      <c r="L93" s="3">
-        <f>'REALIZADO 2025'!J115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>312.36095</v>
-      </c>
-      <c r="M93" s="3">
-        <f>'REALIZADO 2025'!K115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="N93" s="3">
-        <f>'REALIZADO 2025'!L115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>208.98955000000001</v>
-      </c>
-      <c r="O93" s="3">
-        <f>'REALIZADO 2025'!M115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>197.72444999999999</v>
-      </c>
-      <c r="P93" s="3">
-        <f>'REALIZADO 2025'!N115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>441.06314999999995</v>
-      </c>
-      <c r="Q93" s="3">
-        <f>'REALIZADO 2025'!O115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>88.626449999999991</v>
-      </c>
-      <c r="R93" s="4">
-        <f t="shared" si="16"/>
-        <v>3469.6612500000001</v>
-      </c>
-      <c r="S93" s="25">
-        <f t="shared" si="11"/>
-        <v>289.13843750000001</v>
-      </c>
-      <c r="T93" s="5"/>
-    </row>
-    <row r="94" spans="3:21" ht="12">
-      <c r="C94" s="79" t="s">
-        <v>108</v>
-      </c>
-      <c r="D94" s="79"/>
-      <c r="E94" s="79"/>
-      <c r="F94" s="3">
-        <f>'REALIZADO 2025'!D116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <f>'REALIZADO 2025'!E116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>128.21105</v>
-      </c>
-      <c r="H94" s="3">
-        <f>'REALIZADO 2025'!F116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>256.4221</v>
-      </c>
-      <c r="I94" s="3">
-        <f>'REALIZADO 2025'!G116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>9.5408500000000007</v>
-      </c>
-      <c r="J94" s="3">
-        <f>'REALIZADO 2025'!H116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>128.21105</v>
-      </c>
-      <c r="K94" s="3">
-        <f>'REALIZADO 2025'!I116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>140.35395</v>
-      </c>
-      <c r="L94" s="3">
-        <f>'REALIZADO 2025'!J116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="M94" s="3">
-        <f>'REALIZADO 2025'!K116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>335.35095000000001</v>
-      </c>
-      <c r="N94" s="3">
-        <f>'REALIZADO 2025'!L116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>140.11359999999999</v>
-      </c>
-      <c r="O94" s="3">
-        <f>'REALIZADO 2025'!M116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>140.90779999999998</v>
-      </c>
-      <c r="P94" s="3">
-        <f>'REALIZADO 2025'!N116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>140.90779999999998</v>
-      </c>
-      <c r="Q94" s="3">
-        <f>'REALIZADO 2025'!O116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>140.90779999999998</v>
-      </c>
-      <c r="R94" s="4">
-        <f t="shared" si="16"/>
-        <v>1560.9269499999998</v>
-      </c>
-      <c r="S94" s="25">
-        <f t="shared" si="11"/>
-        <v>130.07724583333331</v>
-      </c>
-      <c r="T94" s="5"/>
-    </row>
-    <row r="95" spans="3:21" ht="12">
-      <c r="C95" s="79" t="s">
-        <v>109</v>
-      </c>
-      <c r="D95" s="79"/>
-      <c r="E95" s="79"/>
-      <c r="F95" s="3">
-        <f>'REALIZADO 2025'!D117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>101.25004999999999</v>
-      </c>
-      <c r="G95" s="3">
-        <f>'REALIZADO 2025'!E117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>101.25004999999999</v>
-      </c>
-      <c r="H95" s="3">
-        <f>'REALIZADO 2025'!F117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>101.25004999999999</v>
-      </c>
-      <c r="I95" s="3">
-        <f>'REALIZADO 2025'!G117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>101.25004999999999</v>
-      </c>
-      <c r="J95" s="3">
-        <f>'REALIZADO 2025'!H117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="K95" s="3">
-        <f>'REALIZADO 2025'!I117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>550.70454999999993</v>
-      </c>
-      <c r="L95" s="3">
-        <f>'REALIZADO 2025'!J117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>137.75189999999998</v>
-      </c>
-      <c r="M95" s="3">
-        <f>'REALIZADO 2025'!K117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>352.46805000000001</v>
-      </c>
-      <c r="N95" s="3">
-        <f>'REALIZADO 2025'!L117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>97.007349999999988</v>
-      </c>
-      <c r="O95" s="3">
-        <f>'REALIZADO 2025'!M117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>310.67849999999999</v>
-      </c>
-      <c r="P95" s="3">
-        <f>'REALIZADO 2025'!N117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>208.98955000000001</v>
-      </c>
-      <c r="Q95" s="3">
-        <f>'REALIZADO 2025'!O117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>308.93334999999996</v>
-      </c>
-      <c r="R95" s="4">
-        <f t="shared" si="16"/>
-        <v>2371.5334499999994</v>
-      </c>
-      <c r="S95" s="25">
-        <f t="shared" si="11"/>
-        <v>197.62778749999995</v>
-      </c>
-      <c r="T95" s="5"/>
-    </row>
-    <row r="96" spans="3:21" ht="12">
-      <c r="C96" s="79" t="s">
-        <v>110</v>
-      </c>
-      <c r="D96" s="79"/>
-      <c r="E96" s="79"/>
-      <c r="F96" s="3">
-        <f>'REALIZADO 2025'!D118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="G96" s="3">
-        <f>'REALIZADO 2025'!E118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="H96" s="3">
-        <f>'REALIZADO 2025'!F118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="I96" s="3">
-        <f>'REALIZADO 2025'!G118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="J96" s="3">
-        <f>'REALIZADO 2025'!H118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="K96" s="3">
-        <f>'REALIZADO 2025'!I118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <f>'REALIZADO 2025'!J118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="M96" s="3">
-        <f>'REALIZADO 2025'!K118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="N96" s="3">
-        <f>'REALIZADO 2025'!L118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="O96" s="3">
-        <f>'REALIZADO 2025'!M118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="P96" s="3">
-        <f>'REALIZADO 2025'!N118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="Q96" s="3">
-        <f>'REALIZADO 2025'!O118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>36.470499999999994</v>
-      </c>
-      <c r="R96" s="4">
-        <f t="shared" si="16"/>
-        <v>401.1755</v>
-      </c>
-      <c r="S96" s="25">
-        <f t="shared" si="11"/>
-        <v>33.431291666666667</v>
-      </c>
-      <c r="T96" s="5"/>
-    </row>
-    <row r="97" spans="3:20" ht="12">
-      <c r="C97" s="79" t="s">
-        <v>111</v>
-      </c>
-      <c r="D97" s="79"/>
-      <c r="E97" s="79"/>
-      <c r="F97" s="3">
-        <f>'REALIZADO 2025'!D119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>762.84999999999991</v>
-      </c>
-      <c r="G97" s="3">
-        <f>'REALIZADO 2025'!E119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="H97" s="3">
-        <f>'REALIZADO 2025'!F119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="I97" s="3">
-        <f>'REALIZADO 2025'!G119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>893.47499999999991</v>
-      </c>
-      <c r="J97" s="3">
-        <f>'REALIZADO 2025'!H119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="3">
-        <f>'REALIZADO 2025'!I119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="L97" s="3">
-        <f>'REALIZADO 2025'!J119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="M97" s="3">
-        <f>'REALIZADO 2025'!K119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>893.47499999999991</v>
-      </c>
-      <c r="N97" s="3">
-        <f>'REALIZADO 2025'!L119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="O97" s="3">
-        <f>'REALIZADO 2025'!M119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="P97" s="3">
-        <f>'REALIZADO 2025'!N119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>893.47499999999991</v>
-      </c>
-      <c r="Q97" s="3">
-        <f>'REALIZADO 2025'!O119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>0</v>
-      </c>
-      <c r="R97" s="4">
-        <f t="shared" si="16"/>
-        <v>3443.2749999999996</v>
-      </c>
-      <c r="S97" s="25">
-        <f t="shared" si="11"/>
-        <v>286.9395833333333</v>
-      </c>
-      <c r="T97" s="5"/>
-    </row>
-    <row r="98" spans="3:20" ht="12">
-      <c r="C98" s="79" t="s">
-        <v>112</v>
-      </c>
-      <c r="D98" s="79"/>
-      <c r="E98" s="79"/>
-      <c r="F98" s="3">
-        <f>'REALIZADO 2025'!D120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>1512.3239999999998</v>
-      </c>
-      <c r="G98" s="3">
-        <f>'REALIZADO 2025'!E120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2808.11355</v>
-      </c>
-      <c r="H98" s="3">
-        <f>'REALIZADO 2025'!F120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2170.7262499999997</v>
-      </c>
-      <c r="I98" s="3">
-        <f>'REALIZADO 2025'!G120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2910.8370499999996</v>
-      </c>
-      <c r="J98" s="3">
-        <f>'REALIZADO 2025'!H120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2188.1673000000001</v>
-      </c>
-      <c r="K98" s="3">
-        <f>'REALIZADO 2025'!I120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>1592.8099</v>
-      </c>
-      <c r="L98" s="3">
-        <f>'REALIZADO 2025'!J120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>1730.23785</v>
-      </c>
-      <c r="M98" s="3">
-        <f>'REALIZADO 2025'!K120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>1249.6632499999998</v>
-      </c>
-      <c r="N98" s="3">
-        <f>'REALIZADO 2025'!L120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>1607.1263999999999</v>
-      </c>
-      <c r="O98" s="3">
-        <f>'REALIZADO 2025'!M120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>1652.6674999999998</v>
-      </c>
-      <c r="P98" s="3">
-        <f>'REALIZADO 2025'!N120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2478.6459499999996</v>
-      </c>
-      <c r="Q98" s="3">
-        <f>'REALIZADO 2025'!O120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
-        <v>2191.3022999999998</v>
-      </c>
-      <c r="R98" s="4">
-        <f t="shared" si="16"/>
-        <v>24092.621299999995</v>
-      </c>
-      <c r="S98" s="25">
-        <f t="shared" si="11"/>
-        <v>2007.7184416666662</v>
-      </c>
-      <c r="T98" s="5"/>
-    </row>
-    <row r="99" spans="3:20" ht="12">
-      <c r="C99" s="84" t="s">
+      <c r="T99" s="5"/>
+    </row>
+    <row r="101" spans="3:20" ht="12">
+      <c r="C101" s="70" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="84"/>
-      <c r="E99" s="84"/>
-      <c r="F99" s="60" t="e">
+      <c r="D101" s="70"/>
+      <c r="E101" s="70"/>
+      <c r="F101" s="60" t="e">
         <f>F4</f>
         <v>#REF!</v>
       </c>
-      <c r="G99" s="60" t="e">
-        <f t="shared" ref="G99:Q99" si="17">G4</f>
+      <c r="G101" s="60" t="e">
+        <f t="shared" ref="G101:Q101" si="16">G4</f>
         <v>#REF!</v>
       </c>
-      <c r="H99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="H101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="I99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="I101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="J99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="J101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="K99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="K101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="L99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="L101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="M99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="M101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="N99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="N101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="O99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="O101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="P99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="P101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="Q99" s="60" t="e">
-        <f t="shared" si="17"/>
+      <c r="Q101" s="60" t="e">
+        <f t="shared" si="16"/>
         <v>#REF!</v>
       </c>
-      <c r="R99" s="61">
+      <c r="R101" s="61">
         <f>R86+R78+R38+R22+R5</f>
         <v>3409357.7379999999</v>
       </c>
-      <c r="S99" s="61">
-        <f>R99/12</f>
+      <c r="S101" s="61">
+        <f>R101/12</f>
         <v>284113.14483333332</v>
       </c>
-      <c r="T99" s="62"/>
-    </row>
-    <row r="100" spans="3:20" ht="12">
-      <c r="C100" s="62"/>
-      <c r="D100" s="62"/>
-      <c r="E100" s="62"/>
-      <c r="F100" s="62"/>
-      <c r="G100" s="62"/>
-      <c r="H100" s="62"/>
-      <c r="I100" s="62"/>
-      <c r="J100" s="62"/>
-      <c r="K100" s="62"/>
-      <c r="L100" s="62"/>
-      <c r="M100" s="62"/>
-      <c r="N100" s="62"/>
-      <c r="O100" s="62"/>
-      <c r="P100" s="62"/>
-      <c r="Q100" s="62"/>
-      <c r="R100" s="62"/>
-      <c r="S100" s="62"/>
-      <c r="T100" s="32"/>
-    </row>
-    <row r="101" spans="3:20" ht="14.4">
-      <c r="C101" s="74" t="s">
+      <c r="T101" s="62"/>
+    </row>
+    <row r="102" spans="3:20" ht="12">
+      <c r="C102" s="62"/>
+      <c r="D102" s="62"/>
+      <c r="E102" s="62"/>
+      <c r="F102" s="62"/>
+      <c r="G102" s="62"/>
+      <c r="H102" s="62"/>
+      <c r="I102" s="62"/>
+      <c r="J102" s="62"/>
+      <c r="K102" s="62"/>
+      <c r="L102" s="62"/>
+      <c r="M102" s="62"/>
+      <c r="N102" s="62"/>
+      <c r="O102" s="62"/>
+      <c r="P102" s="62"/>
+      <c r="Q102" s="62"/>
+      <c r="R102" s="62"/>
+      <c r="S102" s="62"/>
+      <c r="T102" s="32"/>
+    </row>
+    <row r="103" spans="3:20" ht="14.4">
+      <c r="C103" s="71" t="s">
         <v>114</v>
       </c>
-      <c r="D101" s="74"/>
-      <c r="E101" s="64">
+      <c r="D103" s="71"/>
+      <c r="E103" s="64">
         <v>270297.34000000003</v>
       </c>
     </row>
-    <row r="102" spans="3:20" ht="14.4">
-      <c r="C102" s="73" t="s">
+    <row r="104" spans="3:20" ht="14.4">
+      <c r="C104" s="72" t="s">
         <v>115</v>
       </c>
-      <c r="D102" s="73"/>
-      <c r="E102" s="65">
-        <f>S99</f>
+      <c r="D104" s="72"/>
+      <c r="E104" s="65">
+        <f>S101</f>
         <v>284113.14483333332</v>
       </c>
-      <c r="F102" s="59"/>
-    </row>
-    <row r="103" spans="3:20" ht="14.4">
-      <c r="C103" s="75" t="s">
+      <c r="F104" s="59"/>
+    </row>
+    <row r="105" spans="3:20" ht="14.4">
+      <c r="C105" s="73" t="s">
         <v>116</v>
       </c>
-      <c r="D103" s="75"/>
-      <c r="E103" s="66">
-        <f>E102-E101</f>
+      <c r="D105" s="73"/>
+      <c r="E105" s="66">
+        <f>E104-E103</f>
         <v>13815.804833333299</v>
       </c>
-      <c r="F103" s="59"/>
-    </row>
-    <row r="104" spans="3:20" ht="14.4">
-      <c r="C104" s="76" t="s">
+      <c r="F105" s="59"/>
+    </row>
+    <row r="106" spans="3:20" ht="14.4">
+      <c r="C106" s="68" t="s">
         <v>117</v>
       </c>
-      <c r="D104" s="76"/>
-      <c r="E104" s="67">
-        <f>E103/E101</f>
+      <c r="D106" s="68"/>
+      <c r="E106" s="67">
+        <f>E105/E103</f>
         <v>5.1113358471575408E-2</v>
       </c>
-      <c r="F104" s="59"/>
-    </row>
-    <row r="105" spans="3:20" ht="12">
-      <c r="C105" s="59"/>
-      <c r="D105" s="59"/>
-      <c r="E105" s="59"/>
-    </row>
-    <row r="106" spans="3:20" ht="12"/>
-    <row r="107" spans="3:20" ht="12"/>
+      <c r="F106" s="59"/>
+    </row>
+    <row r="107" spans="3:20" ht="12">
+      <c r="C107" s="59"/>
+      <c r="D107" s="59"/>
+      <c r="E107" s="59"/>
+    </row>
     <row r="108" spans="3:20" ht="12"/>
     <row r="109" spans="3:20" ht="12"/>
     <row r="110" spans="3:20" ht="12"/>
@@ -21456,33 +21454,76 @@
     <row r="133" ht="12"/>
     <row r="134" ht="12"/>
     <row r="135" ht="12"/>
+    <row r="136" ht="12"/>
+    <row r="137" ht="12"/>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C1:S1"/>
+    <mergeCell ref="C2:S2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
     <mergeCell ref="C73:E73"/>
     <mergeCell ref="C74:E74"/>
     <mergeCell ref="C75:E75"/>
@@ -21495,72 +21536,31 @@
     <mergeCell ref="C70:E70"/>
     <mergeCell ref="C71:E71"/>
     <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C1:S1"/>
-    <mergeCell ref="C2:S2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -21589,11 +21589,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
       <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
@@ -21639,11 +21639,11 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:18" ht="12">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="90"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="87"/>
       <c r="D2" s="33">
         <f>SUM(D3:D24)</f>
         <v>290185.64999999997</v>
@@ -21703,11 +21703,11 @@
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:18" ht="12">
-      <c r="A3" s="86" t="s">
+      <c r="A3" s="85" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="35">
         <v>239580.04</v>
       </c>
@@ -21755,11 +21755,11 @@
       <c r="R3" s="32"/>
     </row>
     <row r="4" spans="1:18" ht="12">
-      <c r="A4" s="87" t="s">
+      <c r="A4" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="87"/>
-      <c r="C4" s="87"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
       <c r="D4" s="38">
         <v>8221.9500000000007</v>
       </c>
@@ -21807,11 +21807,11 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:18" ht="12">
-      <c r="A5" s="86" t="s">
+      <c r="A5" s="85" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
       <c r="D5" s="35">
         <v>0</v>
       </c>
@@ -21859,11 +21859,11 @@
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:18" ht="12">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="86" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
+      <c r="B6" s="86"/>
+      <c r="C6" s="86"/>
       <c r="D6" s="38">
         <v>0</v>
       </c>
@@ -21911,11 +21911,11 @@
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:18" ht="12">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="85" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
       <c r="D7" s="35">
         <v>0</v>
       </c>
@@ -21963,11 +21963,11 @@
       <c r="R7" s="32"/>
     </row>
     <row r="8" spans="1:18" ht="12">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="38">
         <v>525</v>
       </c>
@@ -22015,11 +22015,11 @@
       <c r="R8" s="32"/>
     </row>
     <row r="9" spans="1:18" ht="12">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="85" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="35">
         <v>1260</v>
       </c>
@@ -22067,11 +22067,11 @@
       <c r="R9" s="32"/>
     </row>
     <row r="10" spans="1:18" ht="12">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="86" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="38">
         <v>1706.95</v>
       </c>
@@ -22119,11 +22119,11 @@
       <c r="R10" s="32"/>
     </row>
     <row r="11" spans="1:18" ht="12">
-      <c r="A11" s="86" t="s">
+      <c r="A11" s="85" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="86"/>
-      <c r="C11" s="86"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="35">
         <v>23926.35</v>
       </c>
@@ -22171,11 +22171,11 @@
       <c r="R11" s="32"/>
     </row>
     <row r="12" spans="1:18" ht="12">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="86" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="87"/>
-      <c r="C12" s="87"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="38">
         <v>150</v>
       </c>
@@ -22223,11 +22223,11 @@
       <c r="R12" s="32"/>
     </row>
     <row r="13" spans="1:18" ht="12">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="85" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="85"/>
       <c r="D13" s="35">
         <v>0</v>
       </c>
@@ -22275,11 +22275,11 @@
       <c r="R13" s="32"/>
     </row>
     <row r="14" spans="1:18" ht="12">
-      <c r="A14" s="87" t="s">
+      <c r="A14" s="86" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="87"/>
-      <c r="C14" s="87"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
       <c r="D14" s="38">
         <v>317.67</v>
       </c>
@@ -22327,11 +22327,11 @@
       <c r="R14" s="32"/>
     </row>
     <row r="15" spans="1:18" ht="12">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="85" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="86"/>
-      <c r="C15" s="86"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="85"/>
       <c r="D15" s="35">
         <v>1730</v>
       </c>
@@ -22379,11 +22379,11 @@
       <c r="R15" s="32"/>
     </row>
     <row r="16" spans="1:18" ht="12">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="87"/>
-      <c r="C16" s="87"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="86"/>
       <c r="D16" s="38">
         <v>8050.48</v>
       </c>
@@ -22431,11 +22431,11 @@
       <c r="R16" s="32"/>
     </row>
     <row r="17" spans="1:20" ht="12">
-      <c r="A17" s="86" t="s">
+      <c r="A17" s="85" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="35">
         <v>50.02</v>
       </c>
@@ -22483,11 +22483,11 @@
       <c r="R17" s="32"/>
     </row>
     <row r="18" spans="1:20" ht="12">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="86" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
       <c r="D18" s="38">
         <v>500</v>
       </c>
@@ -22535,11 +22535,11 @@
       <c r="R18" s="32"/>
     </row>
     <row r="19" spans="1:20" ht="12">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="85" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="86"/>
-      <c r="C19" s="86"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="35">
         <v>0</v>
       </c>
@@ -22587,11 +22587,11 @@
       <c r="R19" s="32"/>
     </row>
     <row r="20" spans="1:20" ht="12">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
       <c r="D20" s="38">
         <v>2450.54</v>
       </c>
@@ -22639,11 +22639,11 @@
       <c r="R20" s="32"/>
     </row>
     <row r="21" spans="1:20" ht="12">
-      <c r="A21" s="86" t="s">
+      <c r="A21" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
       <c r="D21" s="35">
         <v>754.13</v>
       </c>
@@ -22691,11 +22691,11 @@
       <c r="R21" s="32"/>
     </row>
     <row r="22" spans="1:20" ht="12">
-      <c r="A22" s="87" t="s">
+      <c r="A22" s="86" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="87"/>
-      <c r="C22" s="87"/>
+      <c r="B22" s="86"/>
+      <c r="C22" s="86"/>
       <c r="D22" s="38">
         <v>797.85</v>
       </c>
@@ -22743,11 +22743,11 @@
       <c r="R22" s="32"/>
     </row>
     <row r="23" spans="1:20" ht="12">
-      <c r="A23" s="86" t="s">
+      <c r="A23" s="85" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="86"/>
-      <c r="C23" s="86"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
       <c r="D23" s="35">
         <v>0</v>
       </c>
@@ -22795,11 +22795,11 @@
       <c r="R23" s="32"/>
     </row>
     <row r="24" spans="1:20" ht="12">
-      <c r="A24" s="87" t="s">
+      <c r="A24" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="87"/>
+      <c r="B24" s="86"/>
+      <c r="C24" s="86"/>
       <c r="D24" s="38">
         <v>164.67</v>
       </c>
@@ -22847,11 +22847,11 @@
       <c r="R24" s="32"/>
     </row>
     <row r="25" spans="1:20" ht="12">
-      <c r="A25" s="85" t="s">
+      <c r="A25" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="85"/>
-      <c r="C25" s="85"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="39">
         <f>D2</f>
         <v>290185.64999999997</v>
@@ -22931,11 +22931,11 @@
       <c r="R26" s="32"/>
     </row>
     <row r="27" spans="1:20" ht="12">
-      <c r="A27" s="77" t="s">
+      <c r="A27" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
+      <c r="B27" s="84"/>
+      <c r="C27" s="84"/>
       <c r="D27" s="23">
         <f t="shared" ref="D27:O27" si="4">D28+D45+D61+D102+D110+D123</f>
         <v>302630.67195000005</v>
@@ -23003,11 +23003,11 @@
       </c>
     </row>
     <row r="28" spans="1:20" ht="12">
-      <c r="A28" s="78" t="s">
+      <c r="A28" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="78"/>
-      <c r="C28" s="78"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="74"/>
       <c r="D28" s="8">
         <f>SUM(D29:D44)</f>
         <v>9137.3607499999998</v>
@@ -23067,11 +23067,11 @@
       <c r="R28" s="32"/>
     </row>
     <row r="29" spans="1:20" ht="12">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="69" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
       <c r="D29" s="3">
         <v>34</v>
       </c>
@@ -23128,11 +23128,11 @@
       <c r="R29" s="5"/>
     </row>
     <row r="30" spans="1:20" ht="12">
-      <c r="A30" s="79" t="s">
+      <c r="A30" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="79"/>
-      <c r="C30" s="79"/>
+      <c r="B30" s="69"/>
+      <c r="C30" s="69"/>
       <c r="D30" s="3">
         <f>'REALIZADO 2025'!D29*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23192,11 +23192,11 @@
       <c r="R30" s="5"/>
     </row>
     <row r="31" spans="1:20" ht="12">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
       <c r="D31" s="3">
         <f>'REALIZADO 2025'!D30*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23256,11 +23256,11 @@
       <c r="R31" s="5"/>
     </row>
     <row r="32" spans="1:20" ht="12">
-      <c r="A32" s="79" t="s">
+      <c r="A32" s="69" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="69"/>
       <c r="D32" s="3">
         <f>'REALIZADO 2025'!D31*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23320,11 +23320,11 @@
       <c r="R32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="12">
-      <c r="A33" s="79" t="s">
+      <c r="A33" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="79"/>
-      <c r="C33" s="79"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="69"/>
       <c r="D33" s="3">
         <f>'REALIZADO 2025'!D34*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23384,11 +23384,11 @@
       <c r="R33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="12">
-      <c r="A34" s="79" t="s">
+      <c r="A34" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="79"/>
-      <c r="C34" s="79"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
       <c r="D34" s="3">
         <f>'REALIZADO 2025'!D35*'PREVISTO 2026'!$S$27</f>
         <v>372.17674999999997</v>
@@ -23448,11 +23448,11 @@
       <c r="R34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="12">
-      <c r="A35" s="79" t="s">
+      <c r="A35" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="79"/>
-      <c r="C35" s="79"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="69"/>
       <c r="D35" s="3">
         <f>'REALIZADO 2025'!D36*'PREVISTO 2026'!$S$27</f>
         <v>522.5</v>
@@ -23512,11 +23512,11 @@
       <c r="R35" s="5"/>
     </row>
     <row r="36" spans="1:21" ht="12">
-      <c r="A36" s="79" t="s">
+      <c r="A36" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="79"/>
-      <c r="C36" s="79"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
       <c r="D36" s="3">
         <f>'REALIZADO 2025'!D37*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23576,11 +23576,11 @@
       <c r="R36" s="5"/>
     </row>
     <row r="37" spans="1:21" ht="12">
-      <c r="A37" s="79" t="s">
+      <c r="A37" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
       <c r="D37" s="3">
         <f>5043.17*$S$27</f>
         <v>5270.11265</v>
@@ -23640,11 +23640,11 @@
       <c r="R37" s="5"/>
     </row>
     <row r="38" spans="1:21" ht="12">
-      <c r="A38" s="79" t="s">
+      <c r="A38" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="69"/>
       <c r="D38" s="3">
         <f>2570.4*$S$27</f>
         <v>2686.0679999999998</v>
@@ -23704,11 +23704,11 @@
       <c r="R38" s="5"/>
     </row>
     <row r="39" spans="1:21" ht="12">
-      <c r="A39" s="79" t="s">
+      <c r="A39" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="79"/>
-      <c r="C39" s="79"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="69"/>
       <c r="D39" s="3">
         <f>'REALIZADO 2025'!D40*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23768,11 +23768,11 @@
       <c r="R39" s="5"/>
     </row>
     <row r="40" spans="1:21" ht="12">
-      <c r="A40" s="79" t="s">
+      <c r="A40" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="79"/>
-      <c r="C40" s="79"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
       <c r="D40" s="3">
         <f>'REALIZADO 2025'!D41*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23832,11 +23832,11 @@
       <c r="R40" s="5"/>
     </row>
     <row r="41" spans="1:21" ht="12">
-      <c r="A41" s="79" t="s">
+      <c r="A41" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="79"/>
-      <c r="C41" s="79"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
       <c r="D41" s="3">
         <f>'REALIZADO 2025'!D42*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23896,11 +23896,11 @@
       <c r="R41" s="5"/>
     </row>
     <row r="42" spans="1:21" ht="12">
-      <c r="A42" s="79" t="s">
+      <c r="A42" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="79"/>
-      <c r="C42" s="79"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
       <c r="D42" s="3">
         <f>'REALIZADO 2025'!D43*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23960,11 +23960,11 @@
       <c r="R42" s="5"/>
     </row>
     <row r="43" spans="1:21" ht="12">
-      <c r="A43" s="79" t="s">
+      <c r="A43" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="B43" s="79"/>
-      <c r="C43" s="79"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
       <c r="D43" s="3">
         <f>'REALIZADO 2025'!D44*'PREVISTO 2026'!$S$27</f>
         <v>252.50334999999998</v>
@@ -24024,11 +24024,11 @@
       <c r="R43" s="5"/>
     </row>
     <row r="44" spans="1:21" ht="12">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="79"/>
-      <c r="C44" s="79"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
       <c r="D44" s="3">
         <f>'REALIZADO 2025'!D45*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -24088,11 +24088,11 @@
       <c r="R44" s="5"/>
     </row>
     <row r="45" spans="1:21" ht="12">
-      <c r="A45" s="80" t="s">
+      <c r="A45" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="80"/>
-      <c r="C45" s="80"/>
+      <c r="B45" s="78"/>
+      <c r="C45" s="78"/>
       <c r="D45" s="7">
         <f>SUM(D46:D60)</f>
         <v>154479.97080000001</v>
@@ -24160,11 +24160,11 @@
       </c>
     </row>
     <row r="46" spans="1:21" ht="12">
-      <c r="A46" s="79" t="s">
+      <c r="A46" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="79"/>
-      <c r="C46" s="79"/>
+      <c r="B46" s="69"/>
+      <c r="C46" s="69"/>
       <c r="D46" s="3">
         <f>'REALIZADO 2025'!D47*'PREVISTO 2026'!$S$45</f>
         <v>52560.36</v>
@@ -24224,11 +24224,11 @@
       <c r="R46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="12">
-      <c r="A47" s="79" t="s">
+      <c r="A47" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="79"/>
-      <c r="C47" s="79"/>
+      <c r="B47" s="69"/>
+      <c r="C47" s="69"/>
       <c r="D47" s="3">
         <f>'REALIZADO 2025'!D48*'PREVISTO 2026'!$S$45</f>
         <v>23252.497200000002</v>
@@ -24292,11 +24292,11 @@
       </c>
     </row>
     <row r="48" spans="1:21" ht="12">
-      <c r="A48" s="79" t="s">
+      <c r="A48" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="79"/>
-      <c r="C48" s="79"/>
+      <c r="B48" s="69"/>
+      <c r="C48" s="69"/>
       <c r="D48" s="3">
         <f>'REALIZADO 2025'!D49*'PREVISTO 2026'!$S$45</f>
         <v>77.652000000000015</v>
@@ -24355,11 +24355,11 @@
       <c r="R48" s="5"/>
     </row>
     <row r="49" spans="1:24" ht="12">
-      <c r="A49" s="79" t="s">
+      <c r="A49" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="79"/>
-      <c r="C49" s="79"/>
+      <c r="B49" s="69"/>
+      <c r="C49" s="69"/>
       <c r="D49" s="3">
         <f>'REALIZADO 2025'!D50*'PREVISTO 2026'!$S$45</f>
         <v>266.14440000000002</v>
@@ -24419,11 +24419,11 @@
       <c r="R49" s="5"/>
     </row>
     <row r="50" spans="1:24" ht="12">
-      <c r="A50" s="79" t="s">
+      <c r="A50" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="79"/>
-      <c r="C50" s="79"/>
+      <c r="B50" s="69"/>
+      <c r="C50" s="69"/>
       <c r="D50" s="3">
         <f>'REALIZADO 2025'!D51*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -24483,11 +24483,11 @@
       <c r="R50" s="5"/>
     </row>
     <row r="51" spans="1:24" ht="12">
-      <c r="A51" s="79" t="s">
+      <c r="A51" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="79"/>
-      <c r="C51" s="79"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="69"/>
       <c r="D51" s="3">
         <f>'REALIZADO 2025'!D52*'PREVISTO 2026'!$S$45</f>
         <v>3033.6120000000001</v>
@@ -24547,11 +24547,11 @@
       <c r="R51" s="5"/>
     </row>
     <row r="52" spans="1:24" ht="12">
-      <c r="A52" s="79" t="s">
+      <c r="A52" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="79"/>
-      <c r="C52" s="79"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="69"/>
       <c r="D52" s="3">
         <f>'REALIZADO 2025'!D53*'PREVISTO 2026'!$S$45</f>
         <v>319.59360000000004</v>
@@ -24611,11 +24611,11 @@
       <c r="R52" s="5"/>
     </row>
     <row r="53" spans="1:24" ht="12">
-      <c r="A53" s="79" t="s">
+      <c r="A53" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="79"/>
-      <c r="C53" s="79"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="69"/>
       <c r="D53" s="3">
         <f>'REALIZADO 2025'!D54*'PREVISTO 2026'!$S$45</f>
         <v>324</v>
@@ -24675,11 +24675,11 @@
       <c r="R53" s="5"/>
     </row>
     <row r="54" spans="1:24" ht="12">
-      <c r="A54" s="79" t="s">
+      <c r="A54" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="79"/>
-      <c r="C54" s="79"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="69"/>
       <c r="D54" s="3">
         <f>'REALIZADO 2025'!D55*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -24739,11 +24739,11 @@
       <c r="R54" s="5"/>
     </row>
     <row r="55" spans="1:24" ht="12">
-      <c r="A55" s="79" t="s">
+      <c r="A55" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="79"/>
-      <c r="C55" s="79"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="69"/>
       <c r="D55" s="3">
         <f>'REALIZADO 2025'!D57*'PREVISTO 2026'!$S$45</f>
         <v>26005.406400000003</v>
@@ -24803,11 +24803,11 @@
       <c r="R55" s="5"/>
     </row>
     <row r="56" spans="1:24" ht="12">
-      <c r="A56" s="79" t="s">
+      <c r="A56" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="79"/>
-      <c r="C56" s="79"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
       <c r="D56" s="3">
         <f>'REALIZADO 2025'!D58*'PREVISTO 2026'!$S$45</f>
         <v>5940.0108000000009</v>
@@ -24867,11 +24867,11 @@
       <c r="R56" s="5"/>
     </row>
     <row r="57" spans="1:24" ht="12">
-      <c r="A57" s="79" t="s">
+      <c r="A57" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="79"/>
-      <c r="C57" s="79"/>
+      <c r="B57" s="69"/>
+      <c r="C57" s="69"/>
       <c r="D57" s="3">
         <f>'REALIZADO 2025'!D59*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -24931,11 +24931,11 @@
       <c r="R57" s="5"/>
     </row>
     <row r="58" spans="1:24" ht="12">
-      <c r="A58" s="79" t="s">
+      <c r="A58" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="B58" s="79"/>
-      <c r="C58" s="79"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="69"/>
       <c r="D58" s="3">
         <f>'REALIZADO 2025'!D60*'PREVISTO 2026'!$S$45</f>
         <v>41884.214400000004</v>
@@ -24995,11 +24995,11 @@
       <c r="R58" s="5"/>
     </row>
     <row r="59" spans="1:24" ht="12">
-      <c r="A59" s="79" t="s">
+      <c r="A59" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="79"/>
-      <c r="C59" s="79"/>
+      <c r="B59" s="69"/>
+      <c r="C59" s="69"/>
       <c r="D59" s="3">
         <f>'REALIZADO 2025'!D61*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -25058,11 +25058,11 @@
       <c r="R59" s="5"/>
     </row>
     <row r="60" spans="1:24" ht="12">
-      <c r="A60" s="79" t="s">
+      <c r="A60" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="79"/>
-      <c r="C60" s="79"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="69"/>
       <c r="D60" s="3">
         <f>'REALIZADO 2025'!D62*'PREVISTO 2026'!$S$45</f>
         <v>816.48</v>
@@ -25122,11 +25122,11 @@
       <c r="R60" s="5"/>
     </row>
     <row r="61" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
+      <c r="B61" s="78"/>
+      <c r="C61" s="78"/>
       <c r="D61" s="7">
         <f>D62+D79+D92+D96</f>
         <v>49045.706050000001</v>
@@ -25192,17 +25192,17 @@
       <c r="T61" s="17">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="U61" s="80"/>
-      <c r="V61" s="80"/>
-      <c r="W61" s="80"/>
+      <c r="U61" s="78"/>
+      <c r="V61" s="78"/>
+      <c r="W61" s="78"/>
       <c r="X61" s="7"/>
     </row>
     <row r="62" spans="1:24" ht="12" customHeight="1">
-      <c r="A62" s="78" t="s">
+      <c r="A62" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B62" s="78"/>
-      <c r="C62" s="78"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="74"/>
       <c r="D62" s="8">
         <f>SUM(D63:D72)</f>
         <v>11923.41865</v>
@@ -25263,11 +25263,11 @@
       <c r="T62" s="58"/>
     </row>
     <row r="63" spans="1:24" ht="12">
-      <c r="A63" s="79" t="s">
+      <c r="A63" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="79"/>
-      <c r="C63" s="79"/>
+      <c r="B63" s="69"/>
+      <c r="C63" s="69"/>
       <c r="D63" s="3">
         <f>'REALIZADO 2025'!D65*'PREVISTO 2026'!$S$61</f>
         <v>1550.68595</v>
@@ -25333,11 +25333,11 @@
       </c>
     </row>
     <row r="64" spans="1:24" ht="12">
-      <c r="A64" s="88" t="s">
+      <c r="A64" s="91" t="s">
         <v>147</v>
       </c>
-      <c r="B64" s="88"/>
-      <c r="C64" s="88"/>
+      <c r="B64" s="91"/>
+      <c r="C64" s="91"/>
       <c r="D64" s="56">
         <f>'REALIZADO 2025'!D66*'PREVISTO 2026'!$S$61</f>
         <v>150.42774999999997</v>
@@ -25401,11 +25401,11 @@
       </c>
     </row>
     <row r="65" spans="1:22" ht="12">
-      <c r="A65" s="79" t="s">
+      <c r="A65" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="79"/>
-      <c r="C65" s="79"/>
+      <c r="B65" s="69"/>
+      <c r="C65" s="69"/>
       <c r="D65" s="3">
         <f>'REALIZADO 2025'!D67*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -25472,11 +25472,11 @@
       </c>
     </row>
     <row r="66" spans="1:22" ht="12">
-      <c r="A66" s="79" t="s">
+      <c r="A66" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="B66" s="79"/>
-      <c r="C66" s="79"/>
+      <c r="B66" s="69"/>
+      <c r="C66" s="69"/>
       <c r="D66" s="3">
         <f>'REALIZADO 2025'!D68*'PREVISTO 2026'!$S$61</f>
         <v>3193.8857499999995</v>
@@ -25542,11 +25542,11 @@
       </c>
     </row>
     <row r="67" spans="1:22" ht="12">
-      <c r="A67" s="79" t="s">
+      <c r="A67" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="B67" s="79"/>
-      <c r="C67" s="79"/>
+      <c r="B67" s="69"/>
+      <c r="C67" s="69"/>
       <c r="D67" s="3">
         <f>'REALIZADO 2025'!D69*'PREVISTO 2026'!$S$61</f>
         <v>610.80250000000001</v>
@@ -25608,11 +25608,11 @@
       </c>
     </row>
     <row r="68" spans="1:22" ht="12">
-      <c r="A68" s="79" t="s">
+      <c r="A68" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="B68" s="79"/>
-      <c r="C68" s="79"/>
+      <c r="B68" s="69"/>
+      <c r="C68" s="69"/>
       <c r="D68" s="3">
         <f>'REALIZADO 2025'!D70*'PREVISTO 2026'!$S$61</f>
         <v>554.51879999999994</v>
@@ -25675,11 +25675,11 @@
       </c>
     </row>
     <row r="69" spans="1:22" ht="12">
-      <c r="A69" s="79" t="s">
+      <c r="A69" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="79"/>
-      <c r="C69" s="79"/>
+      <c r="B69" s="69"/>
+      <c r="C69" s="69"/>
       <c r="D69" s="3">
         <f>'REALIZADO 2025'!D71*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -25742,11 +25742,11 @@
       </c>
     </row>
     <row r="70" spans="1:22" ht="12">
-      <c r="A70" s="79" t="s">
+      <c r="A70" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="79"/>
-      <c r="C70" s="79"/>
+      <c r="B70" s="69"/>
+      <c r="C70" s="69"/>
       <c r="D70" s="3">
         <f>'REALIZADO 2025'!D72*'PREVISTO 2026'!$S$61</f>
         <v>5500.8486499999999</v>
@@ -25808,11 +25808,11 @@
       </c>
     </row>
     <row r="71" spans="1:22" ht="12">
-      <c r="A71" s="88" t="s">
+      <c r="A71" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="88"/>
-      <c r="C71" s="88"/>
+      <c r="B71" s="91"/>
+      <c r="C71" s="91"/>
       <c r="D71" s="3">
         <f>'REALIZADO 2025'!D73*'PREVISTO 2026'!$S$61</f>
         <v>349.70924999999994</v>
@@ -25874,11 +25874,11 @@
       </c>
     </row>
     <row r="72" spans="1:22" ht="12">
-      <c r="A72" s="79" t="s">
+      <c r="A72" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="B72" s="79"/>
-      <c r="C72" s="79"/>
+      <c r="B72" s="69"/>
+      <c r="C72" s="69"/>
       <c r="D72" s="3">
         <f>'REALIZADO 2025'!D74*'PREVISTO 2026'!$S$61</f>
         <v>12.54</v>
@@ -25941,7 +25941,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" ht="12">
-      <c r="A73" s="79" t="s">
+      <c r="A73" s="69" t="s">
         <v>170</v>
       </c>
       <c r="B73" s="92"/>
@@ -25972,7 +25972,7 @@
       </c>
     </row>
     <row r="74" spans="1:22" ht="12">
-      <c r="A74" s="79" t="s">
+      <c r="A74" s="69" t="s">
         <v>171</v>
       </c>
       <c r="B74" s="92"/>
@@ -25999,7 +25999,7 @@
       <c r="R74" s="5"/>
     </row>
     <row r="75" spans="1:22" ht="12">
-      <c r="A75" s="79" t="s">
+      <c r="A75" s="69" t="s">
         <v>172</v>
       </c>
       <c r="B75" s="92"/>
@@ -26026,7 +26026,7 @@
       <c r="R75" s="5"/>
     </row>
     <row r="76" spans="1:22" ht="12">
-      <c r="A76" s="79" t="s">
+      <c r="A76" s="69" t="s">
         <v>173</v>
       </c>
       <c r="B76" s="92"/>
@@ -26053,7 +26053,7 @@
       <c r="R76" s="5"/>
     </row>
     <row r="77" spans="1:22" ht="12">
-      <c r="A77" s="79" t="s">
+      <c r="A77" s="69" t="s">
         <v>174</v>
       </c>
       <c r="B77" s="92"/>
@@ -26080,11 +26080,11 @@
       <c r="R77" s="5"/>
     </row>
     <row r="78" spans="1:22" ht="12">
-      <c r="A78" s="79" t="s">
+      <c r="A78" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="B78" s="79"/>
-      <c r="C78" s="79"/>
+      <c r="B78" s="69"/>
+      <c r="C78" s="69"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -26107,11 +26107,11 @@
       <c r="R78" s="5"/>
     </row>
     <row r="79" spans="1:22" ht="12" customHeight="1">
-      <c r="A79" s="78" t="s">
+      <c r="A79" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="B79" s="78"/>
-      <c r="C79" s="78"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="74"/>
       <c r="D79" s="8">
         <f>SUM(D80:D91)</f>
         <v>13069.940399999999</v>
@@ -26171,11 +26171,11 @@
       <c r="R79" s="5"/>
     </row>
     <row r="80" spans="1:22" ht="12">
-      <c r="A80" s="79" t="s">
+      <c r="A80" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="B80" s="79"/>
-      <c r="C80" s="79"/>
+      <c r="B80" s="69"/>
+      <c r="C80" s="69"/>
       <c r="D80" s="3">
         <f>'REALIZADO 2025'!D76*'PREVISTO 2026'!$S$61</f>
         <v>1201.7082</v>
@@ -26235,11 +26235,11 @@
       <c r="R80" s="5"/>
     </row>
     <row r="81" spans="1:18" ht="12">
-      <c r="A81" s="79" t="s">
+      <c r="A81" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="B81" s="79"/>
-      <c r="C81" s="79"/>
+      <c r="B81" s="69"/>
+      <c r="C81" s="69"/>
       <c r="D81" s="3">
         <f>'REALIZADO 2025'!D77*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26299,11 +26299,11 @@
       <c r="R81" s="5"/>
     </row>
     <row r="82" spans="1:18" ht="12">
-      <c r="A82" s="79" t="s">
+      <c r="A82" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="B82" s="79"/>
-      <c r="C82" s="79"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="69"/>
       <c r="D82" s="3">
         <f>'REALIZADO 2025'!D78*'PREVISTO 2026'!$S$61</f>
         <v>888.24999999999989</v>
@@ -26363,11 +26363,11 @@
       <c r="R82" s="5"/>
     </row>
     <row r="83" spans="1:18" ht="12">
-      <c r="A83" s="79" t="s">
+      <c r="A83" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="B83" s="79"/>
-      <c r="C83" s="79"/>
+      <c r="B83" s="69"/>
+      <c r="C83" s="69"/>
       <c r="D83" s="3">
         <f>'REALIZADO 2025'!D79*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26427,11 +26427,11 @@
       <c r="R83" s="5"/>
     </row>
     <row r="84" spans="1:18" ht="12">
-      <c r="A84" s="79" t="s">
+      <c r="A84" s="69" t="s">
         <v>74</v>
       </c>
-      <c r="B84" s="79"/>
-      <c r="C84" s="79"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="69"/>
       <c r="D84" s="3">
         <f>'REALIZADO 2025'!D80*'PREVISTO 2026'!$S$61</f>
         <v>2080.5113999999999</v>
@@ -26490,11 +26490,11 @@
       <c r="R84" s="5"/>
     </row>
     <row r="85" spans="1:18" ht="12">
-      <c r="A85" s="79" t="s">
+      <c r="A85" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="79"/>
+      <c r="B85" s="69"/>
+      <c r="C85" s="69"/>
       <c r="D85" s="3">
         <f>'REALIZADO 2025'!D81*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26554,11 +26554,11 @@
       <c r="R85" s="5"/>
     </row>
     <row r="86" spans="1:18" ht="12">
-      <c r="A86" s="79" t="s">
+      <c r="A86" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="79"/>
+      <c r="B86" s="69"/>
+      <c r="C86" s="69"/>
       <c r="D86" s="3">
         <f>'REALIZADO 2025'!D82*'PREVISTO 2026'!$S$61</f>
         <v>7691.6597999999994</v>
@@ -26618,11 +26618,11 @@
       <c r="R86" s="5"/>
     </row>
     <row r="87" spans="1:18" ht="12">
-      <c r="A87" s="79" t="s">
+      <c r="A87" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="B87" s="79"/>
-      <c r="C87" s="79"/>
+      <c r="B87" s="69"/>
+      <c r="C87" s="69"/>
       <c r="D87" s="3">
         <f>'REALIZADO 2025'!D83*'PREVISTO 2026'!$S$61</f>
         <v>1149.5</v>
@@ -26681,11 +26681,11 @@
       <c r="R87" s="5"/>
     </row>
     <row r="88" spans="1:18" ht="12">
-      <c r="A88" s="79" t="s">
+      <c r="A88" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="B88" s="79"/>
-      <c r="C88" s="79"/>
+      <c r="B88" s="69"/>
+      <c r="C88" s="69"/>
       <c r="D88" s="3">
         <f>'REALIZADO 2025'!D84*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26745,11 +26745,11 @@
       <c r="R88" s="5"/>
     </row>
     <row r="89" spans="1:18" ht="12">
-      <c r="A89" s="79" t="s">
+      <c r="A89" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="B89" s="79"/>
-      <c r="C89" s="79"/>
+      <c r="B89" s="69"/>
+      <c r="C89" s="69"/>
       <c r="D89" s="3">
         <f>'REALIZADO 2025'!D85*'PREVISTO 2026'!$S$61</f>
         <v>58.310999999999993</v>
@@ -26809,11 +26809,11 @@
       <c r="R89" s="5"/>
     </row>
     <row r="90" spans="1:18" ht="12">
-      <c r="A90" s="79" t="s">
+      <c r="A90" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="B90" s="79"/>
-      <c r="C90" s="79"/>
+      <c r="B90" s="69"/>
+      <c r="C90" s="69"/>
       <c r="D90" s="3">
         <f>'REALIZADO 2025'!D86*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26873,11 +26873,11 @@
       <c r="R90" s="5"/>
     </row>
     <row r="91" spans="1:18" ht="12">
-      <c r="A91" s="79" t="s">
+      <c r="A91" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="B91" s="79"/>
-      <c r="C91" s="79"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="69"/>
       <c r="D91" s="3">
         <f>'REALIZADO 2025'!D87*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26937,11 +26937,11 @@
       <c r="R91" s="5"/>
     </row>
     <row r="92" spans="1:18" ht="12">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="B92" s="78"/>
-      <c r="C92" s="78"/>
+      <c r="B92" s="74"/>
+      <c r="C92" s="74"/>
       <c r="D92" s="8">
         <f>SUM(D93:D95)</f>
         <v>16132.187499999998</v>
@@ -27001,11 +27001,11 @@
       <c r="R92" s="5"/>
     </row>
     <row r="93" spans="1:18" ht="12">
-      <c r="A93" s="79" t="s">
+      <c r="A93" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="79"/>
-      <c r="C93" s="79"/>
+      <c r="B93" s="69"/>
+      <c r="C93" s="69"/>
       <c r="D93" s="3">
         <f>'REALIZADO 2025'!D89*'PREVISTO 2026'!$S$61</f>
         <v>6040.6224999999995</v>
@@ -27065,11 +27065,11 @@
       <c r="R93" s="5"/>
     </row>
     <row r="94" spans="1:18" ht="12">
-      <c r="A94" s="79" t="s">
+      <c r="A94" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="B94" s="79"/>
-      <c r="C94" s="79"/>
+      <c r="B94" s="69"/>
+      <c r="C94" s="69"/>
       <c r="D94" s="3">
         <f>'REALIZADO 2025'!D90*'PREVISTO 2026'!$S$61</f>
         <v>7357.8449999999993</v>
@@ -27128,11 +27128,11 @@
       <c r="R94" s="5"/>
     </row>
     <row r="95" spans="1:18" ht="12">
-      <c r="A95" s="79" t="s">
+      <c r="A95" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="B95" s="79"/>
-      <c r="C95" s="79"/>
+      <c r="B95" s="69"/>
+      <c r="C95" s="69"/>
       <c r="D95" s="3">
         <f>'REALIZADO 2025'!D91*'PREVISTO 2026'!$S$61</f>
         <v>2733.72</v>
@@ -27192,11 +27192,11 @@
       <c r="R95" s="5"/>
     </row>
     <row r="96" spans="1:18" ht="12">
-      <c r="A96" s="78" t="s">
+      <c r="A96" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="B96" s="78"/>
-      <c r="C96" s="78"/>
+      <c r="B96" s="74"/>
+      <c r="C96" s="74"/>
       <c r="D96" s="8">
         <f>SUM(D97:D101)</f>
         <v>7920.1594999999998</v>
@@ -27256,11 +27256,11 @@
       <c r="R96" s="5"/>
     </row>
     <row r="97" spans="1:19" ht="12">
-      <c r="A97" s="79" t="s">
+      <c r="A97" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="B97" s="79"/>
-      <c r="C97" s="79"/>
+      <c r="B97" s="69"/>
+      <c r="C97" s="69"/>
       <c r="D97" s="3">
         <f>'REALIZADO 2025'!D93*'PREVISTO 2026'!$S$61</f>
         <v>909.15</v>
@@ -27320,11 +27320,11 @@
       <c r="R97" s="5"/>
     </row>
     <row r="98" spans="1:19" ht="12">
-      <c r="A98" s="79" t="s">
+      <c r="A98" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="B98" s="79"/>
-      <c r="C98" s="79"/>
+      <c r="B98" s="69"/>
+      <c r="C98" s="69"/>
       <c r="D98" s="3">
         <f>'REALIZADO 2025'!D94*'PREVISTO 2026'!$S$61</f>
         <v>752.4</v>
@@ -27384,11 +27384,11 @@
       <c r="R98" s="5"/>
     </row>
     <row r="99" spans="1:19" ht="12">
-      <c r="A99" s="79" t="s">
+      <c r="A99" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="B99" s="79"/>
-      <c r="C99" s="79"/>
+      <c r="B99" s="69"/>
+      <c r="C99" s="69"/>
       <c r="D99" s="3">
         <f>'REALIZADO 2025'!D95*'PREVISTO 2026'!$S$61</f>
         <v>2403.5</v>
@@ -27448,11 +27448,11 @@
       <c r="R99" s="5"/>
     </row>
     <row r="100" spans="1:19" ht="12">
-      <c r="A100" s="79" t="s">
+      <c r="A100" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="B100" s="79"/>
-      <c r="C100" s="79"/>
+      <c r="B100" s="69"/>
+      <c r="C100" s="69"/>
       <c r="D100" s="3">
         <f>'REALIZADO 2025'!D96*'PREVISTO 2026'!$S$61</f>
         <v>1472.5094999999999</v>
@@ -27511,11 +27511,11 @@
       <c r="R100" s="5"/>
     </row>
     <row r="101" spans="1:19" ht="12">
-      <c r="A101" s="79" t="s">
+      <c r="A101" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="B101" s="79"/>
-      <c r="C101" s="79"/>
+      <c r="B101" s="69"/>
+      <c r="C101" s="69"/>
       <c r="D101" s="3">
         <f>'REALIZADO 2025'!D97*'PREVISTO 2026'!$S$61</f>
         <v>2382.6</v>
@@ -27575,11 +27575,11 @@
       <c r="R101" s="5"/>
     </row>
     <row r="102" spans="1:19" ht="12">
-      <c r="A102" s="78" t="s">
+      <c r="A102" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="B102" s="78"/>
-      <c r="C102" s="78"/>
+      <c r="B102" s="74"/>
+      <c r="C102" s="74"/>
       <c r="D102" s="8">
         <f t="shared" ref="D102:P102" si="17">SUM(D103:D109)</f>
         <v>74062.399949999992</v>
@@ -27644,11 +27644,11 @@
       </c>
     </row>
     <row r="103" spans="1:19" ht="12">
-      <c r="A103" s="79" t="s">
+      <c r="A103" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="B103" s="79"/>
-      <c r="C103" s="79"/>
+      <c r="B103" s="69"/>
+      <c r="C103" s="69"/>
       <c r="D103" s="3">
         <f>'REALIZADO 2025'!D99*'PREVISTO 2026'!$S$102</f>
         <v>4117.2999999999993</v>
@@ -27708,11 +27708,11 @@
       <c r="R103" s="5"/>
     </row>
     <row r="104" spans="1:19" ht="12">
-      <c r="A104" s="79" t="s">
+      <c r="A104" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="B104" s="79"/>
-      <c r="C104" s="79"/>
+      <c r="B104" s="69"/>
+      <c r="C104" s="69"/>
       <c r="D104" s="3">
         <f>'REALIZADO 2025'!D100*'PREVISTO 2026'!$S$102</f>
         <v>2951.08</v>
@@ -27772,11 +27772,11 @@
       <c r="R104" s="5"/>
     </row>
     <row r="105" spans="1:19" ht="12">
-      <c r="A105" s="79" t="s">
+      <c r="A105" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="B105" s="79"/>
-      <c r="C105" s="79"/>
+      <c r="B105" s="69"/>
+      <c r="C105" s="69"/>
       <c r="D105" s="3">
         <f>'REALIZADO 2025'!D101*'PREVISTO 2026'!$S$102</f>
         <v>4270.2671</v>
@@ -27836,11 +27836,11 @@
       <c r="R105" s="5"/>
     </row>
     <row r="106" spans="1:19" ht="12">
-      <c r="A106" s="79" t="s">
+      <c r="A106" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="B106" s="79"/>
-      <c r="C106" s="79"/>
+      <c r="B106" s="69"/>
+      <c r="C106" s="69"/>
       <c r="D106" s="3">
         <f>'REALIZADO 2025'!D102*'PREVISTO 2026'!$S$102</f>
         <v>58965.410349999998</v>
@@ -27900,11 +27900,11 @@
       <c r="R106" s="5"/>
     </row>
     <row r="107" spans="1:19" ht="12">
-      <c r="A107" s="79" t="s">
+      <c r="A107" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="B107" s="79"/>
-      <c r="C107" s="79"/>
+      <c r="B107" s="69"/>
+      <c r="C107" s="69"/>
       <c r="D107" s="3">
         <f>'REALIZADO 2025'!D103*'PREVISTO 2026'!$S$102</f>
         <v>0</v>
@@ -27964,11 +27964,11 @@
       <c r="R107" s="5"/>
     </row>
     <row r="108" spans="1:19" ht="12">
-      <c r="A108" s="79" t="s">
+      <c r="A108" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="B108" s="79"/>
-      <c r="C108" s="79"/>
+      <c r="B108" s="69"/>
+      <c r="C108" s="69"/>
       <c r="D108" s="3">
         <f>'REALIZADO 2025'!D104*'PREVISTO 2026'!$S$102</f>
         <v>2508</v>
@@ -28028,11 +28028,11 @@
       <c r="R108" s="5"/>
     </row>
     <row r="109" spans="1:19" ht="12">
-      <c r="A109" s="79" t="s">
+      <c r="A109" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="B109" s="79"/>
-      <c r="C109" s="79"/>
+      <c r="B109" s="69"/>
+      <c r="C109" s="69"/>
       <c r="D109" s="3">
         <f>'REALIZADO 2025'!D106*'PREVISTO 2026'!$S$102</f>
         <v>1250.3425</v>
@@ -28092,11 +28092,11 @@
       <c r="R109" s="5"/>
     </row>
     <row r="110" spans="1:19" ht="12">
-      <c r="A110" s="78" t="s">
+      <c r="A110" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="B110" s="78"/>
-      <c r="C110" s="78"/>
+      <c r="B110" s="74"/>
+      <c r="C110" s="74"/>
       <c r="D110" s="8">
         <f>SUM(D111:D122)</f>
         <v>15905.234399999999</v>
@@ -28161,11 +28161,11 @@
       </c>
     </row>
     <row r="111" spans="1:19" ht="12">
-      <c r="A111" s="79" t="s">
+      <c r="A111" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="B111" s="79"/>
-      <c r="C111" s="79"/>
+      <c r="B111" s="69"/>
+      <c r="C111" s="69"/>
       <c r="D111" s="3">
         <f>'REALIZADO 2025'!D109*'PREVISTO 2026'!$S$110</f>
         <v>11147.161299999998</v>
@@ -28224,11 +28224,11 @@
       <c r="R111" s="5"/>
     </row>
     <row r="112" spans="1:19" ht="12">
-      <c r="A112" s="79" t="s">
+      <c r="A112" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="B112" s="79"/>
-      <c r="C112" s="79"/>
+      <c r="B112" s="69"/>
+      <c r="C112" s="69"/>
       <c r="D112" s="3">
         <f>'REALIZADO 2025'!D110*'PREVISTO 2026'!$S$110</f>
         <v>1863.7366</v>
@@ -28287,11 +28287,11 @@
       <c r="R112" s="5"/>
     </row>
     <row r="113" spans="1:19" ht="12">
-      <c r="A113" s="79" t="s">
+      <c r="A113" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="B113" s="79"/>
-      <c r="C113" s="79"/>
+      <c r="B113" s="69"/>
+      <c r="C113" s="69"/>
       <c r="D113" s="3">
         <f>'REALIZADO 2025'!D111*'PREVISTO 2026'!$S$110</f>
         <v>0</v>
@@ -28351,11 +28351,11 @@
       <c r="R113" s="5"/>
     </row>
     <row r="114" spans="1:19" ht="12">
-      <c r="A114" s="79" t="s">
+      <c r="A114" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="B114" s="79"/>
-      <c r="C114" s="79"/>
+      <c r="B114" s="69"/>
+      <c r="C114" s="69"/>
       <c r="D114" s="3">
         <f>'REALIZADO 2025'!D112*'PREVISTO 2026'!$S$110</f>
         <v>169.6035</v>
@@ -28415,11 +28415,11 @@
       <c r="R114" s="5"/>
     </row>
     <row r="115" spans="1:19" ht="12">
-      <c r="A115" s="79" t="s">
+      <c r="A115" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="B115" s="79"/>
-      <c r="C115" s="79"/>
+      <c r="B115" s="69"/>
+      <c r="C115" s="69"/>
       <c r="D115" s="3">
         <f>'REALIZADO 2025'!D113*'PREVISTO 2026'!$S$110</f>
         <v>0</v>
@@ -28479,11 +28479,11 @@
       <c r="R115" s="5"/>
     </row>
     <row r="116" spans="1:19" ht="12">
-      <c r="A116" s="79" t="s">
+      <c r="A116" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="B116" s="79"/>
-      <c r="C116" s="79"/>
+      <c r="B116" s="69"/>
+      <c r="C116" s="69"/>
       <c r="D116" s="3">
         <f>'REALIZADO 2025'!D114*'PREVISTO 2026'!$S$110</f>
         <v>102.8489</v>
@@ -28543,11 +28543,11 @@
       <c r="R116" s="5"/>
     </row>
     <row r="117" spans="1:19" ht="12">
-      <c r="A117" s="79" t="s">
+      <c r="A117" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="B117" s="79"/>
-      <c r="C117" s="79"/>
+      <c r="B117" s="69"/>
+      <c r="C117" s="69"/>
       <c r="D117" s="3">
         <f>'REALIZADO 2025'!D115*'PREVISTO 2026'!$S$110</f>
         <v>208.98955000000001</v>
@@ -28607,11 +28607,11 @@
       <c r="R117" s="5"/>
     </row>
     <row r="118" spans="1:19" ht="12">
-      <c r="A118" s="79" t="s">
+      <c r="A118" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="79"/>
-      <c r="C118" s="79"/>
+      <c r="B118" s="69"/>
+      <c r="C118" s="69"/>
       <c r="D118" s="3">
         <f>'REALIZADO 2025'!D116*'PREVISTO 2026'!$S$110</f>
         <v>0</v>
@@ -28671,11 +28671,11 @@
       <c r="R118" s="5"/>
     </row>
     <row r="119" spans="1:19" ht="12">
-      <c r="A119" s="79" t="s">
+      <c r="A119" s="69" t="s">
         <v>109</v>
       </c>
-      <c r="B119" s="79"/>
-      <c r="C119" s="79"/>
+      <c r="B119" s="69"/>
+      <c r="C119" s="69"/>
       <c r="D119" s="3">
         <f>'REALIZADO 2025'!D117*'PREVISTO 2026'!$S$110</f>
         <v>101.25004999999999</v>
@@ -28735,11 +28735,11 @@
       <c r="R119" s="5"/>
     </row>
     <row r="120" spans="1:19" ht="12">
-      <c r="A120" s="79" t="s">
+      <c r="A120" s="69" t="s">
         <v>110</v>
       </c>
-      <c r="B120" s="79"/>
-      <c r="C120" s="79"/>
+      <c r="B120" s="69"/>
+      <c r="C120" s="69"/>
       <c r="D120" s="3">
         <f>'REALIZADO 2025'!D118*'PREVISTO 2026'!$S$110</f>
         <v>36.470499999999994</v>
@@ -28799,11 +28799,11 @@
       <c r="R120" s="5"/>
     </row>
     <row r="121" spans="1:19" ht="12">
-      <c r="A121" s="79" t="s">
+      <c r="A121" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="B121" s="79"/>
-      <c r="C121" s="79"/>
+      <c r="B121" s="69"/>
+      <c r="C121" s="69"/>
       <c r="D121" s="3">
         <f>'REALIZADO 2025'!D119*'PREVISTO 2026'!$S$110</f>
         <v>762.84999999999991</v>
@@ -28863,11 +28863,11 @@
       <c r="R121" s="5"/>
     </row>
     <row r="122" spans="1:19" ht="12">
-      <c r="A122" s="79" t="s">
+      <c r="A122" s="69" t="s">
         <v>112</v>
       </c>
-      <c r="B122" s="79"/>
-      <c r="C122" s="79"/>
+      <c r="B122" s="69"/>
+      <c r="C122" s="69"/>
       <c r="D122" s="3">
         <f>'REALIZADO 2025'!D120*'PREVISTO 2026'!$S$110</f>
         <v>1512.3239999999998</v>
@@ -28927,7 +28927,7 @@
       <c r="R122" s="5"/>
     </row>
     <row r="123" spans="1:19" ht="12" customHeight="1">
-      <c r="A123" s="78" t="s">
+      <c r="A123" s="74" t="s">
         <v>151</v>
       </c>
       <c r="B123" s="93"/>
@@ -28992,7 +28992,7 @@
       <c r="S123" s="14"/>
     </row>
     <row r="124" spans="1:19" ht="12" customHeight="1">
-      <c r="A124" s="79" t="s">
+      <c r="A124" s="69" t="s">
         <v>152</v>
       </c>
       <c r="B124" s="92"/>
@@ -29020,7 +29020,7 @@
       <c r="R124" s="5"/>
     </row>
     <row r="125" spans="1:19" ht="12" customHeight="1">
-      <c r="A125" s="79" t="s">
+      <c r="A125" s="69" t="s">
         <v>153</v>
       </c>
       <c r="B125" s="92"/>
@@ -29048,7 +29048,7 @@
       <c r="R125" s="5"/>
     </row>
     <row r="126" spans="1:19" ht="12" customHeight="1">
-      <c r="A126" s="79" t="s">
+      <c r="A126" s="69" t="s">
         <v>154</v>
       </c>
       <c r="B126" s="92"/>
@@ -29076,7 +29076,7 @@
       <c r="R126" s="5"/>
     </row>
     <row r="127" spans="1:19" ht="12" customHeight="1">
-      <c r="A127" s="79" t="s">
+      <c r="A127" s="69" t="s">
         <v>155</v>
       </c>
       <c r="B127" s="92"/>
@@ -29104,7 +29104,7 @@
       <c r="R127" s="5"/>
     </row>
     <row r="128" spans="1:19" ht="12" customHeight="1">
-      <c r="A128" s="79" t="s">
+      <c r="A128" s="69" t="s">
         <v>156</v>
       </c>
       <c r="B128" s="92"/>
@@ -29132,7 +29132,7 @@
       <c r="R128" s="5"/>
     </row>
     <row r="129" spans="1:18" ht="12" customHeight="1">
-      <c r="A129" s="79" t="s">
+      <c r="A129" s="69" t="s">
         <v>157</v>
       </c>
       <c r="B129" s="92"/>
@@ -29160,7 +29160,7 @@
       <c r="R129" s="5"/>
     </row>
     <row r="130" spans="1:18" ht="12" customHeight="1">
-      <c r="A130" s="79" t="s">
+      <c r="A130" s="69" t="s">
         <v>158</v>
       </c>
       <c r="B130" s="92"/>
@@ -29188,7 +29188,7 @@
       <c r="R130" s="5"/>
     </row>
     <row r="131" spans="1:18" ht="12" customHeight="1">
-      <c r="A131" s="79" t="s">
+      <c r="A131" s="69" t="s">
         <v>159</v>
       </c>
       <c r="B131" s="92"/>
@@ -29216,7 +29216,7 @@
       <c r="R131" s="5"/>
     </row>
     <row r="132" spans="1:18" ht="12" customHeight="1">
-      <c r="A132" s="79" t="s">
+      <c r="A132" s="69" t="s">
         <v>160</v>
       </c>
       <c r="B132" s="92"/>
@@ -29244,7 +29244,7 @@
       <c r="R132" s="5"/>
     </row>
     <row r="133" spans="1:18" ht="12" customHeight="1">
-      <c r="A133" s="79" t="s">
+      <c r="A133" s="69" t="s">
         <v>161</v>
       </c>
       <c r="B133" s="92"/>
@@ -29272,7 +29272,7 @@
       <c r="R133" s="5"/>
     </row>
     <row r="134" spans="1:18" ht="12" customHeight="1">
-      <c r="A134" s="79" t="s">
+      <c r="A134" s="69" t="s">
         <v>162</v>
       </c>
       <c r="B134" s="92"/>
@@ -29300,7 +29300,7 @@
       <c r="R134" s="5"/>
     </row>
     <row r="135" spans="1:18" ht="12" customHeight="1">
-      <c r="A135" s="79" t="s">
+      <c r="A135" s="69" t="s">
         <v>163</v>
       </c>
       <c r="B135" s="92"/>
@@ -29328,7 +29328,7 @@
       <c r="R135" s="5"/>
     </row>
     <row r="136" spans="1:18" ht="12" customHeight="1">
-      <c r="A136" s="79" t="s">
+      <c r="A136" s="69" t="s">
         <v>164</v>
       </c>
       <c r="B136" s="92"/>
@@ -29356,7 +29356,7 @@
       <c r="R136" s="5"/>
     </row>
     <row r="137" spans="1:18" ht="12" customHeight="1">
-      <c r="A137" s="79" t="s">
+      <c r="A137" s="69" t="s">
         <v>165</v>
       </c>
       <c r="B137" s="92"/>
@@ -29384,7 +29384,7 @@
       <c r="R137" s="5"/>
     </row>
     <row r="138" spans="1:18" ht="12" customHeight="1">
-      <c r="A138" s="79" t="s">
+      <c r="A138" s="69" t="s">
         <v>166</v>
       </c>
       <c r="B138" s="92"/>
@@ -29412,7 +29412,7 @@
       <c r="R138" s="5"/>
     </row>
     <row r="139" spans="1:18" ht="12" customHeight="1">
-      <c r="A139" s="79" t="s">
+      <c r="A139" s="69" t="s">
         <v>167</v>
       </c>
       <c r="B139" s="92"/>
@@ -29440,7 +29440,7 @@
       <c r="R139" s="5"/>
     </row>
     <row r="140" spans="1:18" ht="12" customHeight="1">
-      <c r="A140" s="79" t="s">
+      <c r="A140" s="69" t="s">
         <v>168</v>
       </c>
       <c r="B140" s="92"/>
@@ -29468,7 +29468,7 @@
       <c r="R140" s="5"/>
     </row>
     <row r="141" spans="1:18" ht="12" customHeight="1">
-      <c r="A141" s="79" t="s">
+      <c r="A141" s="69" t="s">
         <v>169</v>
       </c>
       <c r="B141" s="92"/>
@@ -29496,11 +29496,11 @@
       <c r="R141" s="5"/>
     </row>
     <row r="142" spans="1:18" ht="12">
-      <c r="A142" s="85" t="s">
+      <c r="A142" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="B142" s="85"/>
-      <c r="C142" s="85"/>
+      <c r="B142" s="90"/>
+      <c r="C142" s="90"/>
       <c r="D142" s="45">
         <f>D27</f>
         <v>302630.67195000005</v>
@@ -29652,124 +29652,6 @@
     <row r="183" ht="12"/>
   </sheetData>
   <mergeCells count="142">
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="U61:W61"/>
@@ -29794,6 +29676,124 @@
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -29801,14 +29801,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30007,21 +30005,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE76326-AFB3-4BAB-B4B8-730EA1F5C7CE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{541A0B4A-F190-4BD3-B675-9D0B56ED84AA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e"/>
-    <ds:schemaRef ds:uri="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -30046,9 +30043,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{541A0B4A-F190-4BD3-B675-9D0B56ED84AA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE76326-AFB3-4BAB-B4B8-730EA1F5C7CE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e"/>
+    <ds:schemaRef ds:uri="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Previsao Orcamentaria.xlsx
+++ b/Previsao Orcamentaria.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="518" documentId="11_A8DEA55DA9ACCEB6161F69D90F8A6D5701A14124" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8DA7EA-994A-42D6-9645-833B6A1F1DBC}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="11_A8DEA55DA9ACCEB6161F69D90F8A6D5701A14124" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B698F27-9F68-4F26-B9F3-71695FE83785}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -578,14 +578,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.00#"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00000_-;\-* #,##0.00000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -637,6 +638,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -807,10 +815,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -981,39 +990,6 @@
     <xf numFmtId="4" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1032,10 +1008,55 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1044,24 +1065,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1394,53 +1406,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
+      <c r="C1" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
     </row>
     <row r="3" spans="3:22" ht="16.5" customHeight="1">
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
       <c r="F3" s="31" t="s">
         <v>3</v>
       </c>
@@ -1486,11 +1498,11 @@
       <c r="T3" s="32"/>
     </row>
     <row r="4" spans="3:22" ht="12">
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="23" t="e">
         <f>F5+F22+F38+F78+F86+#REF!</f>
         <v>#REF!</v>
@@ -1615,11 +1627,11 @@
       </c>
     </row>
     <row r="6" spans="3:22" ht="12">
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
       <c r="F6" s="3">
         <v>34</v>
       </c>
@@ -1676,11 +1688,11 @@
       <c r="T6" s="5"/>
     </row>
     <row r="7" spans="3:22" ht="12">
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
       <c r="F7" s="3">
         <f>'REALIZADO 2025'!D29*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1740,11 +1752,11 @@
       <c r="T7" s="5"/>
     </row>
     <row r="8" spans="3:22" ht="12">
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
       <c r="F8" s="3">
         <f>'REALIZADO 2025'!D30*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1804,11 +1816,11 @@
       <c r="T8" s="5"/>
     </row>
     <row r="9" spans="3:22" ht="12">
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
       <c r="F9" s="3">
         <f>'REALIZADO 2025'!D31*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1868,11 +1880,11 @@
       <c r="T9" s="5"/>
     </row>
     <row r="10" spans="3:22" ht="12">
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
       <c r="F10" s="3">
         <f>'REALIZADO 2025'!D34*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -1932,11 +1944,11 @@
       <c r="T10" s="5"/>
     </row>
     <row r="11" spans="3:22" ht="12">
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
       <c r="F11" s="3">
         <f>'REALIZADO 2025'!D35*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>372.17674999999997</v>
@@ -1996,11 +2008,11 @@
       <c r="T11" s="5"/>
     </row>
     <row r="12" spans="3:22" ht="12">
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
       <c r="F12" s="3">
         <f>'REALIZADO 2025'!D36*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>522.5</v>
@@ -2060,11 +2072,11 @@
       <c r="T12" s="5"/>
     </row>
     <row r="13" spans="3:22" ht="12">
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
       <c r="F13" s="3">
         <f>'REALIZADO 2025'!D37*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2124,11 +2136,11 @@
       <c r="T13" s="5"/>
     </row>
     <row r="14" spans="3:22" ht="12">
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
       <c r="F14" s="3">
         <f t="shared" ref="F14:Q14" si="3">5043.17*$U$4</f>
         <v>5270.11265</v>
@@ -2188,11 +2200,11 @@
       <c r="T14" s="5"/>
     </row>
     <row r="15" spans="3:22" ht="12">
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
       <c r="F15" s="3">
         <f t="shared" ref="F15:Q15" si="4">2570.4*$U$4</f>
         <v>2686.0679999999998</v>
@@ -2252,11 +2264,11 @@
       <c r="T15" s="5"/>
     </row>
     <row r="16" spans="3:22" ht="12">
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
       <c r="F16" s="3">
         <f>'REALIZADO 2025'!D40*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2316,11 +2328,11 @@
       <c r="T16" s="5"/>
     </row>
     <row r="17" spans="3:22" ht="12">
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
       <c r="F17" s="3">
         <f>'REALIZADO 2025'!D41*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2380,11 +2392,11 @@
       <c r="T17" s="5"/>
     </row>
     <row r="18" spans="3:22" ht="12">
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
       <c r="F18" s="3">
         <f>'REALIZADO 2025'!D42*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2444,11 +2456,11 @@
       <c r="T18" s="5"/>
     </row>
     <row r="19" spans="3:22" ht="12">
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
       <c r="F19" s="3">
         <f>'REALIZADO 2025'!D43*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2508,11 +2520,11 @@
       <c r="T19" s="5"/>
     </row>
     <row r="20" spans="3:22" ht="12">
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
       <c r="F20" s="3">
         <f>'REALIZADO 2025'!D44*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>252.50334999999998</v>
@@ -2572,11 +2584,11 @@
       <c r="T20" s="5"/>
     </row>
     <row r="21" spans="3:22" ht="12">
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
       <c r="F21" s="3">
         <f>'REALIZADO 2025'!D45*'PREVISTO 2026 REVISADO'!$U$4</f>
         <v>0</v>
@@ -2636,11 +2648,11 @@
       <c r="T21" s="5"/>
     </row>
     <row r="22" spans="3:22" ht="12">
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
       <c r="F22" s="7">
         <f>SUM(F23:F37)</f>
         <v>154479.97080000001</v>
@@ -2708,11 +2720,11 @@
       </c>
     </row>
     <row r="23" spans="3:22" ht="12">
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
       <c r="F23" s="3">
         <f>'REALIZADO 2025'!D47*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>52560.36</v>
@@ -2772,11 +2784,11 @@
       <c r="T23" s="5"/>
     </row>
     <row r="24" spans="3:22" ht="12">
-      <c r="C24" s="69" t="s">
+      <c r="C24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
       <c r="F24" s="3">
         <f>'REALIZADO 2025'!D48*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>23252.497200000002</v>
@@ -2836,11 +2848,11 @@
       <c r="T24" s="5"/>
     </row>
     <row r="25" spans="3:22" ht="12">
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
       <c r="F25" s="3">
         <f>'REALIZADO 2025'!D49*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>77.652000000000015</v>
@@ -2899,11 +2911,11 @@
       <c r="T25" s="5"/>
     </row>
     <row r="26" spans="3:22" ht="12">
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
       <c r="F26" s="3">
         <f>'REALIZADO 2025'!D50*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>266.14440000000002</v>
@@ -2963,11 +2975,11 @@
       <c r="T26" s="5"/>
     </row>
     <row r="27" spans="3:22" ht="12">
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
       <c r="F27" s="3">
         <f>'REALIZADO 2025'!D51*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3027,11 +3039,11 @@
       <c r="T27" s="5"/>
     </row>
     <row r="28" spans="3:22" ht="12">
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
       <c r="F28" s="3">
         <f>'REALIZADO 2025'!D52*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>3033.6120000000001</v>
@@ -3091,11 +3103,11 @@
       <c r="T28" s="5"/>
     </row>
     <row r="29" spans="3:22" ht="12">
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
       <c r="F29" s="3">
         <f>'REALIZADO 2025'!D53*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>319.59360000000004</v>
@@ -3155,11 +3167,11 @@
       <c r="T29" s="5"/>
     </row>
     <row r="30" spans="3:22" ht="12">
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
       <c r="F30" s="3">
         <f>'REALIZADO 2025'!D54*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>324</v>
@@ -3219,11 +3231,11 @@
       <c r="T30" s="5"/>
     </row>
     <row r="31" spans="3:22" ht="12">
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
       <c r="F31" s="3">
         <f>'REALIZADO 2025'!D55*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3283,11 +3295,11 @@
       <c r="T31" s="5"/>
     </row>
     <row r="32" spans="3:22" ht="12">
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
       <c r="F32" s="3">
         <f>'REALIZADO 2025'!D57*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>26005.406400000003</v>
@@ -3347,11 +3359,11 @@
       <c r="T32" s="5"/>
     </row>
     <row r="33" spans="3:22" ht="12">
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
       <c r="F33" s="3">
         <f>'REALIZADO 2025'!D58*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>5940.0108000000009</v>
@@ -3411,11 +3423,11 @@
       <c r="T33" s="5"/>
     </row>
     <row r="34" spans="3:22" ht="12">
-      <c r="C34" s="69" t="s">
+      <c r="C34" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
       <c r="F34" s="3">
         <f>'REALIZADO 2025'!D59*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3475,11 +3487,11 @@
       <c r="T34" s="5"/>
     </row>
     <row r="35" spans="3:22" ht="12">
-      <c r="C35" s="69" t="s">
+      <c r="C35" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
       <c r="F35" s="3">
         <f>'REALIZADO 2025'!D60*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>41884.214400000004</v>
@@ -3539,11 +3551,11 @@
       <c r="T35" s="5"/>
     </row>
     <row r="36" spans="3:22" ht="12">
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
       <c r="F36" s="3">
         <f>'REALIZADO 2025'!D61*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>0</v>
@@ -3602,11 +3614,11 @@
       <c r="T36" s="5"/>
     </row>
     <row r="37" spans="3:22" ht="12">
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="75"/>
       <c r="F37" s="3">
         <f>'REALIZADO 2025'!D62*'PREVISTO 2026 REVISADO'!$U$22</f>
         <v>816.48</v>
@@ -3666,11 +3678,11 @@
       <c r="T37" s="5"/>
     </row>
     <row r="38" spans="3:22" ht="12.75" customHeight="1">
-      <c r="C38" s="78" t="s">
+      <c r="C38" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
       <c r="F38" s="7">
         <f t="shared" ref="F38:R38" si="7">F39+F55+F68+F72</f>
         <v>48895.278299999998</v>
@@ -3803,11 +3815,11 @@
       <c r="V39" s="58"/>
     </row>
     <row r="40" spans="3:22" ht="12">
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
+      <c r="D40" s="75"/>
+      <c r="E40" s="75"/>
       <c r="F40" s="3">
         <f>'REALIZADO 2025'!D65*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1550.68595</v>
@@ -3867,11 +3879,11 @@
       <c r="V40" s="58"/>
     </row>
     <row r="41" spans="3:22" ht="12">
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="75"/>
       <c r="F41" s="3">
         <f>'REALIZADO 2025'!D67*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -3932,11 +3944,11 @@
       <c r="V41" s="58"/>
     </row>
     <row r="42" spans="3:22" ht="12">
-      <c r="C42" s="69" t="s">
+      <c r="C42" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
       <c r="F42" s="3">
         <f>'REALIZADO 2025'!D68*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>3193.8857499999995</v>
@@ -3996,11 +4008,11 @@
       <c r="V42" s="58"/>
     </row>
     <row r="43" spans="3:22" ht="12">
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
       <c r="F43" s="3">
         <f>'REALIZADO 2025'!D69*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>610.80250000000001</v>
@@ -4059,11 +4071,11 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="3:22" ht="12">
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="75"/>
       <c r="F44" s="3">
         <f>'REALIZADO 2025'!D70*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>554.51879999999994</v>
@@ -4123,11 +4135,11 @@
       <c r="T44" s="5"/>
     </row>
     <row r="45" spans="3:22" ht="12">
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
+      <c r="D45" s="75"/>
+      <c r="E45" s="75"/>
       <c r="F45" s="3">
         <f>'REALIZADO 2025'!D71*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4187,11 +4199,11 @@
       <c r="T45" s="5"/>
     </row>
     <row r="46" spans="3:22" ht="12">
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="75"/>
       <c r="F46" s="3">
         <f>'REALIZADO 2025'!D72*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>5500.8486499999999</v>
@@ -4250,11 +4262,11 @@
       <c r="T46" s="5"/>
     </row>
     <row r="47" spans="3:22" ht="12">
-      <c r="C47" s="77" t="s">
+      <c r="C47" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
       <c r="F47" s="3">
         <f>'REALIZADO 2025'!D73*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>349.70924999999994</v>
@@ -4313,11 +4325,11 @@
       <c r="T47" s="5"/>
     </row>
     <row r="48" spans="3:22" ht="12">
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
       <c r="F48" s="3">
         <f>'REALIZADO 2025'!D74*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>12.54</v>
@@ -4377,11 +4389,11 @@
       <c r="T48" s="5"/>
     </row>
     <row r="49" spans="3:20" ht="12">
-      <c r="C49" s="75" t="s">
+      <c r="C49" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="78"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
@@ -4404,11 +4416,11 @@
       <c r="T49" s="5"/>
     </row>
     <row r="50" spans="3:20" ht="12">
-      <c r="C50" s="75" t="s">
+      <c r="C50" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
+      <c r="D50" s="78"/>
+      <c r="E50" s="78"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -4431,11 +4443,11 @@
       <c r="T50" s="5"/>
     </row>
     <row r="51" spans="3:20" ht="12">
-      <c r="C51" s="75" t="s">
+      <c r="C51" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
@@ -4458,11 +4470,11 @@
       <c r="T51" s="5"/>
     </row>
     <row r="52" spans="3:20" ht="12">
-      <c r="C52" s="75" t="s">
+      <c r="C52" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -4485,11 +4497,11 @@
       <c r="T52" s="5"/>
     </row>
     <row r="53" spans="3:20" ht="12">
-      <c r="C53" s="75" t="s">
+      <c r="C53" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="76"/>
-      <c r="E53" s="76"/>
+      <c r="D53" s="78"/>
+      <c r="E53" s="78"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -4512,11 +4524,11 @@
       <c r="T53" s="5"/>
     </row>
     <row r="54" spans="3:20" ht="12">
-      <c r="C54" s="75" t="s">
+      <c r="C54" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="75"/>
-      <c r="E54" s="75"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="77"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -4603,11 +4615,11 @@
       <c r="T55" s="5"/>
     </row>
     <row r="56" spans="3:20" ht="12">
-      <c r="C56" s="69" t="s">
+      <c r="C56" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="69"/>
-      <c r="E56" s="69"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
       <c r="F56" s="3">
         <f>'REALIZADO 2025'!D76*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1201.7082</v>
@@ -4667,11 +4679,11 @@
       <c r="T56" s="5"/>
     </row>
     <row r="57" spans="3:20" ht="12">
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="D57" s="69"/>
-      <c r="E57" s="69"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
       <c r="F57" s="3">
         <f>'REALIZADO 2025'!D77*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4731,11 +4743,11 @@
       <c r="T57" s="5"/>
     </row>
     <row r="58" spans="3:20" ht="12">
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="69"/>
-      <c r="E58" s="69"/>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
       <c r="F58" s="3">
         <f>'REALIZADO 2025'!D78*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>888.24999999999989</v>
@@ -4795,11 +4807,11 @@
       <c r="T58" s="5"/>
     </row>
     <row r="59" spans="3:20" ht="12">
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D59" s="69"/>
-      <c r="E59" s="69"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
       <c r="F59" s="3">
         <f>'REALIZADO 2025'!D79*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4859,11 +4871,11 @@
       <c r="T59" s="5"/>
     </row>
     <row r="60" spans="3:20" ht="12">
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="69"/>
-      <c r="E60" s="69"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
       <c r="F60" s="3">
         <f>'REALIZADO 2025'!D80*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2080.5113999999999</v>
@@ -4922,11 +4934,11 @@
       <c r="T60" s="5"/>
     </row>
     <row r="61" spans="3:20" ht="12">
-      <c r="C61" s="69" t="s">
+      <c r="C61" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="69"/>
-      <c r="E61" s="69"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
       <c r="F61" s="3">
         <f>'REALIZADO 2025'!D81*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -4986,11 +4998,11 @@
       <c r="T61" s="5"/>
     </row>
     <row r="62" spans="3:20" ht="12">
-      <c r="C62" s="69" t="s">
+      <c r="C62" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
       <c r="F62" s="3">
         <f>'REALIZADO 2025'!D82*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>7691.6597999999994</v>
@@ -5050,11 +5062,11 @@
       <c r="T62" s="5"/>
     </row>
     <row r="63" spans="3:20" ht="12">
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
       <c r="F63" s="3">
         <f>'REALIZADO 2025'!D83*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1149.5</v>
@@ -5113,11 +5125,11 @@
       <c r="T63" s="5"/>
     </row>
     <row r="64" spans="3:20" ht="12">
-      <c r="C64" s="69" t="s">
+      <c r="C64" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
       <c r="F64" s="3">
         <f>'REALIZADO 2025'!D84*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -5177,11 +5189,11 @@
       <c r="T64" s="5"/>
     </row>
     <row r="65" spans="3:21" ht="12">
-      <c r="C65" s="69" t="s">
+      <c r="C65" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="69"/>
-      <c r="E65" s="69"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="75"/>
       <c r="F65" s="3">
         <f>'REALIZADO 2025'!D85*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>58.310999999999993</v>
@@ -5241,11 +5253,11 @@
       <c r="T65" s="5"/>
     </row>
     <row r="66" spans="3:21" ht="12">
-      <c r="C66" s="69" t="s">
+      <c r="C66" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
       <c r="F66" s="3">
         <f>'REALIZADO 2025'!D86*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -5305,11 +5317,11 @@
       <c r="T66" s="5"/>
     </row>
     <row r="67" spans="3:21" ht="12">
-      <c r="C67" s="69" t="s">
+      <c r="C67" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="D67" s="69"/>
-      <c r="E67" s="69"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
       <c r="F67" s="3">
         <f>'REALIZADO 2025'!D87*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>0</v>
@@ -5433,11 +5445,11 @@
       <c r="T68" s="5"/>
     </row>
     <row r="69" spans="3:21" ht="12">
-      <c r="C69" s="69" t="s">
+      <c r="C69" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="69"/>
-      <c r="E69" s="69"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
       <c r="F69" s="3">
         <f>'REALIZADO 2025'!D89*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>6040.6224999999995</v>
@@ -5497,11 +5509,11 @@
       <c r="T69" s="5"/>
     </row>
     <row r="70" spans="3:21" ht="12">
-      <c r="C70" s="69" t="s">
+      <c r="C70" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
       <c r="F70" s="3">
         <f>'REALIZADO 2025'!D90*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>7357.8449999999993</v>
@@ -5560,11 +5572,11 @@
       <c r="T70" s="5"/>
     </row>
     <row r="71" spans="3:21" ht="12">
-      <c r="C71" s="69" t="s">
+      <c r="C71" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
       <c r="F71" s="3">
         <f>'REALIZADO 2025'!D91*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2733.72</v>
@@ -5688,11 +5700,11 @@
       <c r="T72" s="5"/>
     </row>
     <row r="73" spans="3:21" ht="12">
-      <c r="C73" s="69" t="s">
+      <c r="C73" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
       <c r="F73" s="3">
         <f>'REALIZADO 2025'!D93*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>909.15</v>
@@ -5752,11 +5764,11 @@
       <c r="T73" s="5"/>
     </row>
     <row r="74" spans="3:21" ht="12">
-      <c r="C74" s="69" t="s">
+      <c r="C74" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
       <c r="F74" s="3">
         <f>'REALIZADO 2025'!D94*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>752.4</v>
@@ -5816,11 +5828,11 @@
       <c r="T74" s="5"/>
     </row>
     <row r="75" spans="3:21" ht="12">
-      <c r="C75" s="69" t="s">
+      <c r="C75" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
+      <c r="D75" s="75"/>
+      <c r="E75" s="75"/>
       <c r="F75" s="3">
         <f>'REALIZADO 2025'!D95*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2403.5</v>
@@ -5880,11 +5892,11 @@
       <c r="T75" s="5"/>
     </row>
     <row r="76" spans="3:21" ht="12">
-      <c r="C76" s="69" t="s">
+      <c r="C76" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
       <c r="F76" s="3">
         <f>'REALIZADO 2025'!D96*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>1472.5094999999999</v>
@@ -5943,11 +5955,11 @@
       <c r="T76" s="5"/>
     </row>
     <row r="77" spans="3:21" ht="12">
-      <c r="C77" s="69" t="s">
+      <c r="C77" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="69"/>
-      <c r="E77" s="69"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
       <c r="F77" s="3">
         <f>'REALIZADO 2025'!D97*'PREVISTO 2026 REVISADO'!$U$38</f>
         <v>2382.6</v>
@@ -6076,11 +6088,11 @@
       </c>
     </row>
     <row r="79" spans="3:21" ht="12">
-      <c r="C79" s="69" t="s">
+      <c r="C79" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="69"/>
-      <c r="E79" s="69"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
       <c r="F79" s="3">
         <f>'REALIZADO 2025'!D99*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>4117.2999999999993</v>
@@ -6140,11 +6152,11 @@
       <c r="T79" s="5"/>
     </row>
     <row r="80" spans="3:21" ht="12">
-      <c r="C80" s="69" t="s">
+      <c r="C80" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="D80" s="69"/>
-      <c r="E80" s="69"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
       <c r="F80" s="3">
         <f>'REALIZADO 2025'!D100*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>2951.08</v>
@@ -6204,11 +6216,11 @@
       <c r="T80" s="5"/>
     </row>
     <row r="81" spans="3:21" ht="12">
-      <c r="C81" s="69" t="s">
+      <c r="C81" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="D81" s="69"/>
-      <c r="E81" s="69"/>
+      <c r="D81" s="75"/>
+      <c r="E81" s="75"/>
       <c r="F81" s="3">
         <f>'REALIZADO 2025'!D101*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>4270.2671</v>
@@ -6268,11 +6280,11 @@
       <c r="T81" s="5"/>
     </row>
     <row r="82" spans="3:21" ht="12">
-      <c r="C82" s="69" t="s">
+      <c r="C82" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D82" s="69"/>
-      <c r="E82" s="69"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="75"/>
       <c r="F82" s="3">
         <f>'REALIZADO 2025'!D102*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>58965.410349999998</v>
@@ -6332,11 +6344,11 @@
       <c r="T82" s="5"/>
     </row>
     <row r="83" spans="3:21" ht="12">
-      <c r="C83" s="69" t="s">
+      <c r="C83" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="D83" s="69"/>
-      <c r="E83" s="69"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="75"/>
       <c r="F83" s="3">
         <f>'REALIZADO 2025'!D103*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>0</v>
@@ -6396,11 +6408,11 @@
       <c r="T83" s="5"/>
     </row>
     <row r="84" spans="3:21" ht="12">
-      <c r="C84" s="69" t="s">
+      <c r="C84" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="D84" s="69"/>
-      <c r="E84" s="69"/>
+      <c r="D84" s="75"/>
+      <c r="E84" s="75"/>
       <c r="F84" s="3">
         <f>'REALIZADO 2025'!D104*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>2508</v>
@@ -6460,11 +6472,11 @@
       <c r="T84" s="5"/>
     </row>
     <row r="85" spans="3:21" ht="12">
-      <c r="C85" s="69" t="s">
+      <c r="C85" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="69"/>
-      <c r="E85" s="69"/>
+      <c r="D85" s="75"/>
+      <c r="E85" s="75"/>
       <c r="F85" s="3">
         <f>'REALIZADO 2025'!D106*'PREVISTO 2026 REVISADO'!$U$78</f>
         <v>1250.3425</v>
@@ -6593,11 +6605,11 @@
       </c>
     </row>
     <row r="87" spans="3:21" ht="12">
-      <c r="C87" s="69" t="s">
+      <c r="C87" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="D87" s="69"/>
-      <c r="E87" s="69"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="75"/>
       <c r="F87" s="3">
         <f>'REALIZADO 2025'!D109*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>11147.161299999998</v>
@@ -6656,11 +6668,11 @@
       <c r="T87" s="5"/>
     </row>
     <row r="88" spans="3:21" ht="12">
-      <c r="C88" s="69" t="s">
+      <c r="C88" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="D88" s="69"/>
-      <c r="E88" s="69"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="75"/>
       <c r="F88" s="3">
         <f>'REALIZADO 2025'!D110*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>1863.7366</v>
@@ -6719,11 +6731,11 @@
       <c r="T88" s="5"/>
     </row>
     <row r="89" spans="3:21" ht="12">
-      <c r="C89" s="69" t="s">
+      <c r="C89" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="75"/>
       <c r="F89" s="3">
         <f>'REALIZADO 2025'!D111*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>0</v>
@@ -6783,11 +6795,11 @@
       <c r="T89" s="5"/>
     </row>
     <row r="90" spans="3:21" ht="12">
-      <c r="C90" s="69" t="s">
+      <c r="C90" s="75" t="s">
         <v>104</v>
       </c>
-      <c r="D90" s="69"/>
-      <c r="E90" s="69"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="75"/>
       <c r="F90" s="3">
         <f>'REALIZADO 2025'!D112*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>169.6035</v>
@@ -6847,11 +6859,11 @@
       <c r="T90" s="5"/>
     </row>
     <row r="91" spans="3:21" ht="12">
-      <c r="C91" s="69" t="s">
+      <c r="C91" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="D91" s="69"/>
-      <c r="E91" s="69"/>
+      <c r="D91" s="75"/>
+      <c r="E91" s="75"/>
       <c r="F91" s="3">
         <f>'REALIZADO 2025'!D113*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>0</v>
@@ -6911,11 +6923,11 @@
       <c r="T91" s="5"/>
     </row>
     <row r="92" spans="3:21" ht="12">
-      <c r="C92" s="69" t="s">
+      <c r="C92" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
+      <c r="D92" s="75"/>
+      <c r="E92" s="75"/>
       <c r="F92" s="3">
         <f>'REALIZADO 2025'!D114*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>102.8489</v>
@@ -6975,11 +6987,11 @@
       <c r="T92" s="5"/>
     </row>
     <row r="93" spans="3:21" ht="12">
-      <c r="C93" s="69" t="s">
+      <c r="C93" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="D93" s="69"/>
-      <c r="E93" s="69"/>
+      <c r="D93" s="75"/>
+      <c r="E93" s="75"/>
       <c r="F93" s="3">
         <f>'REALIZADO 2025'!D115*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>208.98955000000001</v>
@@ -7039,11 +7051,11 @@
       <c r="T93" s="5"/>
     </row>
     <row r="94" spans="3:21" ht="12">
-      <c r="C94" s="69" t="s">
+      <c r="C94" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="D94" s="69"/>
-      <c r="E94" s="69"/>
+      <c r="D94" s="75"/>
+      <c r="E94" s="75"/>
       <c r="F94" s="3">
         <f>'REALIZADO 2025'!D116*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>0</v>
@@ -7103,11 +7115,11 @@
       <c r="T94" s="5"/>
     </row>
     <row r="95" spans="3:21" ht="12">
-      <c r="C95" s="69" t="s">
+      <c r="C95" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="D95" s="69"/>
-      <c r="E95" s="69"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
       <c r="F95" s="3">
         <f>'REALIZADO 2025'!D117*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>101.25004999999999</v>
@@ -7167,11 +7179,11 @@
       <c r="T95" s="5"/>
     </row>
     <row r="96" spans="3:21" ht="12">
-      <c r="C96" s="69" t="s">
+      <c r="C96" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="69"/>
-      <c r="E96" s="69"/>
+      <c r="D96" s="75"/>
+      <c r="E96" s="75"/>
       <c r="F96" s="3">
         <f>'REALIZADO 2025'!D118*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>36.470499999999994</v>
@@ -7231,11 +7243,11 @@
       <c r="T96" s="5"/>
     </row>
     <row r="97" spans="3:20" ht="12">
-      <c r="C97" s="69" t="s">
+      <c r="C97" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="D97" s="69"/>
-      <c r="E97" s="69"/>
+      <c r="D97" s="75"/>
+      <c r="E97" s="75"/>
       <c r="F97" s="3">
         <f>'REALIZADO 2025'!D119*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>762.84999999999991</v>
@@ -7295,11 +7307,11 @@
       <c r="T97" s="5"/>
     </row>
     <row r="98" spans="3:20" ht="12">
-      <c r="C98" s="69" t="s">
+      <c r="C98" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="D98" s="69"/>
-      <c r="E98" s="69"/>
+      <c r="D98" s="75"/>
+      <c r="E98" s="75"/>
       <c r="F98" s="3">
         <f>'REALIZADO 2025'!D120*'PREVISTO 2026 REVISADO'!$U$86</f>
         <v>1512.3239999999998</v>
@@ -7359,11 +7371,11 @@
       <c r="T98" s="5"/>
     </row>
     <row r="99" spans="3:20" ht="12">
-      <c r="C99" s="70" t="s">
+      <c r="C99" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="70"/>
-      <c r="E99" s="70"/>
+      <c r="D99" s="82"/>
+      <c r="E99" s="82"/>
       <c r="F99" s="60" t="e">
         <f>F4</f>
         <v>#REF!</v>
@@ -7443,19 +7455,19 @@
       <c r="T100" s="32"/>
     </row>
     <row r="101" spans="3:20" ht="14.4">
-      <c r="C101" s="71" t="s">
+      <c r="C101" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="D101" s="71"/>
+      <c r="D101" s="83"/>
       <c r="E101" s="64">
         <v>270297.34000000003</v>
       </c>
     </row>
     <row r="102" spans="3:20" ht="14.4">
-      <c r="C102" s="72" t="s">
+      <c r="C102" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="D102" s="72"/>
+      <c r="D102" s="84"/>
       <c r="E102" s="65">
         <f>S99</f>
         <v>284113.14483333332</v>
@@ -7463,10 +7475,10 @@
       <c r="F102" s="59"/>
     </row>
     <row r="103" spans="3:20" ht="14.4">
-      <c r="C103" s="73" t="s">
+      <c r="C103" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="D103" s="73"/>
+      <c r="D103" s="85"/>
       <c r="E103" s="66">
         <f>E102-E101</f>
         <v>13815.804833333299</v>
@@ -7474,10 +7486,10 @@
       <c r="F103" s="59"/>
     </row>
     <row r="104" spans="3:20" ht="14.4">
-      <c r="C104" s="68" t="s">
+      <c r="C104" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="D104" s="68"/>
+      <c r="D104" s="80"/>
       <c r="E104" s="67">
         <f>E103/E101</f>
         <v>5.1113358471575408E-2</v>
@@ -7521,6 +7533,85 @@
     <row r="135" ht="12"/>
   </sheetData>
   <mergeCells count="103">
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
     <mergeCell ref="C1:S1"/>
     <mergeCell ref="C2:S2"/>
     <mergeCell ref="C3:E3"/>
@@ -7545,85 +7636,6 @@
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C96:E96"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -7651,11 +7663,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
       <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
@@ -7701,11 +7713,11 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:18" ht="12">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
       <c r="D2" s="33">
         <f>SUM(D3:D24)</f>
         <v>290185.64999999997</v>
@@ -7765,11 +7777,11 @@
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:18" ht="12">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
       <c r="D3" s="35">
         <v>239580.04</v>
       </c>
@@ -7817,11 +7829,11 @@
       <c r="R3" s="32"/>
     </row>
     <row r="4" spans="1:18" ht="12">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
       <c r="D4" s="38">
         <v>8221.9500000000007</v>
       </c>
@@ -7869,11 +7881,11 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:18" ht="12">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
       <c r="D5" s="35">
         <v>0</v>
       </c>
@@ -7921,11 +7933,11 @@
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:18" ht="12">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
       <c r="D6" s="38">
         <v>0</v>
       </c>
@@ -7973,11 +7985,11 @@
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:18" ht="12">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="35">
         <v>0</v>
       </c>
@@ -8025,11 +8037,11 @@
       <c r="R7" s="32"/>
     </row>
     <row r="8" spans="1:18" ht="12">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
       <c r="D8" s="38">
         <v>525</v>
       </c>
@@ -8077,11 +8089,11 @@
       <c r="R8" s="32"/>
     </row>
     <row r="9" spans="1:18" ht="12">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
       <c r="D9" s="35">
         <v>1260</v>
       </c>
@@ -8129,11 +8141,11 @@
       <c r="R9" s="32"/>
     </row>
     <row r="10" spans="1:18" ht="12">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
       <c r="D10" s="38">
         <v>1706.95</v>
       </c>
@@ -8181,11 +8193,11 @@
       <c r="R10" s="32"/>
     </row>
     <row r="11" spans="1:18" ht="12">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="35">
         <v>23926.35</v>
       </c>
@@ -8233,11 +8245,11 @@
       <c r="R11" s="32"/>
     </row>
     <row r="12" spans="1:18" ht="12">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
       <c r="D12" s="38">
         <v>150</v>
       </c>
@@ -8285,11 +8297,11 @@
       <c r="R12" s="32"/>
     </row>
     <row r="13" spans="1:18" ht="12">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
       <c r="D13" s="35">
         <v>0</v>
       </c>
@@ -8337,11 +8349,11 @@
       <c r="R13" s="32"/>
     </row>
     <row r="14" spans="1:18" ht="12">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="38">
         <v>317.67</v>
       </c>
@@ -8389,11 +8401,11 @@
       <c r="R14" s="32"/>
     </row>
     <row r="15" spans="1:18" ht="12">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="85"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="35">
         <v>1730</v>
       </c>
@@ -8441,11 +8453,11 @@
       <c r="R15" s="32"/>
     </row>
     <row r="16" spans="1:18" ht="12">
-      <c r="A16" s="86" t="s">
+      <c r="A16" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
       <c r="D16" s="38">
         <v>8050.48</v>
       </c>
@@ -8493,11 +8505,11 @@
       <c r="R16" s="32"/>
     </row>
     <row r="17" spans="1:18" ht="12">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="35">
         <v>50.02</v>
       </c>
@@ -8545,11 +8557,11 @@
       <c r="R17" s="32"/>
     </row>
     <row r="18" spans="1:18" ht="12">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="88"/>
       <c r="D18" s="38">
         <v>500</v>
       </c>
@@ -8597,11 +8609,11 @@
       <c r="R18" s="32"/>
     </row>
     <row r="19" spans="1:18" ht="12">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="35">
         <v>0</v>
       </c>
@@ -8649,11 +8661,11 @@
       <c r="R19" s="32"/>
     </row>
     <row r="20" spans="1:18" ht="12">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
       <c r="D20" s="38">
         <v>2450.54</v>
       </c>
@@ -8701,11 +8713,11 @@
       <c r="R20" s="32"/>
     </row>
     <row r="21" spans="1:18" ht="12">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="35">
         <v>754.13</v>
       </c>
@@ -8753,11 +8765,11 @@
       <c r="R21" s="32"/>
     </row>
     <row r="22" spans="1:18" ht="12">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
       <c r="D22" s="38">
         <v>797.85</v>
       </c>
@@ -8805,11 +8817,11 @@
       <c r="R22" s="32"/>
     </row>
     <row r="23" spans="1:18" ht="12">
-      <c r="A23" s="85" t="s">
+      <c r="A23" s="87" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
       <c r="D23" s="35">
         <v>0</v>
       </c>
@@ -8857,11 +8869,11 @@
       <c r="R23" s="32"/>
     </row>
     <row r="24" spans="1:18" ht="12">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="88"/>
       <c r="D24" s="38">
         <v>164.67</v>
       </c>
@@ -8909,11 +8921,11 @@
       <c r="R24" s="32"/>
     </row>
     <row r="25" spans="1:18" ht="12">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="86" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
       <c r="D25" s="39">
         <f>D2</f>
         <v>290185.64999999997</v>
@@ -8973,11 +8985,11 @@
       <c r="R25" s="32"/>
     </row>
     <row r="26" spans="1:18" ht="12">
-      <c r="A26" s="87" t="s">
+      <c r="A26" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="87"/>
-      <c r="C26" s="87"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="40">
         <f>D27+D46+D63+D98+D108+D121</f>
         <v>308825.78999999998</v>
@@ -9037,11 +9049,11 @@
       <c r="R26" s="32"/>
     </row>
     <row r="27" spans="1:18" ht="12">
-      <c r="A27" s="89" t="s">
+      <c r="A27" s="90" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="89"/>
-      <c r="C27" s="89"/>
+      <c r="B27" s="90"/>
+      <c r="C27" s="90"/>
       <c r="D27" s="41">
         <f>SUM(D28:D45)</f>
         <v>8428.5899999999983</v>
@@ -9101,11 +9113,11 @@
       <c r="R27" s="32"/>
     </row>
     <row r="28" spans="1:18" ht="12">
-      <c r="A28" s="86" t="s">
+      <c r="A28" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="88"/>
       <c r="D28" s="38">
         <v>553.58000000000004</v>
       </c>
@@ -9153,11 +9165,11 @@
       <c r="R28" s="32"/>
     </row>
     <row r="29" spans="1:18" ht="12">
-      <c r="A29" s="85" t="s">
+      <c r="A29" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="85"/>
-      <c r="C29" s="85"/>
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
       <c r="D29" s="35">
         <v>0</v>
       </c>
@@ -9205,11 +9217,11 @@
       <c r="R29" s="32"/>
     </row>
     <row r="30" spans="1:18" ht="12">
-      <c r="A30" s="86" t="s">
+      <c r="A30" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="86"/>
-      <c r="C30" s="86"/>
+      <c r="B30" s="88"/>
+      <c r="C30" s="88"/>
       <c r="D30" s="38">
         <v>0</v>
       </c>
@@ -9257,11 +9269,11 @@
       <c r="R30" s="32"/>
     </row>
     <row r="31" spans="1:18" ht="12">
-      <c r="A31" s="85" t="s">
+      <c r="A31" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
+      <c r="B31" s="87"/>
+      <c r="C31" s="87"/>
       <c r="D31" s="35">
         <v>0</v>
       </c>
@@ -9309,11 +9321,11 @@
       <c r="R31" s="32"/>
     </row>
     <row r="32" spans="1:18" ht="12">
-      <c r="A32" s="86" t="s">
+      <c r="A32" s="88" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="88"/>
       <c r="D32" s="38">
         <v>0</v>
       </c>
@@ -9361,11 +9373,11 @@
       <c r="R32" s="32"/>
     </row>
     <row r="33" spans="1:18" ht="12">
-      <c r="A33" s="85" t="s">
+      <c r="A33" s="87" t="s">
         <v>144</v>
       </c>
-      <c r="B33" s="85"/>
-      <c r="C33" s="85"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
       <c r="D33" s="35">
         <v>0</v>
       </c>
@@ -9413,11 +9425,11 @@
       <c r="R33" s="32"/>
     </row>
     <row r="34" spans="1:18" ht="12">
-      <c r="A34" s="86" t="s">
+      <c r="A34" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="86"/>
-      <c r="C34" s="86"/>
+      <c r="B34" s="88"/>
+      <c r="C34" s="88"/>
       <c r="D34" s="38">
         <v>0</v>
       </c>
@@ -9465,11 +9477,11 @@
       <c r="R34" s="32"/>
     </row>
     <row r="35" spans="1:18" ht="12">
-      <c r="A35" s="85" t="s">
+      <c r="A35" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="85"/>
-      <c r="C35" s="85"/>
+      <c r="B35" s="87"/>
+      <c r="C35" s="87"/>
       <c r="D35" s="35">
         <v>356.15</v>
       </c>
@@ -9517,11 +9529,11 @@
       <c r="R35" s="32"/>
     </row>
     <row r="36" spans="1:18" ht="12">
-      <c r="A36" s="86" t="s">
+      <c r="A36" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
       <c r="D36" s="38">
         <v>500</v>
       </c>
@@ -9569,11 +9581,11 @@
       <c r="R36" s="32"/>
     </row>
     <row r="37" spans="1:18" ht="12">
-      <c r="A37" s="85" t="s">
+      <c r="A37" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="85"/>
-      <c r="C37" s="85"/>
+      <c r="B37" s="87"/>
+      <c r="C37" s="87"/>
       <c r="D37" s="35">
         <v>0</v>
       </c>
@@ -9621,11 +9633,11 @@
       <c r="R37" s="32"/>
     </row>
     <row r="38" spans="1:18" ht="12">
-      <c r="A38" s="86" t="s">
+      <c r="A38" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="86"/>
-      <c r="C38" s="86"/>
+      <c r="B38" s="88"/>
+      <c r="C38" s="88"/>
       <c r="D38" s="38">
         <v>4540</v>
       </c>
@@ -9673,11 +9685,11 @@
       <c r="R38" s="32"/>
     </row>
     <row r="39" spans="1:18" ht="12">
-      <c r="A39" s="85" t="s">
+      <c r="A39" s="87" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="85"/>
-      <c r="C39" s="85"/>
+      <c r="B39" s="87"/>
+      <c r="C39" s="87"/>
       <c r="D39" s="35">
         <v>2237.23</v>
       </c>
@@ -9725,11 +9737,11 @@
       <c r="R39" s="32"/>
     </row>
     <row r="40" spans="1:18" ht="12">
-      <c r="A40" s="86" t="s">
+      <c r="A40" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
+      <c r="B40" s="88"/>
+      <c r="C40" s="88"/>
       <c r="D40" s="38">
         <v>0</v>
       </c>
@@ -9777,11 +9789,11 @@
       <c r="R40" s="32"/>
     </row>
     <row r="41" spans="1:18" ht="12">
-      <c r="A41" s="85" t="s">
+      <c r="A41" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="B41" s="85"/>
-      <c r="C41" s="85"/>
+      <c r="B41" s="87"/>
+      <c r="C41" s="87"/>
       <c r="D41" s="35">
         <v>0</v>
       </c>
@@ -9829,11 +9841,11 @@
       <c r="R41" s="32"/>
     </row>
     <row r="42" spans="1:18" ht="12">
-      <c r="A42" s="86" t="s">
+      <c r="A42" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="86"/>
-      <c r="C42" s="86"/>
+      <c r="B42" s="88"/>
+      <c r="C42" s="88"/>
       <c r="D42" s="38">
         <v>0</v>
       </c>
@@ -9881,11 +9893,11 @@
       <c r="R42" s="32"/>
     </row>
     <row r="43" spans="1:18" ht="12">
-      <c r="A43" s="85" t="s">
+      <c r="A43" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="B43" s="85"/>
-      <c r="C43" s="85"/>
+      <c r="B43" s="87"/>
+      <c r="C43" s="87"/>
       <c r="D43" s="35">
         <v>0</v>
       </c>
@@ -9933,11 +9945,11 @@
       <c r="R43" s="32"/>
     </row>
     <row r="44" spans="1:18" ht="12">
-      <c r="A44" s="86" t="s">
+      <c r="A44" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="B44" s="86"/>
-      <c r="C44" s="86"/>
+      <c r="B44" s="88"/>
+      <c r="C44" s="88"/>
       <c r="D44" s="38">
         <v>241.63</v>
       </c>
@@ -9985,11 +9997,11 @@
       <c r="R44" s="32"/>
     </row>
     <row r="45" spans="1:18" ht="12">
-      <c r="A45" s="85" t="s">
+      <c r="A45" s="87" t="s">
         <v>145</v>
       </c>
-      <c r="B45" s="85"/>
-      <c r="C45" s="85"/>
+      <c r="B45" s="87"/>
+      <c r="C45" s="87"/>
       <c r="D45" s="35">
         <v>0</v>
       </c>
@@ -10037,11 +10049,11 @@
       <c r="R45" s="32"/>
     </row>
     <row r="46" spans="1:18" ht="12">
-      <c r="A46" s="87" t="s">
+      <c r="A46" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="B46" s="87"/>
-      <c r="C46" s="87"/>
+      <c r="B46" s="91"/>
+      <c r="C46" s="91"/>
       <c r="D46" s="40">
         <f>SUM(D47:D62)</f>
         <v>143203.00999999998</v>
@@ -10101,11 +10113,11 @@
       <c r="R46" s="32"/>
     </row>
     <row r="47" spans="1:18" ht="12">
-      <c r="A47" s="85" t="s">
+      <c r="A47" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
+      <c r="B47" s="87"/>
+      <c r="C47" s="87"/>
       <c r="D47" s="35">
         <v>48667</v>
       </c>
@@ -10153,11 +10165,11 @@
       <c r="R47" s="32"/>
     </row>
     <row r="48" spans="1:18" ht="12">
-      <c r="A48" s="86" t="s">
+      <c r="A48" s="88" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
+      <c r="B48" s="88"/>
+      <c r="C48" s="88"/>
       <c r="D48" s="38">
         <v>21530.09</v>
       </c>
@@ -10205,11 +10217,11 @@
       <c r="R48" s="32"/>
     </row>
     <row r="49" spans="1:18" ht="12">
-      <c r="A49" s="85" t="s">
+      <c r="A49" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="85"/>
-      <c r="C49" s="85"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="87"/>
       <c r="D49" s="35">
         <v>71.900000000000006</v>
       </c>
@@ -10257,11 +10269,11 @@
       <c r="R49" s="32"/>
     </row>
     <row r="50" spans="1:18" ht="12">
-      <c r="A50" s="86" t="s">
+      <c r="A50" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="86"/>
-      <c r="C50" s="86"/>
+      <c r="B50" s="88"/>
+      <c r="C50" s="88"/>
       <c r="D50" s="38">
         <v>246.43</v>
       </c>
@@ -10309,11 +10321,11 @@
       <c r="R50" s="32"/>
     </row>
     <row r="51" spans="1:18" ht="12">
-      <c r="A51" s="85" t="s">
+      <c r="A51" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="85"/>
-      <c r="C51" s="85"/>
+      <c r="B51" s="87"/>
+      <c r="C51" s="87"/>
       <c r="D51" s="35">
         <v>0</v>
       </c>
@@ -10361,11 +10373,11 @@
       <c r="R51" s="32"/>
     </row>
     <row r="52" spans="1:18" ht="12">
-      <c r="A52" s="86" t="s">
+      <c r="A52" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="86"/>
-      <c r="C52" s="86"/>
+      <c r="B52" s="88"/>
+      <c r="C52" s="88"/>
       <c r="D52" s="38">
         <v>2808.9</v>
       </c>
@@ -10413,11 +10425,11 @@
       <c r="R52" s="32"/>
     </row>
     <row r="53" spans="1:18" ht="12">
-      <c r="A53" s="85" t="s">
+      <c r="A53" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="85"/>
-      <c r="C53" s="85"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="87"/>
       <c r="D53" s="35">
         <v>295.92</v>
       </c>
@@ -10465,11 +10477,11 @@
       <c r="R53" s="32"/>
     </row>
     <row r="54" spans="1:18" ht="12">
-      <c r="A54" s="86" t="s">
+      <c r="A54" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="86"/>
-      <c r="C54" s="86"/>
+      <c r="B54" s="88"/>
+      <c r="C54" s="88"/>
       <c r="D54" s="38">
         <v>300</v>
       </c>
@@ -10517,11 +10529,11 @@
       <c r="R54" s="32"/>
     </row>
     <row r="55" spans="1:18" ht="12">
-      <c r="A55" s="85" t="s">
+      <c r="A55" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="B55" s="85"/>
-      <c r="C55" s="85"/>
+      <c r="B55" s="87"/>
+      <c r="C55" s="87"/>
       <c r="D55" s="35">
         <v>0</v>
       </c>
@@ -10569,11 +10581,11 @@
       <c r="R55" s="32"/>
     </row>
     <row r="56" spans="1:18" ht="12">
-      <c r="A56" s="86" t="s">
+      <c r="A56" s="88" t="s">
         <v>146</v>
       </c>
-      <c r="B56" s="86"/>
-      <c r="C56" s="86"/>
+      <c r="B56" s="88"/>
+      <c r="C56" s="88"/>
       <c r="D56" s="38">
         <v>166</v>
       </c>
@@ -10621,11 +10633,11 @@
       <c r="R56" s="32"/>
     </row>
     <row r="57" spans="1:18" ht="12">
-      <c r="A57" s="85" t="s">
+      <c r="A57" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="B57" s="85"/>
-      <c r="C57" s="85"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="87"/>
       <c r="D57" s="35">
         <v>24079.08</v>
       </c>
@@ -10673,11 +10685,11 @@
       <c r="R57" s="32"/>
     </row>
     <row r="58" spans="1:18" ht="12">
-      <c r="A58" s="86" t="s">
+      <c r="A58" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="B58" s="86"/>
-      <c r="C58" s="86"/>
+      <c r="B58" s="88"/>
+      <c r="C58" s="88"/>
       <c r="D58" s="38">
         <v>5500.01</v>
       </c>
@@ -10725,11 +10737,11 @@
       <c r="R58" s="32"/>
     </row>
     <row r="59" spans="1:18" ht="12">
-      <c r="A59" s="85" t="s">
+      <c r="A59" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="B59" s="85"/>
-      <c r="C59" s="85"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="87"/>
       <c r="D59" s="35">
         <v>0</v>
       </c>
@@ -10777,11 +10789,11 @@
       <c r="R59" s="32"/>
     </row>
     <row r="60" spans="1:18" ht="12">
-      <c r="A60" s="86" t="s">
+      <c r="A60" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="B60" s="86"/>
-      <c r="C60" s="86"/>
+      <c r="B60" s="88"/>
+      <c r="C60" s="88"/>
       <c r="D60" s="38">
         <v>38781.68</v>
       </c>
@@ -10829,11 +10841,11 @@
       <c r="R60" s="32"/>
     </row>
     <row r="61" spans="1:18" ht="12">
-      <c r="A61" s="85" t="s">
+      <c r="A61" s="87" t="s">
         <v>50</v>
       </c>
-      <c r="B61" s="85"/>
-      <c r="C61" s="85"/>
+      <c r="B61" s="87"/>
+      <c r="C61" s="87"/>
       <c r="D61" s="35">
         <v>0</v>
       </c>
@@ -10881,11 +10893,11 @@
       <c r="R61" s="32"/>
     </row>
     <row r="62" spans="1:18" ht="12">
-      <c r="A62" s="86" t="s">
+      <c r="A62" s="88" t="s">
         <v>51</v>
       </c>
-      <c r="B62" s="86"/>
-      <c r="C62" s="86"/>
+      <c r="B62" s="88"/>
+      <c r="C62" s="88"/>
       <c r="D62" s="38">
         <v>756</v>
       </c>
@@ -10933,11 +10945,11 @@
       <c r="R62" s="32"/>
     </row>
     <row r="63" spans="1:18" ht="12">
-      <c r="A63" s="89" t="s">
+      <c r="A63" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="B63" s="89"/>
-      <c r="C63" s="89"/>
+      <c r="B63" s="90"/>
+      <c r="C63" s="90"/>
       <c r="D63" s="41">
         <f>D64+D75+D88+D92</f>
         <v>46933.689999999995</v>
@@ -10997,11 +11009,11 @@
       <c r="R63" s="32"/>
     </row>
     <row r="64" spans="1:18" ht="12">
-      <c r="A64" s="87" t="s">
+      <c r="A64" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="B64" s="87"/>
-      <c r="C64" s="87"/>
+      <c r="B64" s="91"/>
+      <c r="C64" s="91"/>
       <c r="D64" s="40">
         <f>SUM(D65:D74)</f>
         <v>11409.97</v>
@@ -11061,11 +11073,11 @@
       <c r="R64" s="32"/>
     </row>
     <row r="65" spans="1:18" ht="12">
-      <c r="A65" s="85" t="s">
+      <c r="A65" s="87" t="s">
         <v>54</v>
       </c>
-      <c r="B65" s="85"/>
-      <c r="C65" s="85"/>
+      <c r="B65" s="87"/>
+      <c r="C65" s="87"/>
       <c r="D65" s="35">
         <v>1483.91</v>
       </c>
@@ -11113,11 +11125,11 @@
       <c r="R65" s="32"/>
     </row>
     <row r="66" spans="1:18" ht="12">
-      <c r="A66" s="86" t="s">
+      <c r="A66" s="88" t="s">
         <v>147</v>
       </c>
-      <c r="B66" s="86"/>
-      <c r="C66" s="86"/>
+      <c r="B66" s="88"/>
+      <c r="C66" s="88"/>
       <c r="D66" s="38">
         <v>143.94999999999999</v>
       </c>
@@ -11165,11 +11177,11 @@
       <c r="R66" s="32"/>
     </row>
     <row r="67" spans="1:18" ht="12">
-      <c r="A67" s="85" t="s">
+      <c r="A67" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="B67" s="85"/>
-      <c r="C67" s="85"/>
+      <c r="B67" s="87"/>
+      <c r="C67" s="87"/>
       <c r="D67" s="35">
         <v>0</v>
       </c>
@@ -11217,11 +11229,11 @@
       <c r="R67" s="32"/>
     </row>
     <row r="68" spans="1:18" s="51" customFormat="1" ht="12">
-      <c r="A68" s="91" t="s">
+      <c r="A68" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="B68" s="91"/>
-      <c r="C68" s="91"/>
+      <c r="B68" s="89"/>
+      <c r="C68" s="89"/>
       <c r="D68" s="48">
         <v>3056.35</v>
       </c>
@@ -11269,11 +11281,11 @@
       <c r="R68" s="50"/>
     </row>
     <row r="69" spans="1:18" s="51" customFormat="1" ht="12">
-      <c r="A69" s="91" t="s">
+      <c r="A69" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="B69" s="91"/>
-      <c r="C69" s="91"/>
+      <c r="B69" s="89"/>
+      <c r="C69" s="89"/>
       <c r="D69" s="48">
         <v>584.5</v>
       </c>
@@ -11321,11 +11333,11 @@
       <c r="R69" s="50"/>
     </row>
     <row r="70" spans="1:18" ht="12">
-      <c r="A70" s="86" t="s">
+      <c r="A70" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="B70" s="86"/>
-      <c r="C70" s="86"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="88"/>
       <c r="D70" s="38">
         <v>530.64</v>
       </c>
@@ -11373,11 +11385,11 @@
       <c r="R70" s="32"/>
     </row>
     <row r="71" spans="1:18" ht="12">
-      <c r="A71" s="85" t="s">
+      <c r="A71" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="B71" s="85"/>
-      <c r="C71" s="85"/>
+      <c r="B71" s="87"/>
+      <c r="C71" s="87"/>
       <c r="D71" s="35">
         <v>0</v>
       </c>
@@ -11425,11 +11437,11 @@
       <c r="R71" s="32"/>
     </row>
     <row r="72" spans="1:18" ht="12">
-      <c r="A72" s="86" t="s">
+      <c r="A72" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="B72" s="86"/>
-      <c r="C72" s="86"/>
+      <c r="B72" s="88"/>
+      <c r="C72" s="88"/>
       <c r="D72" s="38">
         <v>5263.97</v>
       </c>
@@ -11477,11 +11489,11 @@
       <c r="R72" s="32"/>
     </row>
     <row r="73" spans="1:18" ht="12">
-      <c r="A73" s="85" t="s">
+      <c r="A73" s="87" t="s">
         <v>148</v>
       </c>
-      <c r="B73" s="85"/>
-      <c r="C73" s="85"/>
+      <c r="B73" s="87"/>
+      <c r="C73" s="87"/>
       <c r="D73" s="35">
         <v>334.65</v>
       </c>
@@ -11529,11 +11541,11 @@
       <c r="R73" s="32"/>
     </row>
     <row r="74" spans="1:18" ht="12">
-      <c r="A74" s="86" t="s">
+      <c r="A74" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="B74" s="86"/>
-      <c r="C74" s="86"/>
+      <c r="B74" s="88"/>
+      <c r="C74" s="88"/>
       <c r="D74" s="38">
         <v>12</v>
       </c>
@@ -11581,11 +11593,11 @@
       <c r="R74" s="32"/>
     </row>
     <row r="75" spans="1:18" ht="12">
-      <c r="A75" s="89" t="s">
+      <c r="A75" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="B75" s="89"/>
-      <c r="C75" s="89"/>
+      <c r="B75" s="90"/>
+      <c r="C75" s="90"/>
       <c r="D75" s="41">
         <f>SUM(D76:D87)</f>
         <v>12507.119999999999</v>
@@ -11645,11 +11657,11 @@
       <c r="R75" s="32"/>
     </row>
     <row r="76" spans="1:18" ht="12">
-      <c r="A76" s="86" t="s">
+      <c r="A76" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="B76" s="86"/>
-      <c r="C76" s="86"/>
+      <c r="B76" s="88"/>
+      <c r="C76" s="88"/>
       <c r="D76" s="38">
         <v>1149.96</v>
       </c>
@@ -11697,11 +11709,11 @@
       <c r="R76" s="32"/>
     </row>
     <row r="77" spans="1:18" ht="12">
-      <c r="A77" s="85" t="s">
+      <c r="A77" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="B77" s="85"/>
-      <c r="C77" s="85"/>
+      <c r="B77" s="87"/>
+      <c r="C77" s="87"/>
       <c r="D77" s="35">
         <v>0</v>
       </c>
@@ -11749,11 +11761,11 @@
       <c r="R77" s="32"/>
     </row>
     <row r="78" spans="1:18" ht="12">
-      <c r="A78" s="86" t="s">
+      <c r="A78" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="86"/>
-      <c r="C78" s="86"/>
+      <c r="B78" s="88"/>
+      <c r="C78" s="88"/>
       <c r="D78" s="38">
         <v>850</v>
       </c>
@@ -11801,11 +11813,11 @@
       <c r="R78" s="32"/>
     </row>
     <row r="79" spans="1:18" ht="12">
-      <c r="A79" s="85" t="s">
+      <c r="A79" s="87" t="s">
         <v>73</v>
       </c>
-      <c r="B79" s="85"/>
-      <c r="C79" s="85"/>
+      <c r="B79" s="87"/>
+      <c r="C79" s="87"/>
       <c r="D79" s="35">
         <v>0</v>
       </c>
@@ -11853,11 +11865,11 @@
       <c r="R79" s="32"/>
     </row>
     <row r="80" spans="1:18" ht="12">
-      <c r="A80" s="86" t="s">
+      <c r="A80" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="B80" s="86"/>
-      <c r="C80" s="86"/>
+      <c r="B80" s="88"/>
+      <c r="C80" s="88"/>
       <c r="D80" s="38">
         <v>1990.92</v>
       </c>
@@ -11905,11 +11917,11 @@
       <c r="R80" s="32"/>
     </row>
     <row r="81" spans="1:18" ht="12">
-      <c r="A81" s="85" t="s">
+      <c r="A81" s="87" t="s">
         <v>75</v>
       </c>
-      <c r="B81" s="85"/>
-      <c r="C81" s="85"/>
+      <c r="B81" s="87"/>
+      <c r="C81" s="87"/>
       <c r="D81" s="35">
         <v>0</v>
       </c>
@@ -11957,11 +11969,11 @@
       <c r="R81" s="32"/>
     </row>
     <row r="82" spans="1:18" ht="12">
-      <c r="A82" s="86" t="s">
+      <c r="A82" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="B82" s="86"/>
-      <c r="C82" s="86"/>
+      <c r="B82" s="88"/>
+      <c r="C82" s="88"/>
       <c r="D82" s="38">
         <v>7360.44</v>
       </c>
@@ -12009,11 +12021,11 @@
       <c r="R82" s="32"/>
     </row>
     <row r="83" spans="1:18" ht="12">
-      <c r="A83" s="85" t="s">
+      <c r="A83" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="B83" s="85"/>
-      <c r="C83" s="85"/>
+      <c r="B83" s="87"/>
+      <c r="C83" s="87"/>
       <c r="D83" s="35">
         <v>1100</v>
       </c>
@@ -12061,11 +12073,11 @@
       <c r="R83" s="32"/>
     </row>
     <row r="84" spans="1:18" ht="12">
-      <c r="A84" s="86" t="s">
+      <c r="A84" s="88" t="s">
         <v>78</v>
       </c>
-      <c r="B84" s="86"/>
-      <c r="C84" s="86"/>
+      <c r="B84" s="88"/>
+      <c r="C84" s="88"/>
       <c r="D84" s="38">
         <v>0</v>
       </c>
@@ -12113,11 +12125,11 @@
       <c r="R84" s="32"/>
     </row>
     <row r="85" spans="1:18" ht="12">
-      <c r="A85" s="85" t="s">
+      <c r="A85" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="B85" s="85"/>
-      <c r="C85" s="85"/>
+      <c r="B85" s="87"/>
+      <c r="C85" s="87"/>
       <c r="D85" s="35">
         <v>55.8</v>
       </c>
@@ -12165,11 +12177,11 @@
       <c r="R85" s="32"/>
     </row>
     <row r="86" spans="1:18" ht="12">
-      <c r="A86" s="86" t="s">
+      <c r="A86" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="B86" s="86"/>
-      <c r="C86" s="86"/>
+      <c r="B86" s="88"/>
+      <c r="C86" s="88"/>
       <c r="D86" s="38">
         <v>0</v>
       </c>
@@ -12217,11 +12229,11 @@
       <c r="R86" s="32"/>
     </row>
     <row r="87" spans="1:18" ht="12">
-      <c r="A87" s="85" t="s">
+      <c r="A87" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="B87" s="85"/>
-      <c r="C87" s="85"/>
+      <c r="B87" s="87"/>
+      <c r="C87" s="87"/>
       <c r="D87" s="35">
         <v>0</v>
       </c>
@@ -12269,11 +12281,11 @@
       <c r="R87" s="32"/>
     </row>
     <row r="88" spans="1:18" ht="12">
-      <c r="A88" s="87" t="s">
+      <c r="A88" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="B88" s="87"/>
-      <c r="C88" s="87"/>
+      <c r="B88" s="91"/>
+      <c r="C88" s="91"/>
       <c r="D88" s="40">
         <f>SUM(D89:D91)</f>
         <v>15437.5</v>
@@ -12333,11 +12345,11 @@
       <c r="R88" s="32"/>
     </row>
     <row r="89" spans="1:18" ht="12">
-      <c r="A89" s="85" t="s">
+      <c r="A89" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="85"/>
-      <c r="C89" s="85"/>
+      <c r="B89" s="87"/>
+      <c r="C89" s="87"/>
       <c r="D89" s="35">
         <v>5780.5</v>
       </c>
@@ -12385,11 +12397,11 @@
       <c r="R89" s="32"/>
     </row>
     <row r="90" spans="1:18" ht="12">
-      <c r="A90" s="86" t="s">
+      <c r="A90" s="88" t="s">
         <v>84</v>
       </c>
-      <c r="B90" s="86"/>
-      <c r="C90" s="86"/>
+      <c r="B90" s="88"/>
+      <c r="C90" s="88"/>
       <c r="D90" s="38">
         <v>7041</v>
       </c>
@@ -12437,11 +12449,11 @@
       <c r="R90" s="32"/>
     </row>
     <row r="91" spans="1:18" ht="12">
-      <c r="A91" s="85" t="s">
+      <c r="A91" s="87" t="s">
         <v>85</v>
       </c>
-      <c r="B91" s="85"/>
-      <c r="C91" s="85"/>
+      <c r="B91" s="87"/>
+      <c r="C91" s="87"/>
       <c r="D91" s="35">
         <v>2616</v>
       </c>
@@ -12489,11 +12501,11 @@
       <c r="R91" s="32"/>
     </row>
     <row r="92" spans="1:18" ht="12">
-      <c r="A92" s="87" t="s">
+      <c r="A92" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="B92" s="87"/>
-      <c r="C92" s="87"/>
+      <c r="B92" s="91"/>
+      <c r="C92" s="91"/>
       <c r="D92" s="40">
         <f>SUM(D93:D97)</f>
         <v>7579.1</v>
@@ -12553,11 +12565,11 @@
       <c r="R92" s="32"/>
     </row>
     <row r="93" spans="1:18" ht="12">
-      <c r="A93" s="85" t="s">
+      <c r="A93" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="B93" s="85"/>
-      <c r="C93" s="85"/>
+      <c r="B93" s="87"/>
+      <c r="C93" s="87"/>
       <c r="D93" s="35">
         <v>870</v>
       </c>
@@ -12605,11 +12617,11 @@
       <c r="R93" s="32"/>
     </row>
     <row r="94" spans="1:18" ht="12">
-      <c r="A94" s="86" t="s">
+      <c r="A94" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="B94" s="86"/>
-      <c r="C94" s="86"/>
+      <c r="B94" s="88"/>
+      <c r="C94" s="88"/>
       <c r="D94" s="38">
         <v>720</v>
       </c>
@@ -12657,11 +12669,11 @@
       <c r="R94" s="32"/>
     </row>
     <row r="95" spans="1:18" ht="12">
-      <c r="A95" s="85" t="s">
+      <c r="A95" s="87" t="s">
         <v>89</v>
       </c>
-      <c r="B95" s="85"/>
-      <c r="C95" s="85"/>
+      <c r="B95" s="87"/>
+      <c r="C95" s="87"/>
       <c r="D95" s="35">
         <v>2300</v>
       </c>
@@ -12709,11 +12721,11 @@
       <c r="R95" s="32"/>
     </row>
     <row r="96" spans="1:18" ht="12">
-      <c r="A96" s="86" t="s">
+      <c r="A96" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="B96" s="86"/>
-      <c r="C96" s="86"/>
+      <c r="B96" s="88"/>
+      <c r="C96" s="88"/>
       <c r="D96" s="38">
         <v>1409.1</v>
       </c>
@@ -12761,11 +12773,11 @@
       <c r="R96" s="32"/>
     </row>
     <row r="97" spans="1:18" ht="12">
-      <c r="A97" s="85" t="s">
+      <c r="A97" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="B97" s="85"/>
-      <c r="C97" s="85"/>
+      <c r="B97" s="87"/>
+      <c r="C97" s="87"/>
       <c r="D97" s="35">
         <v>2280</v>
       </c>
@@ -12813,11 +12825,11 @@
       <c r="R97" s="32"/>
     </row>
     <row r="98" spans="1:18" ht="12">
-      <c r="A98" s="87" t="s">
+      <c r="A98" s="91" t="s">
         <v>92</v>
       </c>
-      <c r="B98" s="87"/>
-      <c r="C98" s="87"/>
+      <c r="B98" s="91"/>
+      <c r="C98" s="91"/>
       <c r="D98" s="40">
         <f>SUM(D99:D107)</f>
         <v>70873.11</v>
@@ -12877,11 +12889,11 @@
       <c r="R98" s="32"/>
     </row>
     <row r="99" spans="1:18" ht="12">
-      <c r="A99" s="85" t="s">
+      <c r="A99" s="87" t="s">
         <v>93</v>
       </c>
-      <c r="B99" s="85"/>
-      <c r="C99" s="85"/>
+      <c r="B99" s="87"/>
+      <c r="C99" s="87"/>
       <c r="D99" s="35">
         <v>3940</v>
       </c>
@@ -12929,11 +12941,11 @@
       <c r="R99" s="32"/>
     </row>
     <row r="100" spans="1:18" ht="12">
-      <c r="A100" s="86" t="s">
+      <c r="A100" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="B100" s="86"/>
-      <c r="C100" s="86"/>
+      <c r="B100" s="88"/>
+      <c r="C100" s="88"/>
       <c r="D100" s="38">
         <v>2824</v>
       </c>
@@ -12981,11 +12993,11 @@
       <c r="R100" s="32"/>
     </row>
     <row r="101" spans="1:18" ht="12">
-      <c r="A101" s="85" t="s">
+      <c r="A101" s="87" t="s">
         <v>95</v>
       </c>
-      <c r="B101" s="85"/>
-      <c r="C101" s="85"/>
+      <c r="B101" s="87"/>
+      <c r="C101" s="87"/>
       <c r="D101" s="35">
         <v>4086.38</v>
       </c>
@@ -13033,11 +13045,11 @@
       <c r="R101" s="32"/>
     </row>
     <row r="102" spans="1:18" ht="12">
-      <c r="A102" s="86" t="s">
+      <c r="A102" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="B102" s="86"/>
-      <c r="C102" s="86"/>
+      <c r="B102" s="88"/>
+      <c r="C102" s="88"/>
       <c r="D102" s="38">
         <v>56426.23</v>
       </c>
@@ -13085,11 +13097,11 @@
       <c r="R102" s="32"/>
     </row>
     <row r="103" spans="1:18" ht="12">
-      <c r="A103" s="85" t="s">
+      <c r="A103" s="87" t="s">
         <v>97</v>
       </c>
-      <c r="B103" s="85"/>
-      <c r="C103" s="85"/>
+      <c r="B103" s="87"/>
+      <c r="C103" s="87"/>
       <c r="D103" s="35">
         <v>0</v>
       </c>
@@ -13137,11 +13149,11 @@
       <c r="R103" s="32"/>
     </row>
     <row r="104" spans="1:18" ht="12">
-      <c r="A104" s="86" t="s">
+      <c r="A104" s="88" t="s">
         <v>98</v>
       </c>
-      <c r="B104" s="86"/>
-      <c r="C104" s="86"/>
+      <c r="B104" s="88"/>
+      <c r="C104" s="88"/>
       <c r="D104" s="38">
         <v>2400</v>
       </c>
@@ -13189,11 +13201,11 @@
       <c r="R104" s="32"/>
     </row>
     <row r="105" spans="1:18" ht="12">
-      <c r="A105" s="85" t="s">
+      <c r="A105" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="B105" s="85"/>
-      <c r="C105" s="85"/>
+      <c r="B105" s="87"/>
+      <c r="C105" s="87"/>
       <c r="D105" s="35">
         <v>0</v>
       </c>
@@ -13241,11 +13253,11 @@
       <c r="R105" s="32"/>
     </row>
     <row r="106" spans="1:18" ht="12">
-      <c r="A106" s="86" t="s">
+      <c r="A106" s="88" t="s">
         <v>99</v>
       </c>
-      <c r="B106" s="86"/>
-      <c r="C106" s="86"/>
+      <c r="B106" s="88"/>
+      <c r="C106" s="88"/>
       <c r="D106" s="38">
         <v>1196.5</v>
       </c>
@@ -13293,11 +13305,11 @@
       <c r="R106" s="32"/>
     </row>
     <row r="107" spans="1:18" ht="12">
-      <c r="A107" s="85" t="s">
+      <c r="A107" s="87" t="s">
         <v>150</v>
       </c>
-      <c r="B107" s="85"/>
-      <c r="C107" s="85"/>
+      <c r="B107" s="87"/>
+      <c r="C107" s="87"/>
       <c r="D107" s="35">
         <v>0</v>
       </c>
@@ -13345,11 +13357,11 @@
       <c r="R107" s="32"/>
     </row>
     <row r="108" spans="1:18" ht="12">
-      <c r="A108" s="87" t="s">
+      <c r="A108" s="91" t="s">
         <v>100</v>
       </c>
-      <c r="B108" s="87"/>
-      <c r="C108" s="87"/>
+      <c r="B108" s="91"/>
+      <c r="C108" s="91"/>
       <c r="D108" s="40">
         <f>SUM(D109:D120)</f>
         <v>15220.319999999998</v>
@@ -13409,11 +13421,11 @@
       <c r="R108" s="32"/>
     </row>
     <row r="109" spans="1:18" ht="12">
-      <c r="A109" s="85" t="s">
+      <c r="A109" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="B109" s="85"/>
-      <c r="C109" s="85"/>
+      <c r="B109" s="87"/>
+      <c r="C109" s="87"/>
       <c r="D109" s="35">
         <v>10667.14</v>
       </c>
@@ -13461,11 +13473,11 @@
       <c r="R109" s="32"/>
     </row>
     <row r="110" spans="1:18" ht="12">
-      <c r="A110" s="86" t="s">
+      <c r="A110" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="B110" s="86"/>
-      <c r="C110" s="86"/>
+      <c r="B110" s="88"/>
+      <c r="C110" s="88"/>
       <c r="D110" s="38">
         <v>1783.48</v>
       </c>
@@ -13513,11 +13525,11 @@
       <c r="R110" s="32"/>
     </row>
     <row r="111" spans="1:18" ht="12">
-      <c r="A111" s="85" t="s">
+      <c r="A111" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="B111" s="85"/>
-      <c r="C111" s="85"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="87"/>
       <c r="D111" s="35">
         <v>0</v>
       </c>
@@ -13565,11 +13577,11 @@
       <c r="R111" s="32"/>
     </row>
     <row r="112" spans="1:18" ht="12">
-      <c r="A112" s="86" t="s">
+      <c r="A112" s="88" t="s">
         <v>104</v>
       </c>
-      <c r="B112" s="86"/>
-      <c r="C112" s="86"/>
+      <c r="B112" s="88"/>
+      <c r="C112" s="88"/>
       <c r="D112" s="38">
         <v>162.30000000000001</v>
       </c>
@@ -13617,11 +13629,11 @@
       <c r="R112" s="32"/>
     </row>
     <row r="113" spans="1:18" ht="12">
-      <c r="A113" s="85" t="s">
+      <c r="A113" s="87" t="s">
         <v>105</v>
       </c>
-      <c r="B113" s="85"/>
-      <c r="C113" s="85"/>
+      <c r="B113" s="87"/>
+      <c r="C113" s="87"/>
       <c r="D113" s="35">
         <v>0</v>
       </c>
@@ -13669,11 +13681,11 @@
       <c r="R113" s="32"/>
     </row>
     <row r="114" spans="1:18" ht="12">
-      <c r="A114" s="86" t="s">
+      <c r="A114" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="B114" s="86"/>
-      <c r="C114" s="86"/>
+      <c r="B114" s="88"/>
+      <c r="C114" s="88"/>
       <c r="D114" s="38">
         <v>98.42</v>
       </c>
@@ -13721,11 +13733,11 @@
       <c r="R114" s="32"/>
     </row>
     <row r="115" spans="1:18" ht="12">
-      <c r="A115" s="85" t="s">
+      <c r="A115" s="87" t="s">
         <v>107</v>
       </c>
-      <c r="B115" s="85"/>
-      <c r="C115" s="85"/>
+      <c r="B115" s="87"/>
+      <c r="C115" s="87"/>
       <c r="D115" s="35">
         <v>199.99</v>
       </c>
@@ -13773,11 +13785,11 @@
       <c r="R115" s="32"/>
     </row>
     <row r="116" spans="1:18" ht="12">
-      <c r="A116" s="86" t="s">
+      <c r="A116" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="86"/>
-      <c r="C116" s="86"/>
+      <c r="B116" s="88"/>
+      <c r="C116" s="88"/>
       <c r="D116" s="38">
         <v>0</v>
       </c>
@@ -13825,11 +13837,11 @@
       <c r="R116" s="32"/>
     </row>
     <row r="117" spans="1:18" ht="12">
-      <c r="A117" s="85" t="s">
+      <c r="A117" s="87" t="s">
         <v>109</v>
       </c>
-      <c r="B117" s="85"/>
-      <c r="C117" s="85"/>
+      <c r="B117" s="87"/>
+      <c r="C117" s="87"/>
       <c r="D117" s="35">
         <v>96.89</v>
       </c>
@@ -13877,11 +13889,11 @@
       <c r="R117" s="32"/>
     </row>
     <row r="118" spans="1:18" ht="12">
-      <c r="A118" s="86" t="s">
+      <c r="A118" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="B118" s="86"/>
-      <c r="C118" s="86"/>
+      <c r="B118" s="88"/>
+      <c r="C118" s="88"/>
       <c r="D118" s="38">
         <v>34.9</v>
       </c>
@@ -13929,11 +13941,11 @@
       <c r="R118" s="32"/>
     </row>
     <row r="119" spans="1:18" ht="12">
-      <c r="A119" s="85" t="s">
+      <c r="A119" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="B119" s="85"/>
-      <c r="C119" s="85"/>
+      <c r="B119" s="87"/>
+      <c r="C119" s="87"/>
       <c r="D119" s="35">
         <v>730</v>
       </c>
@@ -13981,11 +13993,11 @@
       <c r="R119" s="32"/>
     </row>
     <row r="120" spans="1:18" ht="12">
-      <c r="A120" s="86" t="s">
+      <c r="A120" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="B120" s="86"/>
-      <c r="C120" s="86"/>
+      <c r="B120" s="88"/>
+      <c r="C120" s="88"/>
       <c r="D120" s="38">
         <v>1447.2</v>
       </c>
@@ -14033,11 +14045,11 @@
       <c r="R120" s="32"/>
     </row>
     <row r="121" spans="1:18" ht="12">
-      <c r="A121" s="89" t="s">
+      <c r="A121" s="90" t="s">
         <v>151</v>
       </c>
-      <c r="B121" s="89"/>
-      <c r="C121" s="89"/>
+      <c r="B121" s="90"/>
+      <c r="C121" s="90"/>
       <c r="D121" s="41">
         <f>SUM(D122:D139)</f>
         <v>24167.069999999996</v>
@@ -14097,11 +14109,11 @@
       <c r="R121" s="32"/>
     </row>
     <row r="122" spans="1:18" ht="12">
-      <c r="A122" s="86" t="s">
+      <c r="A122" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="B122" s="86"/>
-      <c r="C122" s="86"/>
+      <c r="B122" s="88"/>
+      <c r="C122" s="88"/>
       <c r="D122" s="38">
         <v>142.21</v>
       </c>
@@ -14149,11 +14161,11 @@
       <c r="R122" s="32"/>
     </row>
     <row r="123" spans="1:18" ht="12">
-      <c r="A123" s="85" t="s">
+      <c r="A123" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="B123" s="85"/>
-      <c r="C123" s="85"/>
+      <c r="B123" s="87"/>
+      <c r="C123" s="87"/>
       <c r="D123" s="35">
         <v>0</v>
       </c>
@@ -14201,11 +14213,11 @@
       <c r="R123" s="32"/>
     </row>
     <row r="124" spans="1:18" ht="12">
-      <c r="A124" s="86" t="s">
+      <c r="A124" s="88" t="s">
         <v>154</v>
       </c>
-      <c r="B124" s="86"/>
-      <c r="C124" s="86"/>
+      <c r="B124" s="88"/>
+      <c r="C124" s="88"/>
       <c r="D124" s="38">
         <v>0</v>
       </c>
@@ -14253,11 +14265,11 @@
       <c r="R124" s="32"/>
     </row>
     <row r="125" spans="1:18" ht="12">
-      <c r="A125" s="85" t="s">
+      <c r="A125" s="87" t="s">
         <v>155</v>
       </c>
-      <c r="B125" s="85"/>
-      <c r="C125" s="85"/>
+      <c r="B125" s="87"/>
+      <c r="C125" s="87"/>
       <c r="D125" s="35">
         <v>0</v>
       </c>
@@ -14305,11 +14317,11 @@
       <c r="R125" s="32"/>
     </row>
     <row r="126" spans="1:18" ht="12">
-      <c r="A126" s="86" t="s">
+      <c r="A126" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="B126" s="86"/>
-      <c r="C126" s="86"/>
+      <c r="B126" s="88"/>
+      <c r="C126" s="88"/>
       <c r="D126" s="38">
         <v>0</v>
       </c>
@@ -14357,11 +14369,11 @@
       <c r="R126" s="32"/>
     </row>
     <row r="127" spans="1:18" ht="12">
-      <c r="A127" s="85" t="s">
+      <c r="A127" s="87" t="s">
         <v>157</v>
       </c>
-      <c r="B127" s="85"/>
-      <c r="C127" s="85"/>
+      <c r="B127" s="87"/>
+      <c r="C127" s="87"/>
       <c r="D127" s="35">
         <v>0</v>
       </c>
@@ -14409,11 +14421,11 @@
       <c r="R127" s="32"/>
     </row>
     <row r="128" spans="1:18" ht="12">
-      <c r="A128" s="86" t="s">
+      <c r="A128" s="88" t="s">
         <v>158</v>
       </c>
-      <c r="B128" s="86"/>
-      <c r="C128" s="86"/>
+      <c r="B128" s="88"/>
+      <c r="C128" s="88"/>
       <c r="D128" s="38">
         <v>0</v>
       </c>
@@ -14461,11 +14473,11 @@
       <c r="R128" s="32"/>
     </row>
     <row r="129" spans="1:20" ht="12">
-      <c r="A129" s="85" t="s">
+      <c r="A129" s="87" t="s">
         <v>159</v>
       </c>
-      <c r="B129" s="85"/>
-      <c r="C129" s="85"/>
+      <c r="B129" s="87"/>
+      <c r="C129" s="87"/>
       <c r="D129" s="35">
         <v>6364.55</v>
       </c>
@@ -14513,11 +14525,11 @@
       <c r="R129" s="32"/>
     </row>
     <row r="130" spans="1:20" s="51" customFormat="1" ht="12">
-      <c r="A130" s="91" t="s">
+      <c r="A130" s="89" t="s">
         <v>160</v>
       </c>
-      <c r="B130" s="91"/>
-      <c r="C130" s="91"/>
+      <c r="B130" s="89"/>
+      <c r="C130" s="89"/>
       <c r="D130" s="48">
         <v>0</v>
       </c>
@@ -14565,11 +14577,11 @@
       <c r="R130" s="50"/>
     </row>
     <row r="131" spans="1:20" ht="12">
-      <c r="A131" s="85" t="s">
+      <c r="A131" s="87" t="s">
         <v>161</v>
       </c>
-      <c r="B131" s="85"/>
-      <c r="C131" s="85"/>
+      <c r="B131" s="87"/>
+      <c r="C131" s="87"/>
       <c r="D131" s="35">
         <v>0</v>
       </c>
@@ -14617,11 +14629,11 @@
       <c r="R131" s="32"/>
     </row>
     <row r="132" spans="1:20" ht="12">
-      <c r="A132" s="86" t="s">
+      <c r="A132" s="88" t="s">
         <v>162</v>
       </c>
-      <c r="B132" s="86"/>
-      <c r="C132" s="86"/>
+      <c r="B132" s="88"/>
+      <c r="C132" s="88"/>
       <c r="D132" s="38">
         <v>17153.759999999998</v>
       </c>
@@ -14669,11 +14681,11 @@
       <c r="R132" s="32"/>
     </row>
     <row r="133" spans="1:20" ht="12">
-      <c r="A133" s="91" t="s">
+      <c r="A133" s="89" t="s">
         <v>163</v>
       </c>
-      <c r="B133" s="91"/>
-      <c r="C133" s="91"/>
+      <c r="B133" s="89"/>
+      <c r="C133" s="89"/>
       <c r="D133" s="35">
         <v>0</v>
       </c>
@@ -14721,11 +14733,11 @@
       <c r="R133" s="32"/>
     </row>
     <row r="134" spans="1:20" ht="12">
-      <c r="A134" s="86" t="s">
+      <c r="A134" s="88" t="s">
         <v>164</v>
       </c>
-      <c r="B134" s="86"/>
-      <c r="C134" s="86"/>
+      <c r="B134" s="88"/>
+      <c r="C134" s="88"/>
       <c r="D134" s="38">
         <v>506.55</v>
       </c>
@@ -14777,11 +14789,11 @@
       </c>
     </row>
     <row r="135" spans="1:20" ht="12">
-      <c r="A135" s="85" t="s">
+      <c r="A135" s="87" t="s">
         <v>165</v>
       </c>
-      <c r="B135" s="85"/>
-      <c r="C135" s="85"/>
+      <c r="B135" s="87"/>
+      <c r="C135" s="87"/>
       <c r="D135" s="35">
         <v>0</v>
       </c>
@@ -14829,11 +14841,11 @@
       <c r="R135" s="32"/>
     </row>
     <row r="136" spans="1:20" ht="12">
-      <c r="A136" s="86" t="s">
+      <c r="A136" s="88" t="s">
         <v>166</v>
       </c>
-      <c r="B136" s="86"/>
-      <c r="C136" s="86"/>
+      <c r="B136" s="88"/>
+      <c r="C136" s="88"/>
       <c r="D136" s="38">
         <v>0</v>
       </c>
@@ -14881,11 +14893,11 @@
       <c r="R136" s="32"/>
     </row>
     <row r="137" spans="1:20" ht="12">
-      <c r="A137" s="85" t="s">
+      <c r="A137" s="87" t="s">
         <v>167</v>
       </c>
-      <c r="B137" s="85"/>
-      <c r="C137" s="85"/>
+      <c r="B137" s="87"/>
+      <c r="C137" s="87"/>
       <c r="D137" s="35">
         <v>0</v>
       </c>
@@ -14933,11 +14945,11 @@
       <c r="R137" s="32"/>
     </row>
     <row r="138" spans="1:20" ht="12">
-      <c r="A138" s="86" t="s">
+      <c r="A138" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="B138" s="86"/>
-      <c r="C138" s="86"/>
+      <c r="B138" s="88"/>
+      <c r="C138" s="88"/>
       <c r="D138" s="38">
         <v>0</v>
       </c>
@@ -14985,11 +14997,11 @@
       <c r="R138" s="32"/>
     </row>
     <row r="139" spans="1:20" ht="12">
-      <c r="A139" s="85" t="s">
+      <c r="A139" s="87" t="s">
         <v>169</v>
       </c>
-      <c r="B139" s="85"/>
-      <c r="C139" s="85"/>
+      <c r="B139" s="87"/>
+      <c r="C139" s="87"/>
       <c r="D139" s="35">
         <v>0</v>
       </c>
@@ -15037,11 +15049,11 @@
       <c r="R139" s="32"/>
     </row>
     <row r="140" spans="1:20" ht="12">
-      <c r="A140" s="90" t="s">
+      <c r="A140" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="B140" s="90"/>
-      <c r="C140" s="90"/>
+      <c r="B140" s="86"/>
+      <c r="C140" s="86"/>
       <c r="D140" s="39">
         <f>D26</f>
         <v>308825.78999999998</v>
@@ -15162,132 +15174,6 @@
     <row r="181" ht="12"/>
   </sheetData>
   <mergeCells count="140">
-    <mergeCell ref="A140:C140"/>
-    <mergeCell ref="A139:C139"/>
-    <mergeCell ref="A138:C138"/>
-    <mergeCell ref="A137:C137"/>
-    <mergeCell ref="A136:C136"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A134:C134"/>
-    <mergeCell ref="A133:C133"/>
-    <mergeCell ref="A132:C132"/>
-    <mergeCell ref="A131:C131"/>
-    <mergeCell ref="A130:C130"/>
-    <mergeCell ref="A129:C129"/>
-    <mergeCell ref="A128:C128"/>
-    <mergeCell ref="A127:C127"/>
-    <mergeCell ref="A126:C126"/>
-    <mergeCell ref="A125:C125"/>
-    <mergeCell ref="A124:C124"/>
-    <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A3:C3"/>
@@ -15302,6 +15188,132 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A116:C116"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A131:C131"/>
+    <mergeCell ref="A130:C130"/>
+    <mergeCell ref="A129:C129"/>
+    <mergeCell ref="A128:C128"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="A125:C125"/>
+    <mergeCell ref="A124:C124"/>
+    <mergeCell ref="A123:C123"/>
+    <mergeCell ref="A140:C140"/>
+    <mergeCell ref="A139:C139"/>
+    <mergeCell ref="A138:C138"/>
+    <mergeCell ref="A137:C137"/>
+    <mergeCell ref="A136:C136"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A134:C134"/>
+    <mergeCell ref="A133:C133"/>
+    <mergeCell ref="A132:C132"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -15313,7 +15325,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="C1:V137"/>
+  <dimension ref="C1:X137"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="1"/>
@@ -15327,57 +15339,58 @@
     <col min="21" max="21" width="0" style="1" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="11.109375" style="1" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.109375" style="1"/>
+    <col min="24" max="24" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
+      <c r="C1" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
+      <c r="M1" s="68"/>
+      <c r="N1" s="68"/>
+      <c r="O1" s="68"/>
+      <c r="P1" s="68"/>
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
     </row>
     <row r="2" spans="3:22" ht="19.5" customHeight="1">
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="69"/>
+      <c r="N2" s="69"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="69"/>
+      <c r="Q2" s="69"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="69"/>
     </row>
     <row r="3" spans="3:22" ht="16.5" customHeight="1">
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="72"/>
       <c r="F3" s="31" t="s">
         <v>3</v>
       </c>
@@ -15423,11 +15436,11 @@
       <c r="T3" s="32"/>
     </row>
     <row r="4" spans="3:22" ht="12">
-      <c r="C4" s="84" t="s">
+      <c r="C4" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="23" t="e">
         <f>F5+F22+F38+F78+F86+#REF!</f>
         <v>#REF!</v>
@@ -15552,11 +15565,11 @@
       </c>
     </row>
     <row r="6" spans="3:22" ht="12">
-      <c r="C6" s="69" t="s">
+      <c r="C6" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="69"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
       <c r="F6" s="3">
         <v>34</v>
       </c>
@@ -15613,11 +15626,11 @@
       <c r="T6" s="5"/>
     </row>
     <row r="7" spans="3:22" ht="12">
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
       <c r="F7" s="3">
         <f>'REALIZADO 2025'!D29*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15677,11 +15690,11 @@
       <c r="T7" s="5"/>
     </row>
     <row r="8" spans="3:22" ht="12">
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="69"/>
-      <c r="E8" s="69"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
       <c r="F8" s="3">
         <f>'REALIZADO 2025'!D30*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15741,11 +15754,11 @@
       <c r="T8" s="5"/>
     </row>
     <row r="9" spans="3:22" ht="12">
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="69"/>
-      <c r="E9" s="69"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
       <c r="F9" s="3">
         <f>'REALIZADO 2025'!D31*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15805,11 +15818,11 @@
       <c r="T9" s="5"/>
     </row>
     <row r="10" spans="3:22" ht="12">
-      <c r="C10" s="69" t="s">
+      <c r="C10" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
       <c r="F10" s="3">
         <f>'REALIZADO 2025'!D34*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -15869,11 +15882,11 @@
       <c r="T10" s="5"/>
     </row>
     <row r="11" spans="3:22" ht="12">
-      <c r="C11" s="69" t="s">
+      <c r="C11" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="69"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
       <c r="F11" s="3">
         <f>'REALIZADO 2025'!D35*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>372.17674999999997</v>
@@ -15933,11 +15946,11 @@
       <c r="T11" s="5"/>
     </row>
     <row r="12" spans="3:22" ht="12">
-      <c r="C12" s="69" t="s">
+      <c r="C12" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="69"/>
-      <c r="E12" s="69"/>
+      <c r="D12" s="75"/>
+      <c r="E12" s="75"/>
       <c r="F12" s="3">
         <f>'REALIZADO 2025'!D36*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>522.5</v>
@@ -15997,11 +16010,11 @@
       <c r="T12" s="5"/>
     </row>
     <row r="13" spans="3:22" ht="12">
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="69"/>
-      <c r="E13" s="69"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
       <c r="F13" s="3">
         <f>'REALIZADO 2025'!D37*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16061,11 +16074,11 @@
       <c r="T13" s="5"/>
     </row>
     <row r="14" spans="3:22" ht="12">
-      <c r="C14" s="69" t="s">
+      <c r="C14" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
       <c r="F14" s="3">
         <f t="shared" ref="F14:Q14" si="3">5043.17*$U$4</f>
         <v>5270.11265</v>
@@ -16125,11 +16138,11 @@
       <c r="T14" s="5"/>
     </row>
     <row r="15" spans="3:22" ht="12">
-      <c r="C15" s="69" t="s">
+      <c r="C15" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="69"/>
-      <c r="E15" s="69"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
       <c r="F15" s="3">
         <f t="shared" ref="F15:Q15" si="4">2570.4*$U$4</f>
         <v>2686.0679999999998</v>
@@ -16189,11 +16202,11 @@
       <c r="T15" s="5"/>
     </row>
     <row r="16" spans="3:22" ht="12">
-      <c r="C16" s="69" t="s">
+      <c r="C16" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="75"/>
       <c r="F16" s="3">
         <f>'REALIZADO 2025'!D40*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16253,11 +16266,11 @@
       <c r="T16" s="5"/>
     </row>
     <row r="17" spans="3:22" ht="12">
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="69"/>
-      <c r="E17" s="69"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="75"/>
       <c r="F17" s="3">
         <f>'REALIZADO 2025'!D41*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16317,11 +16330,11 @@
       <c r="T17" s="5"/>
     </row>
     <row r="18" spans="3:22" ht="12">
-      <c r="C18" s="69" t="s">
+      <c r="C18" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="69"/>
-      <c r="E18" s="69"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
       <c r="F18" s="3">
         <f>'REALIZADO 2025'!D42*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16381,11 +16394,11 @@
       <c r="T18" s="5"/>
     </row>
     <row r="19" spans="3:22" ht="12">
-      <c r="C19" s="69" t="s">
+      <c r="C19" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="69"/>
-      <c r="E19" s="69"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
       <c r="F19" s="3">
         <f>'REALIZADO 2025'!D43*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16445,11 +16458,11 @@
       <c r="T19" s="5"/>
     </row>
     <row r="20" spans="3:22" ht="12">
-      <c r="C20" s="69" t="s">
+      <c r="C20" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="69"/>
-      <c r="E20" s="69"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="75"/>
       <c r="F20" s="3">
         <f>'REALIZADO 2025'!D44*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>252.50334999999998</v>
@@ -16509,11 +16522,11 @@
       <c r="T20" s="5"/>
     </row>
     <row r="21" spans="3:22" ht="12">
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="69"/>
-      <c r="E21" s="69"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
       <c r="F21" s="3">
         <f>'REALIZADO 2025'!D45*'PREVISTO 2026 REVISADO (2)'!$U$4</f>
         <v>0</v>
@@ -16573,11 +16586,11 @@
       <c r="T21" s="5"/>
     </row>
     <row r="22" spans="3:22" ht="12">
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
       <c r="F22" s="7">
         <f>SUM(F23:F37)</f>
         <v>154479.97080000001</v>
@@ -16645,11 +16658,11 @@
       </c>
     </row>
     <row r="23" spans="3:22" ht="12">
-      <c r="C23" s="69" t="s">
+      <c r="C23" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
       <c r="F23" s="3">
         <f>'REALIZADO 2025'!D47*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>52560.36</v>
@@ -16709,11 +16722,11 @@
       <c r="T23" s="5"/>
     </row>
     <row r="24" spans="3:22" ht="12">
-      <c r="C24" s="69" t="s">
+      <c r="C24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="69"/>
-      <c r="E24" s="69"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
       <c r="F24" s="3">
         <f>'REALIZADO 2025'!D48*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>23252.497200000002</v>
@@ -16773,11 +16786,11 @@
       <c r="T24" s="5"/>
     </row>
     <row r="25" spans="3:22" ht="12">
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="69"/>
-      <c r="E25" s="69"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
       <c r="F25" s="3">
         <f>'REALIZADO 2025'!D49*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>77.652000000000015</v>
@@ -16836,11 +16849,11 @@
       <c r="T25" s="5"/>
     </row>
     <row r="26" spans="3:22" ht="12">
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
       <c r="F26" s="3">
         <f>'REALIZADO 2025'!D50*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>266.14440000000002</v>
@@ -16900,11 +16913,11 @@
       <c r="T26" s="5"/>
     </row>
     <row r="27" spans="3:22" ht="12">
-      <c r="C27" s="69" t="s">
+      <c r="C27" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
       <c r="F27" s="3">
         <f>'REALIZADO 2025'!D51*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -16964,11 +16977,11 @@
       <c r="T27" s="5"/>
     </row>
     <row r="28" spans="3:22" ht="12">
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="69"/>
-      <c r="E28" s="69"/>
+      <c r="D28" s="75"/>
+      <c r="E28" s="75"/>
       <c r="F28" s="3">
         <f>'REALIZADO 2025'!D52*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>3033.6120000000001</v>
@@ -17028,11 +17041,11 @@
       <c r="T28" s="5"/>
     </row>
     <row r="29" spans="3:22" ht="12">
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
+      <c r="D29" s="75"/>
+      <c r="E29" s="75"/>
       <c r="F29" s="3">
         <f>'REALIZADO 2025'!D53*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>319.59360000000004</v>
@@ -17092,11 +17105,11 @@
       <c r="T29" s="5"/>
     </row>
     <row r="30" spans="3:22" ht="12">
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="69"/>
-      <c r="E30" s="69"/>
+      <c r="D30" s="75"/>
+      <c r="E30" s="75"/>
       <c r="F30" s="3">
         <f>'REALIZADO 2025'!D54*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>324</v>
@@ -17156,11 +17169,11 @@
       <c r="T30" s="5"/>
     </row>
     <row r="31" spans="3:22" ht="12">
-      <c r="C31" s="69" t="s">
+      <c r="C31" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="69"/>
-      <c r="E31" s="69"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
       <c r="F31" s="3">
         <f>'REALIZADO 2025'!D55*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -17220,11 +17233,11 @@
       <c r="T31" s="5"/>
     </row>
     <row r="32" spans="3:22" ht="12">
-      <c r="C32" s="69" t="s">
+      <c r="C32" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="69"/>
-      <c r="E32" s="69"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
       <c r="F32" s="3">
         <f>'REALIZADO 2025'!D57*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>26005.406400000003</v>
@@ -17284,11 +17297,11 @@
       <c r="T32" s="5"/>
     </row>
     <row r="33" spans="3:22" ht="12">
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="69"/>
-      <c r="E33" s="69"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
       <c r="F33" s="3">
         <f>'REALIZADO 2025'!D58*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>5940.0108000000009</v>
@@ -17348,11 +17361,11 @@
       <c r="T33" s="5"/>
     </row>
     <row r="34" spans="3:22" ht="12">
-      <c r="C34" s="69" t="s">
+      <c r="C34" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
       <c r="F34" s="3">
         <f>'REALIZADO 2025'!D59*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -17412,11 +17425,11 @@
       <c r="T34" s="5"/>
     </row>
     <row r="35" spans="3:22" ht="12">
-      <c r="C35" s="69" t="s">
+      <c r="C35" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="D35" s="69"/>
-      <c r="E35" s="69"/>
+      <c r="D35" s="75"/>
+      <c r="E35" s="75"/>
       <c r="F35" s="3">
         <f>'REALIZADO 2025'!D60*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>41884.214400000004</v>
@@ -17476,11 +17489,11 @@
       <c r="T35" s="5"/>
     </row>
     <row r="36" spans="3:22" ht="12">
-      <c r="C36" s="69" t="s">
+      <c r="C36" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="69"/>
-      <c r="E36" s="69"/>
+      <c r="D36" s="75"/>
+      <c r="E36" s="75"/>
       <c r="F36" s="3">
         <f>'REALIZADO 2025'!D61*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>0</v>
@@ -17539,11 +17552,11 @@
       <c r="T36" s="5"/>
     </row>
     <row r="37" spans="3:22" ht="12">
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="75"/>
       <c r="F37" s="3">
         <f>'REALIZADO 2025'!D62*'PREVISTO 2026 REVISADO (2)'!$U$22</f>
         <v>816.48</v>
@@ -17603,11 +17616,11 @@
       <c r="T37" s="5"/>
     </row>
     <row r="38" spans="3:22" ht="12.75" customHeight="1">
-      <c r="C38" s="78" t="s">
+      <c r="C38" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="76"/>
       <c r="F38" s="7">
         <f t="shared" ref="F38:R38" si="7">F39+F55+F68+F72</f>
         <v>48895.278299999998</v>
@@ -17740,11 +17753,11 @@
       <c r="V39" s="58"/>
     </row>
     <row r="40" spans="3:22" ht="12">
-      <c r="C40" s="69" t="s">
+      <c r="C40" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
+      <c r="D40" s="75"/>
+      <c r="E40" s="75"/>
       <c r="F40" s="3">
         <f>'REALIZADO 2025'!D65*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1550.68595</v>
@@ -17804,11 +17817,11 @@
       <c r="V40" s="58"/>
     </row>
     <row r="41" spans="3:22" ht="12">
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
+      <c r="D41" s="75"/>
+      <c r="E41" s="75"/>
       <c r="F41" s="3">
         <f>'REALIZADO 2025'!D67*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -17869,11 +17882,11 @@
       <c r="V41" s="58"/>
     </row>
     <row r="42" spans="3:22" ht="12">
-      <c r="C42" s="69" t="s">
+      <c r="C42" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
       <c r="F42" s="3">
         <f>'REALIZADO 2025'!D68*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>3193.8857499999995</v>
@@ -17933,11 +17946,11 @@
       <c r="V42" s="58"/>
     </row>
     <row r="43" spans="3:22" ht="12">
-      <c r="C43" s="69" t="s">
+      <c r="C43" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="D43" s="69"/>
-      <c r="E43" s="69"/>
+      <c r="D43" s="75"/>
+      <c r="E43" s="75"/>
       <c r="F43" s="3">
         <f>'REALIZADO 2025'!D69*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>610.80250000000001</v>
@@ -17996,11 +18009,11 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="3:22" ht="12">
-      <c r="C44" s="69" t="s">
+      <c r="C44" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
+      <c r="D44" s="75"/>
+      <c r="E44" s="75"/>
       <c r="F44" s="3">
         <f>'REALIZADO 2025'!D70*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>554.51879999999994</v>
@@ -18060,11 +18073,11 @@
       <c r="T44" s="5"/>
     </row>
     <row r="45" spans="3:22" ht="12">
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
+      <c r="D45" s="75"/>
+      <c r="E45" s="75"/>
       <c r="F45" s="3">
         <f>'REALIZADO 2025'!D71*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18124,11 +18137,11 @@
       <c r="T45" s="5"/>
     </row>
     <row r="46" spans="3:22" ht="12">
-      <c r="C46" s="69" t="s">
+      <c r="C46" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="D46" s="69"/>
-      <c r="E46" s="69"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="75"/>
       <c r="F46" s="3">
         <f>'REALIZADO 2025'!D72*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>5500.8486499999999</v>
@@ -18187,11 +18200,11 @@
       <c r="T46" s="5"/>
     </row>
     <row r="47" spans="3:22" ht="12">
-      <c r="C47" s="77" t="s">
+      <c r="C47" s="79" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
+      <c r="D47" s="79"/>
+      <c r="E47" s="79"/>
       <c r="F47" s="3">
         <f>'REALIZADO 2025'!D73*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>349.70924999999994</v>
@@ -18250,11 +18263,11 @@
       <c r="T47" s="5"/>
     </row>
     <row r="48" spans="3:22" ht="12">
-      <c r="C48" s="69" t="s">
+      <c r="C48" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="69"/>
-      <c r="E48" s="69"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
       <c r="F48" s="3">
         <f>'REALIZADO 2025'!D74*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>12.54</v>
@@ -18314,11 +18327,11 @@
       <c r="T48" s="5"/>
     </row>
     <row r="49" spans="3:20" ht="12">
-      <c r="C49" s="75" t="s">
+      <c r="C49" s="77" t="s">
         <v>63</v>
       </c>
-      <c r="D49" s="76"/>
-      <c r="E49" s="76"/>
+      <c r="D49" s="78"/>
+      <c r="E49" s="78"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
@@ -18341,11 +18354,11 @@
       <c r="T49" s="5"/>
     </row>
     <row r="50" spans="3:20" ht="12">
-      <c r="C50" s="75" t="s">
+      <c r="C50" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="D50" s="76"/>
-      <c r="E50" s="76"/>
+      <c r="D50" s="78"/>
+      <c r="E50" s="78"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
@@ -18368,11 +18381,11 @@
       <c r="T50" s="5"/>
     </row>
     <row r="51" spans="3:20" ht="12">
-      <c r="C51" s="75" t="s">
+      <c r="C51" s="77" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="76"/>
-      <c r="E51" s="76"/>
+      <c r="D51" s="78"/>
+      <c r="E51" s="78"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
@@ -18395,11 +18408,11 @@
       <c r="T51" s="5"/>
     </row>
     <row r="52" spans="3:20" ht="12">
-      <c r="C52" s="75" t="s">
+      <c r="C52" s="77" t="s">
         <v>66</v>
       </c>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="78"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -18422,11 +18435,11 @@
       <c r="T52" s="5"/>
     </row>
     <row r="53" spans="3:20" ht="12">
-      <c r="C53" s="75" t="s">
+      <c r="C53" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="76"/>
-      <c r="E53" s="76"/>
+      <c r="D53" s="78"/>
+      <c r="E53" s="78"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -18449,11 +18462,11 @@
       <c r="T53" s="5"/>
     </row>
     <row r="54" spans="3:20" ht="12">
-      <c r="C54" s="75" t="s">
+      <c r="C54" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="D54" s="75"/>
-      <c r="E54" s="75"/>
+      <c r="D54" s="77"/>
+      <c r="E54" s="77"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
@@ -18540,11 +18553,11 @@
       <c r="T55" s="5"/>
     </row>
     <row r="56" spans="3:20" ht="12">
-      <c r="C56" s="69" t="s">
+      <c r="C56" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="D56" s="69"/>
-      <c r="E56" s="69"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
       <c r="F56" s="3">
         <f>'REALIZADO 2025'!D76*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1201.7082</v>
@@ -18604,11 +18617,11 @@
       <c r="T56" s="5"/>
     </row>
     <row r="57" spans="3:20" ht="12">
-      <c r="C57" s="69" t="s">
+      <c r="C57" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="D57" s="69"/>
-      <c r="E57" s="69"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
       <c r="F57" s="3">
         <f>'REALIZADO 2025'!D77*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18668,11 +18681,11 @@
       <c r="T57" s="5"/>
     </row>
     <row r="58" spans="3:20" ht="12">
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="69"/>
-      <c r="E58" s="69"/>
+      <c r="D58" s="75"/>
+      <c r="E58" s="75"/>
       <c r="F58" s="3">
         <f>'REALIZADO 2025'!D78*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>888.24999999999989</v>
@@ -18732,11 +18745,11 @@
       <c r="T58" s="5"/>
     </row>
     <row r="59" spans="3:20" ht="12">
-      <c r="C59" s="69" t="s">
+      <c r="C59" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="D59" s="69"/>
-      <c r="E59" s="69"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
       <c r="F59" s="3">
         <f>'REALIZADO 2025'!D79*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18796,11 +18809,11 @@
       <c r="T59" s="5"/>
     </row>
     <row r="60" spans="3:20" ht="12">
-      <c r="C60" s="69" t="s">
+      <c r="C60" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="69"/>
-      <c r="E60" s="69"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
       <c r="F60" s="3">
         <f>'REALIZADO 2025'!D80*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2080.5113999999999</v>
@@ -18859,11 +18872,11 @@
       <c r="T60" s="5"/>
     </row>
     <row r="61" spans="3:20" ht="12">
-      <c r="C61" s="69" t="s">
+      <c r="C61" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="D61" s="69"/>
-      <c r="E61" s="69"/>
+      <c r="D61" s="75"/>
+      <c r="E61" s="75"/>
       <c r="F61" s="3">
         <f>'REALIZADO 2025'!D81*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -18923,11 +18936,11 @@
       <c r="T61" s="5"/>
     </row>
     <row r="62" spans="3:20" ht="12">
-      <c r="C62" s="69" t="s">
+      <c r="C62" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="D62" s="69"/>
-      <c r="E62" s="69"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
       <c r="F62" s="3">
         <f>'REALIZADO 2025'!D82*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>7691.6597999999994</v>
@@ -18987,11 +19000,11 @@
       <c r="T62" s="5"/>
     </row>
     <row r="63" spans="3:20" ht="12">
-      <c r="C63" s="69" t="s">
+      <c r="C63" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="D63" s="69"/>
-      <c r="E63" s="69"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
       <c r="F63" s="3">
         <f>'REALIZADO 2025'!D83*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1149.5</v>
@@ -19050,11 +19063,11 @@
       <c r="T63" s="5"/>
     </row>
     <row r="64" spans="3:20" ht="12">
-      <c r="C64" s="69" t="s">
+      <c r="C64" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="D64" s="69"/>
-      <c r="E64" s="69"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
       <c r="F64" s="3">
         <f>'REALIZADO 2025'!D84*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -19114,11 +19127,11 @@
       <c r="T64" s="5"/>
     </row>
     <row r="65" spans="3:21" ht="12">
-      <c r="C65" s="69" t="s">
+      <c r="C65" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="D65" s="69"/>
-      <c r="E65" s="69"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="75"/>
       <c r="F65" s="3">
         <f>'REALIZADO 2025'!D85*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>58.310999999999993</v>
@@ -19178,11 +19191,11 @@
       <c r="T65" s="5"/>
     </row>
     <row r="66" spans="3:21" ht="12">
-      <c r="C66" s="69" t="s">
+      <c r="C66" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="D66" s="69"/>
-      <c r="E66" s="69"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
       <c r="F66" s="3">
         <f>'REALIZADO 2025'!D86*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -19242,11 +19255,11 @@
       <c r="T66" s="5"/>
     </row>
     <row r="67" spans="3:21" ht="12">
-      <c r="C67" s="69" t="s">
+      <c r="C67" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="D67" s="69"/>
-      <c r="E67" s="69"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
       <c r="F67" s="3">
         <f>'REALIZADO 2025'!D87*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>0</v>
@@ -19370,11 +19383,11 @@
       <c r="T68" s="5"/>
     </row>
     <row r="69" spans="3:21" ht="12">
-      <c r="C69" s="69" t="s">
+      <c r="C69" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="69"/>
-      <c r="E69" s="69"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
       <c r="F69" s="3">
         <f>'REALIZADO 2025'!D89*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>6040.6224999999995</v>
@@ -19434,11 +19447,11 @@
       <c r="T69" s="5"/>
     </row>
     <row r="70" spans="3:21" ht="12">
-      <c r="C70" s="69" t="s">
+      <c r="C70" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="69"/>
-      <c r="E70" s="69"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
       <c r="F70" s="3">
         <f>'REALIZADO 2025'!D90*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>7357.8449999999993</v>
@@ -19497,11 +19510,11 @@
       <c r="T70" s="5"/>
     </row>
     <row r="71" spans="3:21" ht="12">
-      <c r="C71" s="69" t="s">
+      <c r="C71" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="D71" s="69"/>
-      <c r="E71" s="69"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
       <c r="F71" s="3">
         <f>'REALIZADO 2025'!D91*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2733.72</v>
@@ -19625,11 +19638,11 @@
       <c r="T72" s="5"/>
     </row>
     <row r="73" spans="3:21" ht="12">
-      <c r="C73" s="69" t="s">
+      <c r="C73" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="D73" s="69"/>
-      <c r="E73" s="69"/>
+      <c r="D73" s="75"/>
+      <c r="E73" s="75"/>
       <c r="F73" s="3">
         <f>'REALIZADO 2025'!D93*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>909.15</v>
@@ -19689,11 +19702,11 @@
       <c r="T73" s="5"/>
     </row>
     <row r="74" spans="3:21" ht="12">
-      <c r="C74" s="69" t="s">
+      <c r="C74" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="D74" s="69"/>
-      <c r="E74" s="69"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
       <c r="F74" s="3">
         <f>'REALIZADO 2025'!D94*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>752.4</v>
@@ -19753,11 +19766,11 @@
       <c r="T74" s="5"/>
     </row>
     <row r="75" spans="3:21" ht="12">
-      <c r="C75" s="69" t="s">
+      <c r="C75" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="D75" s="69"/>
-      <c r="E75" s="69"/>
+      <c r="D75" s="75"/>
+      <c r="E75" s="75"/>
       <c r="F75" s="3">
         <f>'REALIZADO 2025'!D95*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2403.5</v>
@@ -19817,11 +19830,11 @@
       <c r="T75" s="5"/>
     </row>
     <row r="76" spans="3:21" ht="12">
-      <c r="C76" s="69" t="s">
+      <c r="C76" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="D76" s="69"/>
-      <c r="E76" s="69"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
       <c r="F76" s="3">
         <f>'REALIZADO 2025'!D96*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>1472.5094999999999</v>
@@ -19880,11 +19893,11 @@
       <c r="T76" s="5"/>
     </row>
     <row r="77" spans="3:21" ht="12">
-      <c r="C77" s="69" t="s">
+      <c r="C77" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="D77" s="69"/>
-      <c r="E77" s="69"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
       <c r="F77" s="3">
         <f>'REALIZADO 2025'!D97*'PREVISTO 2026 REVISADO (2)'!$U$38</f>
         <v>2382.6</v>
@@ -20013,11 +20026,11 @@
       </c>
     </row>
     <row r="79" spans="3:21" ht="12">
-      <c r="C79" s="69" t="s">
+      <c r="C79" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="D79" s="69"/>
-      <c r="E79" s="69"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
       <c r="F79" s="3">
         <f>'REALIZADO 2025'!D99*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>4117.2999999999993</v>
@@ -20077,11 +20090,11 @@
       <c r="T79" s="5"/>
     </row>
     <row r="80" spans="3:21" ht="12">
-      <c r="C80" s="69" t="s">
+      <c r="C80" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="D80" s="69"/>
-      <c r="E80" s="69"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
       <c r="F80" s="3">
         <f>'REALIZADO 2025'!D100*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>2951.08</v>
@@ -20141,11 +20154,11 @@
       <c r="T80" s="5"/>
     </row>
     <row r="81" spans="3:21" ht="12">
-      <c r="C81" s="69" t="s">
+      <c r="C81" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="D81" s="69"/>
-      <c r="E81" s="69"/>
+      <c r="D81" s="75"/>
+      <c r="E81" s="75"/>
       <c r="F81" s="3">
         <f>'REALIZADO 2025'!D101*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>4270.2671</v>
@@ -20205,11 +20218,11 @@
       <c r="T81" s="5"/>
     </row>
     <row r="82" spans="3:21" ht="12">
-      <c r="C82" s="69" t="s">
+      <c r="C82" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D82" s="69"/>
-      <c r="E82" s="69"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="75"/>
       <c r="F82" s="3">
         <f>'REALIZADO 2025'!D102*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>58965.410349999998</v>
@@ -20269,11 +20282,11 @@
       <c r="T82" s="5"/>
     </row>
     <row r="83" spans="3:21" ht="12">
-      <c r="C83" s="69" t="s">
+      <c r="C83" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="D83" s="69"/>
-      <c r="E83" s="69"/>
+      <c r="D83" s="75"/>
+      <c r="E83" s="75"/>
       <c r="F83" s="3">
         <f>'REALIZADO 2025'!D103*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>0</v>
@@ -20333,11 +20346,11 @@
       <c r="T83" s="5"/>
     </row>
     <row r="84" spans="3:21" ht="12">
-      <c r="C84" s="69" t="s">
+      <c r="C84" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="D84" s="69"/>
-      <c r="E84" s="69"/>
+      <c r="D84" s="75"/>
+      <c r="E84" s="75"/>
       <c r="F84" s="3">
         <f>'REALIZADO 2025'!D104*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>2508</v>
@@ -20397,11 +20410,11 @@
       <c r="T84" s="5"/>
     </row>
     <row r="85" spans="3:21" ht="12">
-      <c r="C85" s="69" t="s">
+      <c r="C85" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="D85" s="69"/>
-      <c r="E85" s="69"/>
+      <c r="D85" s="75"/>
+      <c r="E85" s="75"/>
       <c r="F85" s="3">
         <f>'REALIZADO 2025'!D106*'PREVISTO 2026 REVISADO (2)'!$U$78</f>
         <v>1250.3425</v>
@@ -20467,51 +20480,51 @@
       <c r="D86" s="74"/>
       <c r="E86" s="74"/>
       <c r="F86" s="8">
-        <f>SUM(F87:F96)</f>
+        <f t="shared" ref="F86:Q86" si="15">SUM(F87:F96)</f>
         <v>13871.8943</v>
       </c>
       <c r="G86" s="8">
-        <f>SUM(G87:G96)</f>
+        <f t="shared" si="15"/>
         <v>20017.058599999997</v>
       </c>
       <c r="H86" s="8">
-        <f>SUM(H87:H96)</f>
+        <f t="shared" si="15"/>
         <v>18725.417699999995</v>
       </c>
       <c r="I86" s="8">
-        <f>SUM(I87:I96)</f>
+        <f t="shared" si="15"/>
         <v>7115.7602999999981</v>
       </c>
       <c r="J86" s="8">
-        <f>SUM(J87:J96)</f>
+        <f t="shared" si="15"/>
         <v>33776.176500000001</v>
       </c>
       <c r="K86" s="8">
-        <f>SUM(K87:K96)</f>
+        <f t="shared" si="15"/>
         <v>17102.8253</v>
       </c>
       <c r="L86" s="8">
-        <f>SUM(L87:L96)</f>
+        <f t="shared" si="15"/>
         <v>16127.474549999999</v>
       </c>
       <c r="M86" s="8">
-        <f>SUM(M87:M96)</f>
+        <f t="shared" si="15"/>
         <v>17502.4751</v>
       </c>
       <c r="N86" s="8">
-        <f>SUM(N87:N96)</f>
+        <f t="shared" si="15"/>
         <v>14729.24365</v>
       </c>
       <c r="O86" s="8">
-        <f>SUM(O87:O96)</f>
+        <f t="shared" si="15"/>
         <v>16369.684649999999</v>
       </c>
       <c r="P86" s="8">
-        <f>SUM(P87:P96)</f>
+        <f t="shared" si="15"/>
         <v>17673.928250000001</v>
       </c>
       <c r="Q86" s="8">
-        <f>SUM(Q87:Q96)</f>
+        <f t="shared" si="15"/>
         <v>9433.4449000000004</v>
       </c>
       <c r="R86" s="9">
@@ -20530,11 +20543,11 @@
       </c>
     </row>
     <row r="87" spans="3:21" ht="12">
-      <c r="C87" s="69" t="s">
+      <c r="C87" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="D87" s="69"/>
-      <c r="E87" s="69"/>
+      <c r="D87" s="75"/>
+      <c r="E87" s="75"/>
       <c r="F87" s="3">
         <f>'REALIZADO 2025'!D109*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>11147.161299999998</v>
@@ -20593,11 +20606,11 @@
       <c r="T87" s="5"/>
     </row>
     <row r="88" spans="3:21" ht="12">
-      <c r="C88" s="69" t="s">
+      <c r="C88" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="D88" s="69"/>
-      <c r="E88" s="69"/>
+      <c r="D88" s="75"/>
+      <c r="E88" s="75"/>
       <c r="F88" s="3">
         <f>'REALIZADO 2025'!D113*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
@@ -20657,11 +20670,11 @@
       <c r="T88" s="5"/>
     </row>
     <row r="89" spans="3:21" ht="12">
-      <c r="C89" s="69" t="s">
+      <c r="C89" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="75"/>
       <c r="F89" s="3">
         <f>'REALIZADO 2025'!D114*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>102.8489</v>
@@ -20721,11 +20734,11 @@
       <c r="T89" s="5"/>
     </row>
     <row r="90" spans="3:21" ht="12">
-      <c r="C90" s="69" t="s">
+      <c r="C90" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="D90" s="69"/>
-      <c r="E90" s="69"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="75"/>
       <c r="F90" s="3">
         <f>'REALIZADO 2025'!D115*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>208.98955000000001</v>
@@ -20785,11 +20798,11 @@
       <c r="T90" s="5"/>
     </row>
     <row r="92" spans="3:21" ht="12">
-      <c r="C92" s="69" t="s">
+      <c r="C92" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="D92" s="69"/>
-      <c r="E92" s="69"/>
+      <c r="D92" s="75"/>
+      <c r="E92" s="75"/>
       <c r="F92" s="3">
         <f>'REALIZADO 2025'!D116*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
@@ -20843,17 +20856,17 @@
         <v>1560.9269499999998</v>
       </c>
       <c r="S92" s="25">
-        <f>R92/12</f>
+        <f t="shared" ref="S92:S99" si="16">R92/12</f>
         <v>130.07724583333331</v>
       </c>
       <c r="T92" s="5"/>
     </row>
     <row r="93" spans="3:21" ht="12">
-      <c r="C93" s="69" t="s">
+      <c r="C93" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="D93" s="69"/>
-      <c r="E93" s="69"/>
+      <c r="D93" s="75"/>
+      <c r="E93" s="75"/>
       <c r="F93" s="3">
         <f>'REALIZADO 2025'!D117*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>101.25004999999999</v>
@@ -20907,17 +20920,17 @@
         <v>2371.5334499999994</v>
       </c>
       <c r="S93" s="25">
-        <f>R93/12</f>
+        <f t="shared" si="16"/>
         <v>197.62778749999995</v>
       </c>
       <c r="T93" s="5"/>
     </row>
     <row r="94" spans="3:21" ht="12" customHeight="1">
-      <c r="C94" s="69" t="s">
+      <c r="C94" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="D94" s="92"/>
-      <c r="E94" s="92"/>
+      <c r="D94" s="81"/>
+      <c r="E94" s="81"/>
       <c r="F94" s="3">
         <f>'REALIZADO 2025'!D118*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>36.470499999999994</v>
@@ -20971,17 +20984,17 @@
         <v>401.1755</v>
       </c>
       <c r="S94" s="25">
-        <f>R94/12</f>
+        <f t="shared" si="16"/>
         <v>33.431291666666667</v>
       </c>
       <c r="T94" s="5"/>
     </row>
     <row r="95" spans="3:21" ht="12" customHeight="1">
-      <c r="C95" s="69" t="s">
+      <c r="C95" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="D95" s="92"/>
-      <c r="E95" s="92"/>
+      <c r="D95" s="81"/>
+      <c r="E95" s="81"/>
       <c r="F95" s="3">
         <f>'REALIZADO 2025'!D119*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>762.84999999999991</v>
@@ -21035,17 +21048,17 @@
         <v>3443.2749999999996</v>
       </c>
       <c r="S95" s="25">
-        <f>R95/12</f>
+        <f t="shared" si="16"/>
         <v>286.9395833333333</v>
       </c>
       <c r="T95" s="5"/>
     </row>
     <row r="96" spans="3:21" ht="12" customHeight="1">
-      <c r="C96" s="69" t="s">
+      <c r="C96" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="D96" s="92"/>
-      <c r="E96" s="92"/>
+      <c r="D96" s="81"/>
+      <c r="E96" s="81"/>
       <c r="F96" s="3">
         <f>'REALIZADO 2025'!D120*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1512.3239999999998</v>
@@ -21095,21 +21108,21 @@
         <v>2191.3022999999998</v>
       </c>
       <c r="R96" s="4">
-        <f t="shared" ref="R96" si="15">SUM(F96:Q96)</f>
+        <f t="shared" ref="R96" si="17">SUM(F96:Q96)</f>
         <v>24092.621299999995</v>
       </c>
       <c r="S96" s="25">
-        <f>R96/12</f>
+        <f t="shared" si="16"/>
         <v>2007.7184416666662</v>
       </c>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" spans="3:20" ht="12">
-      <c r="C97" s="69" t="s">
+    <row r="97" spans="3:24" ht="12">
+      <c r="C97" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="D97" s="69"/>
-      <c r="E97" s="69"/>
+      <c r="D97" s="75"/>
+      <c r="E97" s="75"/>
       <c r="F97" s="3">
         <f>'REALIZADO 2025'!D110*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>1863.7366</v>
@@ -21162,17 +21175,17 @@
         <v>24000</v>
       </c>
       <c r="S97" s="25">
-        <f>R97/12</f>
+        <f t="shared" si="16"/>
         <v>2000</v>
       </c>
       <c r="T97" s="5"/>
     </row>
-    <row r="98" spans="3:20" ht="12">
-      <c r="C98" s="69" t="s">
+    <row r="98" spans="3:24" ht="12">
+      <c r="C98" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="D98" s="69"/>
-      <c r="E98" s="69"/>
+      <c r="D98" s="75"/>
+      <c r="E98" s="75"/>
       <c r="F98" s="3">
         <f>'REALIZADO 2025'!D111*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>0</v>
@@ -21226,17 +21239,17 @@
         <v>8386.8251499999988</v>
       </c>
       <c r="S98" s="25">
-        <f>R98/12</f>
+        <f t="shared" si="16"/>
         <v>698.90209583333319</v>
       </c>
       <c r="T98" s="5"/>
     </row>
-    <row r="99" spans="3:20" ht="12">
-      <c r="C99" s="69" t="s">
+    <row r="99" spans="3:24" ht="12">
+      <c r="C99" s="75" t="s">
         <v>104</v>
       </c>
-      <c r="D99" s="69"/>
-      <c r="E99" s="69"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="75"/>
       <c r="F99" s="3">
         <f>'REALIZADO 2025'!D112*'PREVISTO 2026 REVISADO (2)'!$U$86</f>
         <v>169.6035</v>
@@ -21290,63 +21303,63 @@
         <v>1450.6689999999999</v>
       </c>
       <c r="S99" s="25">
-        <f>R99/12</f>
+        <f t="shared" si="16"/>
         <v>120.88908333333332</v>
       </c>
       <c r="T99" s="5"/>
     </row>
-    <row r="101" spans="3:20" ht="12">
-      <c r="C101" s="70" t="s">
+    <row r="101" spans="3:24" ht="12">
+      <c r="C101" s="82" t="s">
         <v>113</v>
       </c>
-      <c r="D101" s="70"/>
-      <c r="E101" s="70"/>
+      <c r="D101" s="82"/>
+      <c r="E101" s="82"/>
       <c r="F101" s="60" t="e">
         <f>F4</f>
         <v>#REF!</v>
       </c>
       <c r="G101" s="60" t="e">
-        <f t="shared" ref="G101:Q101" si="16">G4</f>
+        <f t="shared" ref="G101:Q101" si="18">G4</f>
         <v>#REF!</v>
       </c>
       <c r="H101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="I101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="J101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="K101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="L101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="M101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="N101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="O101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="P101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="Q101" s="60" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>#REF!</v>
       </c>
       <c r="R101" s="61">
@@ -21359,7 +21372,7 @@
       </c>
       <c r="T101" s="62"/>
     </row>
-    <row r="102" spans="3:20" ht="12">
+    <row r="102" spans="3:24" ht="12">
       <c r="C102" s="62"/>
       <c r="D102" s="62"/>
       <c r="E102" s="62"/>
@@ -21379,58 +21392,68 @@
       <c r="S102" s="62"/>
       <c r="T102" s="32"/>
     </row>
-    <row r="103" spans="3:20" ht="14.4">
-      <c r="C103" s="71" t="s">
+    <row r="103" spans="3:24" ht="14.4">
+      <c r="C103" s="83" t="s">
         <v>114</v>
       </c>
-      <c r="D103" s="71"/>
+      <c r="D103" s="83"/>
       <c r="E103" s="64">
         <v>270297.34000000003</v>
       </c>
-    </row>
-    <row r="104" spans="3:20" ht="14.4">
-      <c r="C104" s="72" t="s">
+      <c r="X103" s="94">
+        <v>1112022.17</v>
+      </c>
+    </row>
+    <row r="104" spans="3:24" ht="14.4">
+      <c r="C104" s="84" t="s">
         <v>115</v>
       </c>
-      <c r="D104" s="72"/>
+      <c r="D104" s="84"/>
       <c r="E104" s="65">
         <f>S101</f>
         <v>284113.14483333332</v>
       </c>
       <c r="F104" s="59"/>
-    </row>
-    <row r="105" spans="3:20" ht="14.4">
-      <c r="C105" s="73" t="s">
+      <c r="X104" s="1">
+        <v>9387.0499999999993</v>
+      </c>
+    </row>
+    <row r="105" spans="3:24" ht="14.4">
+      <c r="C105" s="85" t="s">
         <v>116</v>
       </c>
-      <c r="D105" s="73"/>
+      <c r="D105" s="85"/>
       <c r="E105" s="66">
         <f>E104-E103</f>
         <v>13815.804833333299</v>
       </c>
       <c r="F105" s="59"/>
-    </row>
-    <row r="106" spans="3:20" ht="14.4">
-      <c r="C106" s="68" t="s">
+      <c r="X105" s="95">
+        <f>X103+X104</f>
+        <v>1121409.22</v>
+      </c>
+    </row>
+    <row r="106" spans="3:24" ht="14.4">
+      <c r="C106" s="80" t="s">
         <v>117</v>
       </c>
-      <c r="D106" s="68"/>
+      <c r="D106" s="80"/>
       <c r="E106" s="67">
         <f>E105/E103</f>
         <v>5.1113358471575408E-2</v>
       </c>
       <c r="F106" s="59"/>
     </row>
-    <row r="107" spans="3:20" ht="12">
+    <row r="107" spans="3:24" ht="12">
       <c r="C107" s="59"/>
       <c r="D107" s="59"/>
       <c r="E107" s="59"/>
     </row>
-    <row r="108" spans="3:20" ht="12"/>
-    <row r="109" spans="3:20" ht="12"/>
-    <row r="110" spans="3:20" ht="12"/>
-    <row r="111" spans="3:20" ht="12"/>
-    <row r="112" spans="3:20" ht="12"/>
+    <row r="108" spans="3:24" ht="12"/>
+    <row r="109" spans="3:24" ht="12"/>
+    <row r="110" spans="3:24" ht="12"/>
+    <row r="111" spans="3:24" ht="12"/>
+    <row r="112" spans="3:24" ht="12"/>
     <row r="113" ht="12"/>
     <row r="114" ht="12"/>
     <row r="115" ht="12"/>
@@ -21458,96 +21481,6 @@
     <row r="137" ht="12"/>
   </sheetData>
   <mergeCells count="103">
-    <mergeCell ref="C1:S1"/>
-    <mergeCell ref="C2:S2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
     <mergeCell ref="C106:D106"/>
     <mergeCell ref="C95:E95"/>
     <mergeCell ref="C96:E96"/>
@@ -21561,6 +21494,96 @@
     <mergeCell ref="C92:E92"/>
     <mergeCell ref="C93:E93"/>
     <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C1:S1"/>
+    <mergeCell ref="C2:S2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -21589,11 +21612,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="12">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="92" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
       <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
@@ -21639,11 +21662,11 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:18" ht="12">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="87"/>
-      <c r="C2" s="87"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="91"/>
       <c r="D2" s="33">
         <f>SUM(D3:D24)</f>
         <v>290185.64999999997</v>
@@ -21703,11 +21726,11 @@
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:18" ht="12">
-      <c r="A3" s="85" t="s">
+      <c r="A3" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="87"/>
       <c r="D3" s="35">
         <v>239580.04</v>
       </c>
@@ -21755,11 +21778,11 @@
       <c r="R3" s="32"/>
     </row>
     <row r="4" spans="1:18" ht="12">
-      <c r="A4" s="86" t="s">
+      <c r="A4" s="88" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
       <c r="D4" s="38">
         <v>8221.9500000000007</v>
       </c>
@@ -21807,11 +21830,11 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:18" ht="12">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="87" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
       <c r="D5" s="35">
         <v>0</v>
       </c>
@@ -21859,11 +21882,11 @@
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:18" ht="12">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="88" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
+      <c r="B6" s="88"/>
+      <c r="C6" s="88"/>
       <c r="D6" s="38">
         <v>0</v>
       </c>
@@ -21911,11 +21934,11 @@
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:18" ht="12">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="87" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="85"/>
-      <c r="C7" s="85"/>
+      <c r="B7" s="87"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="35">
         <v>0</v>
       </c>
@@ -21963,11 +21986,11 @@
       <c r="R7" s="32"/>
     </row>
     <row r="8" spans="1:18" ht="12">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="88"/>
       <c r="D8" s="38">
         <v>525</v>
       </c>
@@ -22015,11 +22038,11 @@
       <c r="R8" s="32"/>
     </row>
     <row r="9" spans="1:18" ht="12">
-      <c r="A9" s="85" t="s">
+      <c r="A9" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
       <c r="D9" s="35">
         <v>1260</v>
       </c>
@@ -22067,11 +22090,11 @@
       <c r="R9" s="32"/>
     </row>
     <row r="10" spans="1:18" ht="12">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
       <c r="D10" s="38">
         <v>1706.95</v>
       </c>
@@ -22119,11 +22142,11 @@
       <c r="R10" s="32"/>
     </row>
     <row r="11" spans="1:18" ht="12">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="35">
         <v>23926.35</v>
       </c>
@@ -22171,11 +22194,11 @@
       <c r="R11" s="32"/>
     </row>
     <row r="12" spans="1:18" ht="12">
-      <c r="A12" s="86" t="s">
+      <c r="A12" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="88"/>
       <c r="D12" s="38">
         <v>150</v>
       </c>
@@ -22223,11 +22246,11 @@
       <c r="R12" s="32"/>
     </row>
     <row r="13" spans="1:18" ht="12">
-      <c r="A13" s="85" t="s">
+      <c r="A13" s="87" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="85"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="87"/>
       <c r="D13" s="35">
         <v>0</v>
       </c>
@@ -22275,11 +22298,11 @@
       <c r="R13" s="32"/>
     </row>
     <row r="14" spans="1:18" ht="12">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="38">
         <v>317.67</v>
       </c>
@@ -22327,11 +22350,11 @@
       <c r="R14" s="32"/>
     </row>
     <row r="15" spans="1:18" ht="12">
-      <c r="A15" s="85" t="s">
+      <c r="A15" s="87" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="85"/>
+      <c r="B15" s="87"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="35">
         <v>1730</v>
       </c>
@@ -22379,11 +22402,11 @@
       <c r="R15" s="32"/>
     </row>
     <row r="16" spans="1:18" ht="12">
-      <c r="A16" s="86" t="s">
+      <c r="A16" s="88" t="s">
         <v>133</v>
       </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
       <c r="D16" s="38">
         <v>8050.48</v>
       </c>
@@ -22431,11 +22454,11 @@
       <c r="R16" s="32"/>
     </row>
     <row r="17" spans="1:20" ht="12">
-      <c r="A17" s="85" t="s">
+      <c r="A17" s="87" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="35">
         <v>50.02</v>
       </c>
@@ -22483,11 +22506,11 @@
       <c r="R17" s="32"/>
     </row>
     <row r="18" spans="1:20" ht="12">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="B18" s="86"/>
-      <c r="C18" s="86"/>
+      <c r="B18" s="88"/>
+      <c r="C18" s="88"/>
       <c r="D18" s="38">
         <v>500</v>
       </c>
@@ -22535,11 +22558,11 @@
       <c r="R18" s="32"/>
     </row>
     <row r="19" spans="1:20" ht="12">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="35">
         <v>0</v>
       </c>
@@ -22587,11 +22610,11 @@
       <c r="R19" s="32"/>
     </row>
     <row r="20" spans="1:20" ht="12">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="88" t="s">
         <v>137</v>
       </c>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="88"/>
       <c r="D20" s="38">
         <v>2450.54</v>
       </c>
@@ -22639,11 +22662,11 @@
       <c r="R20" s="32"/>
     </row>
     <row r="21" spans="1:20" ht="12">
-      <c r="A21" s="85" t="s">
+      <c r="A21" s="87" t="s">
         <v>138</v>
       </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85"/>
+      <c r="B21" s="87"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="35">
         <v>754.13</v>
       </c>
@@ -22691,11 +22714,11 @@
       <c r="R21" s="32"/>
     </row>
     <row r="22" spans="1:20" ht="12">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="88" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="86"/>
-      <c r="C22" s="86"/>
+      <c r="B22" s="88"/>
+      <c r="C22" s="88"/>
       <c r="D22" s="38">
         <v>797.85</v>
       </c>
@@ -22743,11 +22766,11 @@
       <c r="R22" s="32"/>
     </row>
     <row r="23" spans="1:20" ht="12">
-      <c r="A23" s="85" t="s">
+      <c r="A23" s="87" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="87"/>
       <c r="D23" s="35">
         <v>0</v>
       </c>
@@ -22795,11 +22818,11 @@
       <c r="R23" s="32"/>
     </row>
     <row r="24" spans="1:20" ht="12">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="88" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="86"/>
-      <c r="C24" s="86"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="88"/>
       <c r="D24" s="38">
         <v>164.67</v>
       </c>
@@ -22847,11 +22870,11 @@
       <c r="R24" s="32"/>
     </row>
     <row r="25" spans="1:20" ht="12">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="86" t="s">
         <v>142</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
+      <c r="B25" s="86"/>
+      <c r="C25" s="86"/>
       <c r="D25" s="39">
         <f>D2</f>
         <v>290185.64999999997</v>
@@ -22931,11 +22954,11 @@
       <c r="R26" s="32"/>
     </row>
     <row r="27" spans="1:20" ht="12">
-      <c r="A27" s="84" t="s">
+      <c r="A27" s="73" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="84"/>
-      <c r="C27" s="84"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
       <c r="D27" s="23">
         <f t="shared" ref="D27:O27" si="4">D28+D45+D61+D102+D110+D123</f>
         <v>302630.67195000005</v>
@@ -23067,11 +23090,11 @@
       <c r="R28" s="32"/>
     </row>
     <row r="29" spans="1:20" ht="12">
-      <c r="A29" s="69" t="s">
+      <c r="A29" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="75"/>
       <c r="D29" s="3">
         <v>34</v>
       </c>
@@ -23128,11 +23151,11 @@
       <c r="R29" s="5"/>
     </row>
     <row r="30" spans="1:20" ht="12">
-      <c r="A30" s="69" t="s">
+      <c r="A30" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="75"/>
       <c r="D30" s="3">
         <f>'REALIZADO 2025'!D29*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23192,11 +23215,11 @@
       <c r="R30" s="5"/>
     </row>
     <row r="31" spans="1:20" ht="12">
-      <c r="A31" s="69" t="s">
+      <c r="A31" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
+      <c r="B31" s="75"/>
+      <c r="C31" s="75"/>
       <c r="D31" s="3">
         <f>'REALIZADO 2025'!D30*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23256,11 +23279,11 @@
       <c r="R31" s="5"/>
     </row>
     <row r="32" spans="1:20" ht="12">
-      <c r="A32" s="69" t="s">
+      <c r="A32" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="B32" s="69"/>
-      <c r="C32" s="69"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="75"/>
       <c r="D32" s="3">
         <f>'REALIZADO 2025'!D31*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23320,11 +23343,11 @@
       <c r="R32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="12">
-      <c r="A33" s="69" t="s">
+      <c r="A33" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="B33" s="69"/>
-      <c r="C33" s="69"/>
+      <c r="B33" s="75"/>
+      <c r="C33" s="75"/>
       <c r="D33" s="3">
         <f>'REALIZADO 2025'!D34*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23384,11 +23407,11 @@
       <c r="R33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="12">
-      <c r="A34" s="69" t="s">
+      <c r="A34" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="75"/>
       <c r="D34" s="3">
         <f>'REALIZADO 2025'!D35*'PREVISTO 2026'!$S$27</f>
         <v>372.17674999999997</v>
@@ -23448,11 +23471,11 @@
       <c r="R34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="12">
-      <c r="A35" s="69" t="s">
+      <c r="A35" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="B35" s="69"/>
-      <c r="C35" s="69"/>
+      <c r="B35" s="75"/>
+      <c r="C35" s="75"/>
       <c r="D35" s="3">
         <f>'REALIZADO 2025'!D36*'PREVISTO 2026'!$S$27</f>
         <v>522.5</v>
@@ -23512,11 +23535,11 @@
       <c r="R35" s="5"/>
     </row>
     <row r="36" spans="1:21" ht="12">
-      <c r="A36" s="69" t="s">
+      <c r="A36" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="69"/>
-      <c r="C36" s="69"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="75"/>
       <c r="D36" s="3">
         <f>'REALIZADO 2025'!D37*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23576,11 +23599,11 @@
       <c r="R36" s="5"/>
     </row>
     <row r="37" spans="1:21" ht="12">
-      <c r="A37" s="69" t="s">
+      <c r="A37" s="75" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="75"/>
       <c r="D37" s="3">
         <f>5043.17*$S$27</f>
         <v>5270.11265</v>
@@ -23640,11 +23663,11 @@
       <c r="R37" s="5"/>
     </row>
     <row r="38" spans="1:21" ht="12">
-      <c r="A38" s="69" t="s">
+      <c r="A38" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="69"/>
-      <c r="C38" s="69"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="75"/>
       <c r="D38" s="3">
         <f>2570.4*$S$27</f>
         <v>2686.0679999999998</v>
@@ -23704,11 +23727,11 @@
       <c r="R38" s="5"/>
     </row>
     <row r="39" spans="1:21" ht="12">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
+      <c r="B39" s="75"/>
+      <c r="C39" s="75"/>
       <c r="D39" s="3">
         <f>'REALIZADO 2025'!D40*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23768,11 +23791,11 @@
       <c r="R39" s="5"/>
     </row>
     <row r="40" spans="1:21" ht="12">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="75"/>
       <c r="D40" s="3">
         <f>'REALIZADO 2025'!D41*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23832,11 +23855,11 @@
       <c r="R40" s="5"/>
     </row>
     <row r="41" spans="1:21" ht="12">
-      <c r="A41" s="69" t="s">
+      <c r="A41" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="69"/>
-      <c r="C41" s="69"/>
+      <c r="B41" s="75"/>
+      <c r="C41" s="75"/>
       <c r="D41" s="3">
         <f>'REALIZADO 2025'!D42*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23896,11 +23919,11 @@
       <c r="R41" s="5"/>
     </row>
     <row r="42" spans="1:21" ht="12">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
       <c r="D42" s="3">
         <f>'REALIZADO 2025'!D43*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -23960,11 +23983,11 @@
       <c r="R42" s="5"/>
     </row>
     <row r="43" spans="1:21" ht="12">
-      <c r="A43" s="69" t="s">
+      <c r="A43" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="B43" s="69"/>
-      <c r="C43" s="69"/>
+      <c r="B43" s="75"/>
+      <c r="C43" s="75"/>
       <c r="D43" s="3">
         <f>'REALIZADO 2025'!D44*'PREVISTO 2026'!$S$27</f>
         <v>252.50334999999998</v>
@@ -24024,11 +24047,11 @@
       <c r="R43" s="5"/>
     </row>
     <row r="44" spans="1:21" ht="12">
-      <c r="A44" s="69" t="s">
+      <c r="A44" s="75" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
+      <c r="B44" s="75"/>
+      <c r="C44" s="75"/>
       <c r="D44" s="3">
         <f>'REALIZADO 2025'!D45*'PREVISTO 2026'!$S$27</f>
         <v>0</v>
@@ -24088,11 +24111,11 @@
       <c r="R44" s="5"/>
     </row>
     <row r="45" spans="1:21" ht="12">
-      <c r="A45" s="78" t="s">
+      <c r="A45" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="B45" s="78"/>
-      <c r="C45" s="78"/>
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
       <c r="D45" s="7">
         <f>SUM(D46:D60)</f>
         <v>154479.97080000001</v>
@@ -24160,11 +24183,11 @@
       </c>
     </row>
     <row r="46" spans="1:21" ht="12">
-      <c r="A46" s="69" t="s">
+      <c r="A46" s="75" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="69"/>
-      <c r="C46" s="69"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="75"/>
       <c r="D46" s="3">
         <f>'REALIZADO 2025'!D47*'PREVISTO 2026'!$S$45</f>
         <v>52560.36</v>
@@ -24224,11 +24247,11 @@
       <c r="R46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="12">
-      <c r="A47" s="69" t="s">
+      <c r="A47" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="69"/>
-      <c r="C47" s="69"/>
+      <c r="B47" s="75"/>
+      <c r="C47" s="75"/>
       <c r="D47" s="3">
         <f>'REALIZADO 2025'!D48*'PREVISTO 2026'!$S$45</f>
         <v>23252.497200000002</v>
@@ -24292,11 +24315,11 @@
       </c>
     </row>
     <row r="48" spans="1:21" ht="12">
-      <c r="A48" s="69" t="s">
+      <c r="A48" s="75" t="s">
         <v>39</v>
       </c>
-      <c r="B48" s="69"/>
-      <c r="C48" s="69"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
       <c r="D48" s="3">
         <f>'REALIZADO 2025'!D49*'PREVISTO 2026'!$S$45</f>
         <v>77.652000000000015</v>
@@ -24355,11 +24378,11 @@
       <c r="R48" s="5"/>
     </row>
     <row r="49" spans="1:24" ht="12">
-      <c r="A49" s="69" t="s">
+      <c r="A49" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="B49" s="69"/>
-      <c r="C49" s="69"/>
+      <c r="B49" s="75"/>
+      <c r="C49" s="75"/>
       <c r="D49" s="3">
         <f>'REALIZADO 2025'!D50*'PREVISTO 2026'!$S$45</f>
         <v>266.14440000000002</v>
@@ -24419,11 +24442,11 @@
       <c r="R49" s="5"/>
     </row>
     <row r="50" spans="1:24" ht="12">
-      <c r="A50" s="69" t="s">
+      <c r="A50" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="B50" s="69"/>
-      <c r="C50" s="69"/>
+      <c r="B50" s="75"/>
+      <c r="C50" s="75"/>
       <c r="D50" s="3">
         <f>'REALIZADO 2025'!D51*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -24483,11 +24506,11 @@
       <c r="R50" s="5"/>
     </row>
     <row r="51" spans="1:24" ht="12">
-      <c r="A51" s="69" t="s">
+      <c r="A51" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="B51" s="69"/>
-      <c r="C51" s="69"/>
+      <c r="B51" s="75"/>
+      <c r="C51" s="75"/>
       <c r="D51" s="3">
         <f>'REALIZADO 2025'!D52*'PREVISTO 2026'!$S$45</f>
         <v>3033.6120000000001</v>
@@ -24547,11 +24570,11 @@
       <c r="R51" s="5"/>
     </row>
     <row r="52" spans="1:24" ht="12">
-      <c r="A52" s="69" t="s">
+      <c r="A52" s="75" t="s">
         <v>43</v>
       </c>
-      <c r="B52" s="69"/>
-      <c r="C52" s="69"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="75"/>
       <c r="D52" s="3">
         <f>'REALIZADO 2025'!D53*'PREVISTO 2026'!$S$45</f>
         <v>319.59360000000004</v>
@@ -24611,11 +24634,11 @@
       <c r="R52" s="5"/>
     </row>
     <row r="53" spans="1:24" ht="12">
-      <c r="A53" s="69" t="s">
+      <c r="A53" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="B53" s="69"/>
-      <c r="C53" s="69"/>
+      <c r="B53" s="75"/>
+      <c r="C53" s="75"/>
       <c r="D53" s="3">
         <f>'REALIZADO 2025'!D54*'PREVISTO 2026'!$S$45</f>
         <v>324</v>
@@ -24675,11 +24698,11 @@
       <c r="R53" s="5"/>
     </row>
     <row r="54" spans="1:24" ht="12">
-      <c r="A54" s="69" t="s">
+      <c r="A54" s="75" t="s">
         <v>45</v>
       </c>
-      <c r="B54" s="69"/>
-      <c r="C54" s="69"/>
+      <c r="B54" s="75"/>
+      <c r="C54" s="75"/>
       <c r="D54" s="3">
         <f>'REALIZADO 2025'!D55*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -24739,11 +24762,11 @@
       <c r="R54" s="5"/>
     </row>
     <row r="55" spans="1:24" ht="12">
-      <c r="A55" s="69" t="s">
+      <c r="A55" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="B55" s="69"/>
-      <c r="C55" s="69"/>
+      <c r="B55" s="75"/>
+      <c r="C55" s="75"/>
       <c r="D55" s="3">
         <f>'REALIZADO 2025'!D57*'PREVISTO 2026'!$S$45</f>
         <v>26005.406400000003</v>
@@ -24803,11 +24826,11 @@
       <c r="R55" s="5"/>
     </row>
     <row r="56" spans="1:24" ht="12">
-      <c r="A56" s="69" t="s">
+      <c r="A56" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
+      <c r="B56" s="75"/>
+      <c r="C56" s="75"/>
       <c r="D56" s="3">
         <f>'REALIZADO 2025'!D58*'PREVISTO 2026'!$S$45</f>
         <v>5940.0108000000009</v>
@@ -24867,11 +24890,11 @@
       <c r="R56" s="5"/>
     </row>
     <row r="57" spans="1:24" ht="12">
-      <c r="A57" s="69" t="s">
+      <c r="A57" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="69"/>
-      <c r="C57" s="69"/>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
       <c r="D57" s="3">
         <f>'REALIZADO 2025'!D59*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -24931,11 +24954,11 @@
       <c r="R57" s="5"/>
     </row>
     <row r="58" spans="1:24" ht="12">
-      <c r="A58" s="69" t="s">
+      <c r="A58" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="B58" s="69"/>
-      <c r="C58" s="69"/>
+      <c r="B58" s="75"/>
+      <c r="C58" s="75"/>
       <c r="D58" s="3">
         <f>'REALIZADO 2025'!D60*'PREVISTO 2026'!$S$45</f>
         <v>41884.214400000004</v>
@@ -24995,11 +25018,11 @@
       <c r="R58" s="5"/>
     </row>
     <row r="59" spans="1:24" ht="12">
-      <c r="A59" s="69" t="s">
+      <c r="A59" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="B59" s="69"/>
-      <c r="C59" s="69"/>
+      <c r="B59" s="75"/>
+      <c r="C59" s="75"/>
       <c r="D59" s="3">
         <f>'REALIZADO 2025'!D61*'PREVISTO 2026'!$S$45</f>
         <v>0</v>
@@ -25058,11 +25081,11 @@
       <c r="R59" s="5"/>
     </row>
     <row r="60" spans="1:24" ht="12">
-      <c r="A60" s="69" t="s">
+      <c r="A60" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="69"/>
-      <c r="C60" s="69"/>
+      <c r="B60" s="75"/>
+      <c r="C60" s="75"/>
       <c r="D60" s="3">
         <f>'REALIZADO 2025'!D62*'PREVISTO 2026'!$S$45</f>
         <v>816.48</v>
@@ -25122,11 +25145,11 @@
       <c r="R60" s="5"/>
     </row>
     <row r="61" spans="1:24" ht="12.75" customHeight="1">
-      <c r="A61" s="78" t="s">
+      <c r="A61" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="B61" s="78"/>
-      <c r="C61" s="78"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="76"/>
       <c r="D61" s="7">
         <f>D62+D79+D92+D96</f>
         <v>49045.706050000001</v>
@@ -25192,9 +25215,9 @@
       <c r="T61" s="17">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="U61" s="78"/>
-      <c r="V61" s="78"/>
-      <c r="W61" s="78"/>
+      <c r="U61" s="76"/>
+      <c r="V61" s="76"/>
+      <c r="W61" s="76"/>
       <c r="X61" s="7"/>
     </row>
     <row r="62" spans="1:24" ht="12" customHeight="1">
@@ -25263,11 +25286,11 @@
       <c r="T62" s="58"/>
     </row>
     <row r="63" spans="1:24" ht="12">
-      <c r="A63" s="69" t="s">
+      <c r="A63" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="B63" s="69"/>
-      <c r="C63" s="69"/>
+      <c r="B63" s="75"/>
+      <c r="C63" s="75"/>
       <c r="D63" s="3">
         <f>'REALIZADO 2025'!D65*'PREVISTO 2026'!$S$61</f>
         <v>1550.68595</v>
@@ -25333,11 +25356,11 @@
       </c>
     </row>
     <row r="64" spans="1:24" ht="12">
-      <c r="A64" s="91" t="s">
+      <c r="A64" s="89" t="s">
         <v>147</v>
       </c>
-      <c r="B64" s="91"/>
-      <c r="C64" s="91"/>
+      <c r="B64" s="89"/>
+      <c r="C64" s="89"/>
       <c r="D64" s="56">
         <f>'REALIZADO 2025'!D66*'PREVISTO 2026'!$S$61</f>
         <v>150.42774999999997</v>
@@ -25401,11 +25424,11 @@
       </c>
     </row>
     <row r="65" spans="1:22" ht="12">
-      <c r="A65" s="69" t="s">
+      <c r="A65" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="B65" s="69"/>
-      <c r="C65" s="69"/>
+      <c r="B65" s="75"/>
+      <c r="C65" s="75"/>
       <c r="D65" s="3">
         <f>'REALIZADO 2025'!D67*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -25472,11 +25495,11 @@
       </c>
     </row>
     <row r="66" spans="1:22" ht="12">
-      <c r="A66" s="69" t="s">
+      <c r="A66" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="B66" s="69"/>
-      <c r="C66" s="69"/>
+      <c r="B66" s="75"/>
+      <c r="C66" s="75"/>
       <c r="D66" s="3">
         <f>'REALIZADO 2025'!D68*'PREVISTO 2026'!$S$61</f>
         <v>3193.8857499999995</v>
@@ -25542,11 +25565,11 @@
       </c>
     </row>
     <row r="67" spans="1:22" ht="12">
-      <c r="A67" s="69" t="s">
+      <c r="A67" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="B67" s="69"/>
-      <c r="C67" s="69"/>
+      <c r="B67" s="75"/>
+      <c r="C67" s="75"/>
       <c r="D67" s="3">
         <f>'REALIZADO 2025'!D69*'PREVISTO 2026'!$S$61</f>
         <v>610.80250000000001</v>
@@ -25608,11 +25631,11 @@
       </c>
     </row>
     <row r="68" spans="1:22" ht="12">
-      <c r="A68" s="69" t="s">
+      <c r="A68" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="B68" s="69"/>
-      <c r="C68" s="69"/>
+      <c r="B68" s="75"/>
+      <c r="C68" s="75"/>
       <c r="D68" s="3">
         <f>'REALIZADO 2025'!D70*'PREVISTO 2026'!$S$61</f>
         <v>554.51879999999994</v>
@@ -25675,11 +25698,11 @@
       </c>
     </row>
     <row r="69" spans="1:22" ht="12">
-      <c r="A69" s="69" t="s">
+      <c r="A69" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="69"/>
-      <c r="C69" s="69"/>
+      <c r="B69" s="75"/>
+      <c r="C69" s="75"/>
       <c r="D69" s="3">
         <f>'REALIZADO 2025'!D71*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -25742,11 +25765,11 @@
       </c>
     </row>
     <row r="70" spans="1:22" ht="12">
-      <c r="A70" s="69" t="s">
+      <c r="A70" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="69"/>
-      <c r="C70" s="69"/>
+      <c r="B70" s="75"/>
+      <c r="C70" s="75"/>
       <c r="D70" s="3">
         <f>'REALIZADO 2025'!D72*'PREVISTO 2026'!$S$61</f>
         <v>5500.8486499999999</v>
@@ -25808,11 +25831,11 @@
       </c>
     </row>
     <row r="71" spans="1:22" ht="12">
-      <c r="A71" s="91" t="s">
+      <c r="A71" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="B71" s="91"/>
-      <c r="C71" s="91"/>
+      <c r="B71" s="89"/>
+      <c r="C71" s="89"/>
       <c r="D71" s="3">
         <f>'REALIZADO 2025'!D73*'PREVISTO 2026'!$S$61</f>
         <v>349.70924999999994</v>
@@ -25874,11 +25897,11 @@
       </c>
     </row>
     <row r="72" spans="1:22" ht="12">
-      <c r="A72" s="69" t="s">
+      <c r="A72" s="75" t="s">
         <v>62</v>
       </c>
-      <c r="B72" s="69"/>
-      <c r="C72" s="69"/>
+      <c r="B72" s="75"/>
+      <c r="C72" s="75"/>
       <c r="D72" s="3">
         <f>'REALIZADO 2025'!D74*'PREVISTO 2026'!$S$61</f>
         <v>12.54</v>
@@ -25941,11 +25964,11 @@
       </c>
     </row>
     <row r="73" spans="1:22" ht="12">
-      <c r="A73" s="69" t="s">
+      <c r="A73" s="75" t="s">
         <v>170</v>
       </c>
-      <c r="B73" s="92"/>
-      <c r="C73" s="92"/>
+      <c r="B73" s="81"/>
+      <c r="C73" s="81"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -25972,11 +25995,11 @@
       </c>
     </row>
     <row r="74" spans="1:22" ht="12">
-      <c r="A74" s="69" t="s">
+      <c r="A74" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="B74" s="92"/>
-      <c r="C74" s="92"/>
+      <c r="B74" s="81"/>
+      <c r="C74" s="81"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -25999,11 +26022,11 @@
       <c r="R74" s="5"/>
     </row>
     <row r="75" spans="1:22" ht="12">
-      <c r="A75" s="69" t="s">
+      <c r="A75" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="B75" s="92"/>
-      <c r="C75" s="92"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="81"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -26026,11 +26049,11 @@
       <c r="R75" s="5"/>
     </row>
     <row r="76" spans="1:22" ht="12">
-      <c r="A76" s="69" t="s">
+      <c r="A76" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="B76" s="92"/>
-      <c r="C76" s="92"/>
+      <c r="B76" s="81"/>
+      <c r="C76" s="81"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
@@ -26053,11 +26076,11 @@
       <c r="R76" s="5"/>
     </row>
     <row r="77" spans="1:22" ht="12">
-      <c r="A77" s="69" t="s">
+      <c r="A77" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="B77" s="92"/>
-      <c r="C77" s="92"/>
+      <c r="B77" s="81"/>
+      <c r="C77" s="81"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -26080,11 +26103,11 @@
       <c r="R77" s="5"/>
     </row>
     <row r="78" spans="1:22" ht="12">
-      <c r="A78" s="69" t="s">
+      <c r="A78" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="B78" s="69"/>
-      <c r="C78" s="69"/>
+      <c r="B78" s="75"/>
+      <c r="C78" s="75"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -26171,11 +26194,11 @@
       <c r="R79" s="5"/>
     </row>
     <row r="80" spans="1:22" ht="12">
-      <c r="A80" s="69" t="s">
+      <c r="A80" s="75" t="s">
         <v>70</v>
       </c>
-      <c r="B80" s="69"/>
-      <c r="C80" s="69"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="75"/>
       <c r="D80" s="3">
         <f>'REALIZADO 2025'!D76*'PREVISTO 2026'!$S$61</f>
         <v>1201.7082</v>
@@ -26235,11 +26258,11 @@
       <c r="R80" s="5"/>
     </row>
     <row r="81" spans="1:18" ht="12">
-      <c r="A81" s="69" t="s">
+      <c r="A81" s="75" t="s">
         <v>71</v>
       </c>
-      <c r="B81" s="69"/>
-      <c r="C81" s="69"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="75"/>
       <c r="D81" s="3">
         <f>'REALIZADO 2025'!D77*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26299,11 +26322,11 @@
       <c r="R81" s="5"/>
     </row>
     <row r="82" spans="1:18" ht="12">
-      <c r="A82" s="69" t="s">
+      <c r="A82" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="B82" s="69"/>
-      <c r="C82" s="69"/>
+      <c r="B82" s="75"/>
+      <c r="C82" s="75"/>
       <c r="D82" s="3">
         <f>'REALIZADO 2025'!D78*'PREVISTO 2026'!$S$61</f>
         <v>888.24999999999989</v>
@@ -26363,11 +26386,11 @@
       <c r="R82" s="5"/>
     </row>
     <row r="83" spans="1:18" ht="12">
-      <c r="A83" s="69" t="s">
+      <c r="A83" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="B83" s="69"/>
-      <c r="C83" s="69"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="75"/>
       <c r="D83" s="3">
         <f>'REALIZADO 2025'!D79*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26427,11 +26450,11 @@
       <c r="R83" s="5"/>
     </row>
     <row r="84" spans="1:18" ht="12">
-      <c r="A84" s="69" t="s">
+      <c r="A84" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="B84" s="69"/>
-      <c r="C84" s="69"/>
+      <c r="B84" s="75"/>
+      <c r="C84" s="75"/>
       <c r="D84" s="3">
         <f>'REALIZADO 2025'!D80*'PREVISTO 2026'!$S$61</f>
         <v>2080.5113999999999</v>
@@ -26490,11 +26513,11 @@
       <c r="R84" s="5"/>
     </row>
     <row r="85" spans="1:18" ht="12">
-      <c r="A85" s="69" t="s">
+      <c r="A85" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="B85" s="69"/>
-      <c r="C85" s="69"/>
+      <c r="B85" s="75"/>
+      <c r="C85" s="75"/>
       <c r="D85" s="3">
         <f>'REALIZADO 2025'!D81*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26554,11 +26577,11 @@
       <c r="R85" s="5"/>
     </row>
     <row r="86" spans="1:18" ht="12">
-      <c r="A86" s="69" t="s">
+      <c r="A86" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="B86" s="69"/>
-      <c r="C86" s="69"/>
+      <c r="B86" s="75"/>
+      <c r="C86" s="75"/>
       <c r="D86" s="3">
         <f>'REALIZADO 2025'!D82*'PREVISTO 2026'!$S$61</f>
         <v>7691.6597999999994</v>
@@ -26618,11 +26641,11 @@
       <c r="R86" s="5"/>
     </row>
     <row r="87" spans="1:18" ht="12">
-      <c r="A87" s="69" t="s">
+      <c r="A87" s="75" t="s">
         <v>77</v>
       </c>
-      <c r="B87" s="69"/>
-      <c r="C87" s="69"/>
+      <c r="B87" s="75"/>
+      <c r="C87" s="75"/>
       <c r="D87" s="3">
         <f>'REALIZADO 2025'!D83*'PREVISTO 2026'!$S$61</f>
         <v>1149.5</v>
@@ -26681,11 +26704,11 @@
       <c r="R87" s="5"/>
     </row>
     <row r="88" spans="1:18" ht="12">
-      <c r="A88" s="69" t="s">
+      <c r="A88" s="75" t="s">
         <v>78</v>
       </c>
-      <c r="B88" s="69"/>
-      <c r="C88" s="69"/>
+      <c r="B88" s="75"/>
+      <c r="C88" s="75"/>
       <c r="D88" s="3">
         <f>'REALIZADO 2025'!D84*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26745,11 +26768,11 @@
       <c r="R88" s="5"/>
     </row>
     <row r="89" spans="1:18" ht="12">
-      <c r="A89" s="69" t="s">
+      <c r="A89" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="B89" s="69"/>
-      <c r="C89" s="69"/>
+      <c r="B89" s="75"/>
+      <c r="C89" s="75"/>
       <c r="D89" s="3">
         <f>'REALIZADO 2025'!D85*'PREVISTO 2026'!$S$61</f>
         <v>58.310999999999993</v>
@@ -26809,11 +26832,11 @@
       <c r="R89" s="5"/>
     </row>
     <row r="90" spans="1:18" ht="12">
-      <c r="A90" s="69" t="s">
+      <c r="A90" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="B90" s="69"/>
-      <c r="C90" s="69"/>
+      <c r="B90" s="75"/>
+      <c r="C90" s="75"/>
       <c r="D90" s="3">
         <f>'REALIZADO 2025'!D86*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -26873,11 +26896,11 @@
       <c r="R90" s="5"/>
     </row>
     <row r="91" spans="1:18" ht="12">
-      <c r="A91" s="69" t="s">
+      <c r="A91" s="75" t="s">
         <v>81</v>
       </c>
-      <c r="B91" s="69"/>
-      <c r="C91" s="69"/>
+      <c r="B91" s="75"/>
+      <c r="C91" s="75"/>
       <c r="D91" s="3">
         <f>'REALIZADO 2025'!D87*'PREVISTO 2026'!$S$61</f>
         <v>0</v>
@@ -27001,11 +27024,11 @@
       <c r="R92" s="5"/>
     </row>
     <row r="93" spans="1:18" ht="12">
-      <c r="A93" s="69" t="s">
+      <c r="A93" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B93" s="69"/>
-      <c r="C93" s="69"/>
+      <c r="B93" s="75"/>
+      <c r="C93" s="75"/>
       <c r="D93" s="3">
         <f>'REALIZADO 2025'!D89*'PREVISTO 2026'!$S$61</f>
         <v>6040.6224999999995</v>
@@ -27065,11 +27088,11 @@
       <c r="R93" s="5"/>
     </row>
     <row r="94" spans="1:18" ht="12">
-      <c r="A94" s="69" t="s">
+      <c r="A94" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="B94" s="69"/>
-      <c r="C94" s="69"/>
+      <c r="B94" s="75"/>
+      <c r="C94" s="75"/>
       <c r="D94" s="3">
         <f>'REALIZADO 2025'!D90*'PREVISTO 2026'!$S$61</f>
         <v>7357.8449999999993</v>
@@ -27128,11 +27151,11 @@
       <c r="R94" s="5"/>
     </row>
     <row r="95" spans="1:18" ht="12">
-      <c r="A95" s="69" t="s">
+      <c r="A95" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="B95" s="69"/>
-      <c r="C95" s="69"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="75"/>
       <c r="D95" s="3">
         <f>'REALIZADO 2025'!D91*'PREVISTO 2026'!$S$61</f>
         <v>2733.72</v>
@@ -27256,11 +27279,11 @@
       <c r="R96" s="5"/>
     </row>
     <row r="97" spans="1:19" ht="12">
-      <c r="A97" s="69" t="s">
+      <c r="A97" s="75" t="s">
         <v>87</v>
       </c>
-      <c r="B97" s="69"/>
-      <c r="C97" s="69"/>
+      <c r="B97" s="75"/>
+      <c r="C97" s="75"/>
       <c r="D97" s="3">
         <f>'REALIZADO 2025'!D93*'PREVISTO 2026'!$S$61</f>
         <v>909.15</v>
@@ -27320,11 +27343,11 @@
       <c r="R97" s="5"/>
     </row>
     <row r="98" spans="1:19" ht="12">
-      <c r="A98" s="69" t="s">
+      <c r="A98" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="B98" s="69"/>
-      <c r="C98" s="69"/>
+      <c r="B98" s="75"/>
+      <c r="C98" s="75"/>
       <c r="D98" s="3">
         <f>'REALIZADO 2025'!D94*'PREVISTO 2026'!$S$61</f>
         <v>752.4</v>
@@ -27384,11 +27407,11 @@
       <c r="R98" s="5"/>
     </row>
     <row r="99" spans="1:19" ht="12">
-      <c r="A99" s="69" t="s">
+      <c r="A99" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="B99" s="69"/>
-      <c r="C99" s="69"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="75"/>
       <c r="D99" s="3">
         <f>'REALIZADO 2025'!D95*'PREVISTO 2026'!$S$61</f>
         <v>2403.5</v>
@@ -27448,11 +27471,11 @@
       <c r="R99" s="5"/>
     </row>
     <row r="100" spans="1:19" ht="12">
-      <c r="A100" s="69" t="s">
+      <c r="A100" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="B100" s="69"/>
-      <c r="C100" s="69"/>
+      <c r="B100" s="75"/>
+      <c r="C100" s="75"/>
       <c r="D100" s="3">
         <f>'REALIZADO 2025'!D96*'PREVISTO 2026'!$S$61</f>
         <v>1472.5094999999999</v>
@@ -27511,11 +27534,11 @@
       <c r="R100" s="5"/>
     </row>
     <row r="101" spans="1:19" ht="12">
-      <c r="A101" s="69" t="s">
+      <c r="A101" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="B101" s="69"/>
-      <c r="C101" s="69"/>
+      <c r="B101" s="75"/>
+      <c r="C101" s="75"/>
       <c r="D101" s="3">
         <f>'REALIZADO 2025'!D97*'PREVISTO 2026'!$S$61</f>
         <v>2382.6</v>
@@ -27644,11 +27667,11 @@
       </c>
     </row>
     <row r="103" spans="1:19" ht="12">
-      <c r="A103" s="69" t="s">
+      <c r="A103" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="B103" s="69"/>
-      <c r="C103" s="69"/>
+      <c r="B103" s="75"/>
+      <c r="C103" s="75"/>
       <c r="D103" s="3">
         <f>'REALIZADO 2025'!D99*'PREVISTO 2026'!$S$102</f>
         <v>4117.2999999999993</v>
@@ -27708,11 +27731,11 @@
       <c r="R103" s="5"/>
     </row>
     <row r="104" spans="1:19" ht="12">
-      <c r="A104" s="69" t="s">
+      <c r="A104" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="B104" s="69"/>
-      <c r="C104" s="69"/>
+      <c r="B104" s="75"/>
+      <c r="C104" s="75"/>
       <c r="D104" s="3">
         <f>'REALIZADO 2025'!D100*'PREVISTO 2026'!$S$102</f>
         <v>2951.08</v>
@@ -27772,11 +27795,11 @@
       <c r="R104" s="5"/>
     </row>
     <row r="105" spans="1:19" ht="12">
-      <c r="A105" s="69" t="s">
+      <c r="A105" s="75" t="s">
         <v>95</v>
       </c>
-      <c r="B105" s="69"/>
-      <c r="C105" s="69"/>
+      <c r="B105" s="75"/>
+      <c r="C105" s="75"/>
       <c r="D105" s="3">
         <f>'REALIZADO 2025'!D101*'PREVISTO 2026'!$S$102</f>
         <v>4270.2671</v>
@@ -27836,11 +27859,11 @@
       <c r="R105" s="5"/>
     </row>
     <row r="106" spans="1:19" ht="12">
-      <c r="A106" s="69" t="s">
+      <c r="A106" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="B106" s="69"/>
-      <c r="C106" s="69"/>
+      <c r="B106" s="75"/>
+      <c r="C106" s="75"/>
       <c r="D106" s="3">
         <f>'REALIZADO 2025'!D102*'PREVISTO 2026'!$S$102</f>
         <v>58965.410349999998</v>
@@ -27900,11 +27923,11 @@
       <c r="R106" s="5"/>
     </row>
     <row r="107" spans="1:19" ht="12">
-      <c r="A107" s="69" t="s">
+      <c r="A107" s="75" t="s">
         <v>97</v>
       </c>
-      <c r="B107" s="69"/>
-      <c r="C107" s="69"/>
+      <c r="B107" s="75"/>
+      <c r="C107" s="75"/>
       <c r="D107" s="3">
         <f>'REALIZADO 2025'!D103*'PREVISTO 2026'!$S$102</f>
         <v>0</v>
@@ -27964,11 +27987,11 @@
       <c r="R107" s="5"/>
     </row>
     <row r="108" spans="1:19" ht="12">
-      <c r="A108" s="69" t="s">
+      <c r="A108" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="B108" s="69"/>
-      <c r="C108" s="69"/>
+      <c r="B108" s="75"/>
+      <c r="C108" s="75"/>
       <c r="D108" s="3">
         <f>'REALIZADO 2025'!D104*'PREVISTO 2026'!$S$102</f>
         <v>2508</v>
@@ -28028,11 +28051,11 @@
       <c r="R108" s="5"/>
     </row>
     <row r="109" spans="1:19" ht="12">
-      <c r="A109" s="69" t="s">
+      <c r="A109" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="B109" s="69"/>
-      <c r="C109" s="69"/>
+      <c r="B109" s="75"/>
+      <c r="C109" s="75"/>
       <c r="D109" s="3">
         <f>'REALIZADO 2025'!D106*'PREVISTO 2026'!$S$102</f>
         <v>1250.3425</v>
@@ -28161,11 +28184,11 @@
       </c>
     </row>
     <row r="111" spans="1:19" ht="12">
-      <c r="A111" s="69" t="s">
+      <c r="A111" s="75" t="s">
         <v>101</v>
       </c>
-      <c r="B111" s="69"/>
-      <c r="C111" s="69"/>
+      <c r="B111" s="75"/>
+      <c r="C111" s="75"/>
       <c r="D111" s="3">
         <f>'REALIZADO 2025'!D109*'PREVISTO 2026'!$S$110</f>
         <v>11147.161299999998</v>
@@ -28224,11 +28247,11 @@
       <c r="R111" s="5"/>
     </row>
     <row r="112" spans="1:19" ht="12">
-      <c r="A112" s="69" t="s">
+      <c r="A112" s="75" t="s">
         <v>102</v>
       </c>
-      <c r="B112" s="69"/>
-      <c r="C112" s="69"/>
+      <c r="B112" s="75"/>
+      <c r="C112" s="75"/>
       <c r="D112" s="3">
         <f>'REALIZADO 2025'!D110*'PREVISTO 2026'!$S$110</f>
         <v>1863.7366</v>
@@ -28287,11 +28310,11 @@
       <c r="R112" s="5"/>
     </row>
     <row r="113" spans="1:19" ht="12">
-      <c r="A113" s="69" t="s">
+      <c r="A113" s="75" t="s">
         <v>103</v>
       </c>
-      <c r="B113" s="69"/>
-      <c r="C113" s="69"/>
+      <c r="B113" s="75"/>
+      <c r="C113" s="75"/>
       <c r="D113" s="3">
         <f>'REALIZADO 2025'!D111*'PREVISTO 2026'!$S$110</f>
         <v>0</v>
@@ -28351,11 +28374,11 @@
       <c r="R113" s="5"/>
     </row>
     <row r="114" spans="1:19" ht="12">
-      <c r="A114" s="69" t="s">
+      <c r="A114" s="75" t="s">
         <v>104</v>
       </c>
-      <c r="B114" s="69"/>
-      <c r="C114" s="69"/>
+      <c r="B114" s="75"/>
+      <c r="C114" s="75"/>
       <c r="D114" s="3">
         <f>'REALIZADO 2025'!D112*'PREVISTO 2026'!$S$110</f>
         <v>169.6035</v>
@@ -28415,11 +28438,11 @@
       <c r="R114" s="5"/>
     </row>
     <row r="115" spans="1:19" ht="12">
-      <c r="A115" s="69" t="s">
+      <c r="A115" s="75" t="s">
         <v>105</v>
       </c>
-      <c r="B115" s="69"/>
-      <c r="C115" s="69"/>
+      <c r="B115" s="75"/>
+      <c r="C115" s="75"/>
       <c r="D115" s="3">
         <f>'REALIZADO 2025'!D113*'PREVISTO 2026'!$S$110</f>
         <v>0</v>
@@ -28479,11 +28502,11 @@
       <c r="R115" s="5"/>
     </row>
     <row r="116" spans="1:19" ht="12">
-      <c r="A116" s="69" t="s">
+      <c r="A116" s="75" t="s">
         <v>106</v>
       </c>
-      <c r="B116" s="69"/>
-      <c r="C116" s="69"/>
+      <c r="B116" s="75"/>
+      <c r="C116" s="75"/>
       <c r="D116" s="3">
         <f>'REALIZADO 2025'!D114*'PREVISTO 2026'!$S$110</f>
         <v>102.8489</v>
@@ -28543,11 +28566,11 @@
       <c r="R116" s="5"/>
     </row>
     <row r="117" spans="1:19" ht="12">
-      <c r="A117" s="69" t="s">
+      <c r="A117" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="B117" s="69"/>
-      <c r="C117" s="69"/>
+      <c r="B117" s="75"/>
+      <c r="C117" s="75"/>
       <c r="D117" s="3">
         <f>'REALIZADO 2025'!D115*'PREVISTO 2026'!$S$110</f>
         <v>208.98955000000001</v>
@@ -28607,11 +28630,11 @@
       <c r="R117" s="5"/>
     </row>
     <row r="118" spans="1:19" ht="12">
-      <c r="A118" s="69" t="s">
+      <c r="A118" s="75" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="69"/>
-      <c r="C118" s="69"/>
+      <c r="B118" s="75"/>
+      <c r="C118" s="75"/>
       <c r="D118" s="3">
         <f>'REALIZADO 2025'!D116*'PREVISTO 2026'!$S$110</f>
         <v>0</v>
@@ -28671,11 +28694,11 @@
       <c r="R118" s="5"/>
     </row>
     <row r="119" spans="1:19" ht="12">
-      <c r="A119" s="69" t="s">
+      <c r="A119" s="75" t="s">
         <v>109</v>
       </c>
-      <c r="B119" s="69"/>
-      <c r="C119" s="69"/>
+      <c r="B119" s="75"/>
+      <c r="C119" s="75"/>
       <c r="D119" s="3">
         <f>'REALIZADO 2025'!D117*'PREVISTO 2026'!$S$110</f>
         <v>101.25004999999999</v>
@@ -28735,11 +28758,11 @@
       <c r="R119" s="5"/>
     </row>
     <row r="120" spans="1:19" ht="12">
-      <c r="A120" s="69" t="s">
+      <c r="A120" s="75" t="s">
         <v>110</v>
       </c>
-      <c r="B120" s="69"/>
-      <c r="C120" s="69"/>
+      <c r="B120" s="75"/>
+      <c r="C120" s="75"/>
       <c r="D120" s="3">
         <f>'REALIZADO 2025'!D118*'PREVISTO 2026'!$S$110</f>
         <v>36.470499999999994</v>
@@ -28799,11 +28822,11 @@
       <c r="R120" s="5"/>
     </row>
     <row r="121" spans="1:19" ht="12">
-      <c r="A121" s="69" t="s">
+      <c r="A121" s="75" t="s">
         <v>111</v>
       </c>
-      <c r="B121" s="69"/>
-      <c r="C121" s="69"/>
+      <c r="B121" s="75"/>
+      <c r="C121" s="75"/>
       <c r="D121" s="3">
         <f>'REALIZADO 2025'!D119*'PREVISTO 2026'!$S$110</f>
         <v>762.84999999999991</v>
@@ -28863,11 +28886,11 @@
       <c r="R121" s="5"/>
     </row>
     <row r="122" spans="1:19" ht="12">
-      <c r="A122" s="69" t="s">
+      <c r="A122" s="75" t="s">
         <v>112</v>
       </c>
-      <c r="B122" s="69"/>
-      <c r="C122" s="69"/>
+      <c r="B122" s="75"/>
+      <c r="C122" s="75"/>
       <c r="D122" s="3">
         <f>'REALIZADO 2025'!D120*'PREVISTO 2026'!$S$110</f>
         <v>1512.3239999999998</v>
@@ -28992,11 +29015,11 @@
       <c r="S123" s="14"/>
     </row>
     <row r="124" spans="1:19" ht="12" customHeight="1">
-      <c r="A124" s="69" t="s">
+      <c r="A124" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="B124" s="92"/>
-      <c r="C124" s="92"/>
+      <c r="B124" s="81"/>
+      <c r="C124" s="81"/>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
       <c r="F124" s="6"/>
@@ -29020,11 +29043,11 @@
       <c r="R124" s="5"/>
     </row>
     <row r="125" spans="1:19" ht="12" customHeight="1">
-      <c r="A125" s="69" t="s">
+      <c r="A125" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="B125" s="92"/>
-      <c r="C125" s="92"/>
+      <c r="B125" s="81"/>
+      <c r="C125" s="81"/>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
       <c r="F125" s="6"/>
@@ -29048,11 +29071,11 @@
       <c r="R125" s="5"/>
     </row>
     <row r="126" spans="1:19" ht="12" customHeight="1">
-      <c r="A126" s="69" t="s">
+      <c r="A126" s="75" t="s">
         <v>154</v>
       </c>
-      <c r="B126" s="92"/>
-      <c r="C126" s="92"/>
+      <c r="B126" s="81"/>
+      <c r="C126" s="81"/>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
       <c r="F126" s="6"/>
@@ -29076,11 +29099,11 @@
       <c r="R126" s="5"/>
     </row>
     <row r="127" spans="1:19" ht="12" customHeight="1">
-      <c r="A127" s="69" t="s">
+      <c r="A127" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="B127" s="92"/>
-      <c r="C127" s="92"/>
+      <c r="B127" s="81"/>
+      <c r="C127" s="81"/>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
       <c r="F127" s="6"/>
@@ -29104,11 +29127,11 @@
       <c r="R127" s="5"/>
     </row>
     <row r="128" spans="1:19" ht="12" customHeight="1">
-      <c r="A128" s="69" t="s">
+      <c r="A128" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="B128" s="92"/>
-      <c r="C128" s="92"/>
+      <c r="B128" s="81"/>
+      <c r="C128" s="81"/>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
       <c r="F128" s="6"/>
@@ -29132,11 +29155,11 @@
       <c r="R128" s="5"/>
     </row>
     <row r="129" spans="1:18" ht="12" customHeight="1">
-      <c r="A129" s="69" t="s">
+      <c r="A129" s="75" t="s">
         <v>157</v>
       </c>
-      <c r="B129" s="92"/>
-      <c r="C129" s="92"/>
+      <c r="B129" s="81"/>
+      <c r="C129" s="81"/>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
       <c r="F129" s="6"/>
@@ -29160,11 +29183,11 @@
       <c r="R129" s="5"/>
     </row>
     <row r="130" spans="1:18" ht="12" customHeight="1">
-      <c r="A130" s="69" t="s">
+      <c r="A130" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="B130" s="92"/>
-      <c r="C130" s="92"/>
+      <c r="B130" s="81"/>
+      <c r="C130" s="81"/>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
       <c r="F130" s="6"/>
@@ -29188,11 +29211,11 @@
       <c r="R130" s="5"/>
     </row>
     <row r="131" spans="1:18" ht="12" customHeight="1">
-      <c r="A131" s="69" t="s">
+      <c r="A131" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="B131" s="92"/>
-      <c r="C131" s="92"/>
+      <c r="B131" s="81"/>
+      <c r="C131" s="81"/>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
       <c r="F131" s="6"/>
@@ -29216,11 +29239,11 @@
       <c r="R131" s="5"/>
     </row>
     <row r="132" spans="1:18" ht="12" customHeight="1">
-      <c r="A132" s="69" t="s">
+      <c r="A132" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="B132" s="92"/>
-      <c r="C132" s="92"/>
+      <c r="B132" s="81"/>
+      <c r="C132" s="81"/>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
       <c r="F132" s="6"/>
@@ -29244,11 +29267,11 @@
       <c r="R132" s="5"/>
     </row>
     <row r="133" spans="1:18" ht="12" customHeight="1">
-      <c r="A133" s="69" t="s">
+      <c r="A133" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="B133" s="92"/>
-      <c r="C133" s="92"/>
+      <c r="B133" s="81"/>
+      <c r="C133" s="81"/>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
       <c r="F133" s="6"/>
@@ -29272,11 +29295,11 @@
       <c r="R133" s="5"/>
     </row>
     <row r="134" spans="1:18" ht="12" customHeight="1">
-      <c r="A134" s="69" t="s">
+      <c r="A134" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="B134" s="92"/>
-      <c r="C134" s="92"/>
+      <c r="B134" s="81"/>
+      <c r="C134" s="81"/>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
       <c r="F134" s="6"/>
@@ -29300,11 +29323,11 @@
       <c r="R134" s="5"/>
     </row>
     <row r="135" spans="1:18" ht="12" customHeight="1">
-      <c r="A135" s="69" t="s">
+      <c r="A135" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="B135" s="92"/>
-      <c r="C135" s="92"/>
+      <c r="B135" s="81"/>
+      <c r="C135" s="81"/>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
       <c r="F135" s="6"/>
@@ -29328,11 +29351,11 @@
       <c r="R135" s="5"/>
     </row>
     <row r="136" spans="1:18" ht="12" customHeight="1">
-      <c r="A136" s="69" t="s">
+      <c r="A136" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="B136" s="92"/>
-      <c r="C136" s="92"/>
+      <c r="B136" s="81"/>
+      <c r="C136" s="81"/>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
       <c r="F136" s="6"/>
@@ -29356,11 +29379,11 @@
       <c r="R136" s="5"/>
     </row>
     <row r="137" spans="1:18" ht="12" customHeight="1">
-      <c r="A137" s="69" t="s">
+      <c r="A137" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="B137" s="92"/>
-      <c r="C137" s="92"/>
+      <c r="B137" s="81"/>
+      <c r="C137" s="81"/>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
       <c r="F137" s="6"/>
@@ -29384,11 +29407,11 @@
       <c r="R137" s="5"/>
     </row>
     <row r="138" spans="1:18" ht="12" customHeight="1">
-      <c r="A138" s="69" t="s">
+      <c r="A138" s="75" t="s">
         <v>166</v>
       </c>
-      <c r="B138" s="92"/>
-      <c r="C138" s="92"/>
+      <c r="B138" s="81"/>
+      <c r="C138" s="81"/>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
       <c r="F138" s="6"/>
@@ -29412,11 +29435,11 @@
       <c r="R138" s="5"/>
     </row>
     <row r="139" spans="1:18" ht="12" customHeight="1">
-      <c r="A139" s="69" t="s">
+      <c r="A139" s="75" t="s">
         <v>167</v>
       </c>
-      <c r="B139" s="92"/>
-      <c r="C139" s="92"/>
+      <c r="B139" s="81"/>
+      <c r="C139" s="81"/>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
       <c r="F139" s="6"/>
@@ -29440,11 +29463,11 @@
       <c r="R139" s="5"/>
     </row>
     <row r="140" spans="1:18" ht="12" customHeight="1">
-      <c r="A140" s="69" t="s">
+      <c r="A140" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="B140" s="92"/>
-      <c r="C140" s="92"/>
+      <c r="B140" s="81"/>
+      <c r="C140" s="81"/>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
       <c r="F140" s="6"/>
@@ -29468,11 +29491,11 @@
       <c r="R140" s="5"/>
     </row>
     <row r="141" spans="1:18" ht="12" customHeight="1">
-      <c r="A141" s="69" t="s">
+      <c r="A141" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="B141" s="92"/>
-      <c r="C141" s="92"/>
+      <c r="B141" s="81"/>
+      <c r="C141" s="81"/>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
       <c r="F141" s="6"/>
@@ -29496,11 +29519,11 @@
       <c r="R141" s="5"/>
     </row>
     <row r="142" spans="1:18" ht="12">
-      <c r="A142" s="90" t="s">
+      <c r="A142" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="B142" s="90"/>
-      <c r="C142" s="90"/>
+      <c r="B142" s="86"/>
+      <c r="C142" s="86"/>
       <c r="D142" s="45">
         <f>D27</f>
         <v>302630.67195000005</v>
@@ -29652,6 +29675,124 @@
     <row r="183" ht="12"/>
   </sheetData>
   <mergeCells count="142">
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="A86:C86"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A95:C95"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A100:C100"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A93:C93"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A108:C108"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A102:C102"/>
+    <mergeCell ref="A103:C103"/>
+    <mergeCell ref="A104:C104"/>
+    <mergeCell ref="A105:C105"/>
+    <mergeCell ref="A106:C106"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="A121:C121"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A111:C111"/>
+    <mergeCell ref="A112:C112"/>
+    <mergeCell ref="A113:C113"/>
+    <mergeCell ref="A114:C114"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="A116:C116"/>
     <mergeCell ref="A141:C141"/>
     <mergeCell ref="A142:C142"/>
     <mergeCell ref="U61:W61"/>
@@ -29676,124 +29817,6 @@
     <mergeCell ref="A117:C117"/>
     <mergeCell ref="A118:C118"/>
     <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="A121:C121"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A111:C111"/>
-    <mergeCell ref="A112:C112"/>
-    <mergeCell ref="A113:C113"/>
-    <mergeCell ref="A114:C114"/>
-    <mergeCell ref="A115:C115"/>
-    <mergeCell ref="A116:C116"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A108:C108"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A110:C110"/>
-    <mergeCell ref="A101:C101"/>
-    <mergeCell ref="A102:C102"/>
-    <mergeCell ref="A103:C103"/>
-    <mergeCell ref="A104:C104"/>
-    <mergeCell ref="A105:C105"/>
-    <mergeCell ref="A106:C106"/>
-    <mergeCell ref="A95:C95"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A89:C89"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A91:C91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A93:C93"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:C84"/>
-    <mergeCell ref="A85:C85"/>
-    <mergeCell ref="A86:C86"/>
-    <mergeCell ref="A87:C87"/>
-    <mergeCell ref="A88:C88"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A81:C81"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -29801,12 +29824,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30005,20 +30030,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{541A0B4A-F190-4BD3-B675-9D0B56ED84AA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE76326-AFB3-4BAB-B4B8-730EA1F5C7CE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e"/>
+    <ds:schemaRef ds:uri="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -30043,12 +30069,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE76326-AFB3-4BAB-B4B8-730EA1F5C7CE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{541A0B4A-F190-4BD3-B675-9D0B56ED84AA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="29a6f6d6-12cc-4ee5-bc50-ed190aecdc6e"/>
-    <ds:schemaRef ds:uri="348eb2b9-9a2d-4e0e-a7c0-e81e5a6c9f29"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>